--- a/data/Dev_Schedule.xlsx
+++ b/data/Dev_Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ohmylab-my.sharepoint.com/personal/cb_park_ohmyhotel_com/Documents/Microsoft Teams 채팅 파일/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="490" documentId="13_ncr:1_{0F904C33-17B9-4CDF-A4CC-3C44E91FED1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{882A3DA7-1289-4567-B95B-20DBE14C9EA8}"/>
+  <xr:revisionPtr revIDLastSave="494" documentId="13_ncr:1_{0F904C33-17B9-4CDF-A4CC-3C44E91FED1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8CCB3992-9609-450E-9597-A36C6CE1739E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2596" uniqueCount="646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2688" uniqueCount="655">
   <si>
     <t>API 연동 개발 트래커 — 대시보드  ·  API Integration Tracker — Dashboard</t>
   </si>
@@ -1975,6 +1975,33 @@
   </si>
   <si>
     <t>⑤ Contract Signed (30%)</t>
+  </si>
+  <si>
+    <t>OMH Supply</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>메일 활동 자동 기록 (auto from mailbox)</t>
+  </si>
+  <si>
+    <t>⑭ 고객 라이브 확정 (고객 통보) · Customer Live</t>
+  </si>
+  <si>
+    <t>NDA 체결 · NDA Signed</t>
+  </si>
+  <si>
+    <t>개발 착수 · SPEC/DEV 키 · 크리덴셜 · Kickoff / Credential</t>
+  </si>
+  <si>
+    <t>제안·소개 발송 · Proposal Sent</t>
+  </si>
+  <si>
+    <t>SLA 확정 · SLA Finalized</t>
+  </si>
+  <si>
+    <t>Switch vendors</t>
   </si>
   <si>
     <t>읽는 법 · 입력 규칙  /  How to read · how to update</t>
@@ -2598,7 +2625,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2777,6 +2804,13 @@
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="24" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2833,12 +2867,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -5238,87 +5266,87 @@
       </c>
     </row>
     <row r="4" spans="2:21" ht="30" customHeight="1">
-      <c r="B4" s="71" t="s">
+      <c r="B4" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="87"/>
-      <c r="D4" s="71" t="s">
+      <c r="C4" s="88"/>
+      <c r="D4" s="74" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="87"/>
-      <c r="F4" s="71" t="s">
+      <c r="E4" s="88"/>
+      <c r="F4" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="87"/>
-      <c r="H4" s="71" t="s">
+      <c r="G4" s="88"/>
+      <c r="H4" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="87"/>
-      <c r="J4" s="71" t="s">
+      <c r="I4" s="88"/>
+      <c r="J4" s="74" t="s">
         <v>5</v>
       </c>
-      <c r="K4" s="87"/>
-      <c r="L4" s="71" t="s">
+      <c r="K4" s="88"/>
+      <c r="L4" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="M4" s="87"/>
-      <c r="N4" s="71" t="s">
+      <c r="M4" s="88"/>
+      <c r="N4" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="O4" s="87"/>
+      <c r="O4" s="88"/>
     </row>
     <row r="5" spans="2:21">
-      <c r="B5" s="73">
+      <c r="B5" s="76">
         <f>COUNTA('스위칭 업체 Switch vendors'!$G$5:$G$400)+COUNTA('스위칭 연동 Switching'!$G$5:$G$400)+COUNTA('서드파티 연동 3rd Party'!$G$5:$G$399)+COUNTA('우리가 공급사 OMH Supply'!$G$5:$G$399)+COUNTA('상호연동 Two-way'!$G$5:$G$400)</f>
         <v>142</v>
       </c>
-      <c r="C5" s="87"/>
-      <c r="D5" s="74">
+      <c r="C5" s="88"/>
+      <c r="D5" s="77">
         <f>COUNTIF('스위칭 업체 Switch vendors'!$B$5:$B$400,"Live")+COUNTIF('스위칭 업체 Switch vendors'!$B$5:$B$400,"Partially Live")+COUNTIF('스위칭 연동 Switching'!$B$5:$B$400,"Live")+COUNTIF('스위칭 연동 Switching'!$B$5:$B$400,"Partially Live")+COUNTIF('서드파티 연동 3rd Party'!$B$5:$B$399,"Live")+COUNTIF('서드파티 연동 3rd Party'!$B$5:$B$399,"Partially Live")+COUNTIF('우리가 공급사 OMH Supply'!$B$5:$B$399,"Live")+COUNTIF('우리가 공급사 OMH Supply'!$B$5:$B$399,"Partially Live")+COUNTIF('상호연동 Two-way'!$B$5:$B$400,"Live")+COUNTIF('상호연동 Two-way'!$B$5:$B$400,"Partially Live")</f>
         <v>34</v>
       </c>
-      <c r="E5" s="87"/>
-      <c r="F5" s="75">
+      <c r="E5" s="88"/>
+      <c r="F5" s="78">
         <f>COUNTIF('스위칭 업체 Switch vendors'!$B$5:$B$400,"In Development")+COUNTIF('스위칭 업체 Switch vendors'!$B$5:$B$400,"Testing")+COUNTIF('스위칭 업체 Switch vendors'!$B$5:$B$400,"Pending Live")+COUNTIF('스위칭 연동 Switching'!$B$5:$B$400,"In Development")+COUNTIF('스위칭 연동 Switching'!$B$5:$B$400,"Testing")+COUNTIF('스위칭 연동 Switching'!$B$5:$B$400,"Pending Live")+COUNTIF('서드파티 연동 3rd Party'!$B$5:$B$399,"In Development")+COUNTIF('서드파티 연동 3rd Party'!$B$5:$B$399,"Testing")+COUNTIF('서드파티 연동 3rd Party'!$B$5:$B$399,"Pending Live")+COUNTIF('우리가 공급사 OMH Supply'!$B$5:$B$399,"In Development")+COUNTIF('우리가 공급사 OMH Supply'!$B$5:$B$399,"Testing")+COUNTIF('우리가 공급사 OMH Supply'!$B$5:$B$399,"Pending Live")+COUNTIF('상호연동 Two-way'!$B$5:$B$400,"In Development")+COUNTIF('상호연동 Two-way'!$B$5:$B$400,"Testing")+COUNTIF('상호연동 Two-way'!$B$5:$B$400,"Pending Live")</f>
         <v>14</v>
       </c>
-      <c r="G5" s="87"/>
-      <c r="H5" s="78">
+      <c r="G5" s="88"/>
+      <c r="H5" s="81">
         <f>COUNTIF('스위칭 업체 Switch vendors'!$B$5:$B$400,"NDA/Contract")+COUNTIF('스위칭 연동 Switching'!$B$5:$B$400,"NDA/Contract")+COUNTIF('서드파티 연동 3rd Party'!$B$5:$B$399,"NDA/Contract")+COUNTIF('우리가 공급사 OMH Supply'!$B$5:$B$399,"NDA/Contract")+COUNTIF('상호연동 Two-way'!$B$5:$B$400,"NDA/Contract")</f>
         <v>15</v>
       </c>
-      <c r="I5" s="87"/>
-      <c r="J5" s="79">
+      <c r="I5" s="88"/>
+      <c r="J5" s="82">
         <f>COUNTIF('스위칭 업체 Switch vendors'!$B$5:$B$400,"Pipeline")+COUNTIF('스위칭 업체 Switch vendors'!$B$5:$B$400,"Contact")+COUNTIF('스위칭 연동 Switching'!$B$5:$B$400,"Pipeline")+COUNTIF('스위칭 연동 Switching'!$B$5:$B$400,"Contact")+COUNTIF('서드파티 연동 3rd Party'!$B$5:$B$399,"Pipeline")+COUNTIF('서드파티 연동 3rd Party'!$B$5:$B$399,"Contact")+COUNTIF('우리가 공급사 OMH Supply'!$B$5:$B$399,"Pipeline")+COUNTIF('우리가 공급사 OMH Supply'!$B$5:$B$399,"Contact")+COUNTIF('상호연동 Two-way'!$B$5:$B$400,"Pipeline")+COUNTIF('상호연동 Two-way'!$B$5:$B$400,"Contact")</f>
         <v>79</v>
       </c>
-      <c r="K5" s="87"/>
-      <c r="L5" s="76">
+      <c r="K5" s="88"/>
+      <c r="L5" s="79">
         <f ca="1">COUNTIF('스위칭 업체 Switch vendors'!$V$5:$V$400,"Stalled 60d+")+COUNTIF('스위칭 업체 Switch vendors'!$V$5:$V$400,"Stalled 90d+")+COUNTIF('스위칭 연동 Switching'!$S$5:$S$400,"Stalled 60d+")+COUNTIF('스위칭 연동 Switching'!$S$5:$S$400,"Stalled 90d+")+COUNTIF('서드파티 연동 3rd Party'!$S$5:$S$399,"Stalled 60d+")+COUNTIF('서드파티 연동 3rd Party'!$S$5:$S$399,"Stalled 90d+")+COUNTIF('우리가 공급사 OMH Supply'!$S$5:$S$399,"Stalled 60d+")+COUNTIF('우리가 공급사 OMH Supply'!$S$5:$S$399,"Stalled 90d+")+COUNTIF('상호연동 Two-way'!$V$5:$V$400,"Stalled 60d+")+COUNTIF('상호연동 Two-way'!$V$5:$V$400,"Stalled 90d+")</f>
         <v>14</v>
       </c>
-      <c r="M5" s="87"/>
-      <c r="N5" s="70">
+      <c r="M5" s="88"/>
+      <c r="N5" s="73">
         <f ca="1">COUNTIF('스위칭 업체 Switch vendors'!$AC$5:$AC$400,"Chase Overdue")+COUNTIF('스위칭 업체 Switch vendors'!$AC$5:$AC$400,"Chase Needed")+COUNTIF('스위칭 연동 Switching'!$Z$5:$Z$400,"Chase Overdue")+COUNTIF('스위칭 연동 Switching'!$Z$5:$Z$400,"Chase Needed")+COUNTIF('서드파티 연동 3rd Party'!$Z$5:$Z$399,"Chase Overdue")+COUNTIF('서드파티 연동 3rd Party'!$Z$5:$Z$399,"Chase Needed")+COUNTIF('우리가 공급사 OMH Supply'!$Z$5:$Z$399,"Chase Overdue")+COUNTIF('우리가 공급사 OMH Supply'!$Z$5:$Z$399,"Chase Needed")+COUNTIF('상호연동 Two-way'!$AC$5:$AC$400,"Chase Overdue")+COUNTIF('상호연동 Two-way'!$AC$5:$AC$400,"Chase Needed")</f>
-        <v>29</v>
-      </c>
-      <c r="O5" s="87"/>
+        <v>26</v>
+      </c>
+      <c r="O5" s="88"/>
     </row>
     <row r="6" spans="2:21">
-      <c r="B6" s="87"/>
-      <c r="C6" s="87"/>
-      <c r="D6" s="87"/>
-      <c r="E6" s="87"/>
-      <c r="F6" s="87"/>
-      <c r="G6" s="87"/>
-      <c r="H6" s="87"/>
-      <c r="I6" s="87"/>
-      <c r="J6" s="87"/>
-      <c r="K6" s="87"/>
-      <c r="L6" s="87"/>
-      <c r="M6" s="87"/>
-      <c r="N6" s="87"/>
-      <c r="O6" s="87"/>
+      <c r="B6" s="88"/>
+      <c r="C6" s="88"/>
+      <c r="D6" s="88"/>
+      <c r="E6" s="88"/>
+      <c r="F6" s="88"/>
+      <c r="G6" s="88"/>
+      <c r="H6" s="88"/>
+      <c r="I6" s="88"/>
+      <c r="J6" s="88"/>
+      <c r="K6" s="88"/>
+      <c r="L6" s="88"/>
+      <c r="M6" s="88"/>
+      <c r="N6" s="88"/>
+      <c r="O6" s="88"/>
     </row>
     <row r="8" spans="2:21">
       <c r="B8" s="3" t="s">
@@ -6008,7 +6036,7 @@
       </c>
       <c r="W23" s="12">
         <f ca="1">COUNTIFS('스위칭 업체 Switch vendors'!$P$5:$P$400,$O23,'스위칭 업체 Switch vendors'!$AC$5:$AC$400,"Chase Overdue")+COUNTIFS('스위칭 업체 Switch vendors'!$P$5:$P$400,$O23,'스위칭 업체 Switch vendors'!$AC$5:$AC$400,"Chase Needed")+COUNTIFS('스위칭 연동 Switching'!$M$5:$M$400,$O23,'스위칭 연동 Switching'!$Z$5:$Z$400,"Chase Overdue")+COUNTIFS('스위칭 연동 Switching'!$M$5:$M$400,$O23,'스위칭 연동 Switching'!$Z$5:$Z$400,"Chase Needed")+COUNTIFS('서드파티 연동 3rd Party'!$M$5:$M$399,$O23,'서드파티 연동 3rd Party'!$Z$5:$Z$399,"Chase Overdue")+COUNTIFS('서드파티 연동 3rd Party'!$M$5:$M$399,$O23,'서드파티 연동 3rd Party'!$Z$5:$Z$399,"Chase Needed")+COUNTIFS('우리가 공급사 OMH Supply'!$M$5:$M$399,$O23,'우리가 공급사 OMH Supply'!$Z$5:$Z$399,"Chase Overdue")+COUNTIFS('우리가 공급사 OMH Supply'!$M$5:$M$399,$O23,'우리가 공급사 OMH Supply'!$Z$5:$Z$399,"Chase Needed")+COUNTIFS('상호연동 Two-way'!$P$5:$P$400,$O23,'상호연동 Two-way'!$AC$5:$AC$400,"Chase Overdue")+COUNTIFS('상호연동 Two-way'!$P$5:$P$400,$O23,'상호연동 Two-way'!$AC$5:$AC$400,"Chase Needed")</f>
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="15:23">
@@ -6045,7 +6073,7 @@
       </c>
       <c r="W24" s="12">
         <f ca="1">COUNTIFS('스위칭 업체 Switch vendors'!$P$5:$P$400,$O24,'스위칭 업체 Switch vendors'!$AC$5:$AC$400,"Chase Overdue")+COUNTIFS('스위칭 업체 Switch vendors'!$P$5:$P$400,$O24,'스위칭 업체 Switch vendors'!$AC$5:$AC$400,"Chase Needed")+COUNTIFS('스위칭 연동 Switching'!$M$5:$M$400,$O24,'스위칭 연동 Switching'!$Z$5:$Z$400,"Chase Overdue")+COUNTIFS('스위칭 연동 Switching'!$M$5:$M$400,$O24,'스위칭 연동 Switching'!$Z$5:$Z$400,"Chase Needed")+COUNTIFS('서드파티 연동 3rd Party'!$M$5:$M$399,$O24,'서드파티 연동 3rd Party'!$Z$5:$Z$399,"Chase Overdue")+COUNTIFS('서드파티 연동 3rd Party'!$M$5:$M$399,$O24,'서드파티 연동 3rd Party'!$Z$5:$Z$399,"Chase Needed")+COUNTIFS('우리가 공급사 OMH Supply'!$M$5:$M$399,$O24,'우리가 공급사 OMH Supply'!$Z$5:$Z$399,"Chase Overdue")+COUNTIFS('우리가 공급사 OMH Supply'!$M$5:$M$399,$O24,'우리가 공급사 OMH Supply'!$Z$5:$Z$399,"Chase Needed")+COUNTIFS('상호연동 Two-way'!$P$5:$P$400,$O24,'상호연동 Two-way'!$AC$5:$AC$400,"Chase Overdue")+COUNTIFS('상호연동 Two-way'!$P$5:$P$400,$O24,'상호연동 Two-way'!$AC$5:$AC$400,"Chase Needed")</f>
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="15:23">
@@ -6082,7 +6110,7 @@
       </c>
       <c r="W25" s="12">
         <f ca="1">COUNTIFS('스위칭 업체 Switch vendors'!$P$5:$P$400,$O25,'스위칭 업체 Switch vendors'!$AC$5:$AC$400,"Chase Overdue")+COUNTIFS('스위칭 업체 Switch vendors'!$P$5:$P$400,$O25,'스위칭 업체 Switch vendors'!$AC$5:$AC$400,"Chase Needed")+COUNTIFS('스위칭 연동 Switching'!$M$5:$M$400,$O25,'스위칭 연동 Switching'!$Z$5:$Z$400,"Chase Overdue")+COUNTIFS('스위칭 연동 Switching'!$M$5:$M$400,$O25,'스위칭 연동 Switching'!$Z$5:$Z$400,"Chase Needed")+COUNTIFS('서드파티 연동 3rd Party'!$M$5:$M$399,$O25,'서드파티 연동 3rd Party'!$Z$5:$Z$399,"Chase Overdue")+COUNTIFS('서드파티 연동 3rd Party'!$M$5:$M$399,$O25,'서드파티 연동 3rd Party'!$Z$5:$Z$399,"Chase Needed")+COUNTIFS('우리가 공급사 OMH Supply'!$M$5:$M$399,$O25,'우리가 공급사 OMH Supply'!$Z$5:$Z$399,"Chase Overdue")+COUNTIFS('우리가 공급사 OMH Supply'!$M$5:$M$399,$O25,'우리가 공급사 OMH Supply'!$Z$5:$Z$399,"Chase Needed")+COUNTIFS('상호연동 Two-way'!$P$5:$P$400,$O25,'상호연동 Two-way'!$AC$5:$AC$400,"Chase Overdue")+COUNTIFS('상호연동 Two-way'!$P$5:$P$400,$O25,'상호연동 Two-way'!$AC$5:$AC$400,"Chase Needed")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="15:23">
@@ -6220,14 +6248,14 @@
       <c r="G36" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="H36" s="77" t="s">
+      <c r="H36" s="80" t="s">
         <v>53</v>
       </c>
-      <c r="I36" s="88"/>
-      <c r="J36" s="88"/>
-      <c r="K36" s="88"/>
-      <c r="L36" s="88"/>
-      <c r="M36" s="89"/>
+      <c r="I36" s="89"/>
+      <c r="J36" s="89"/>
+      <c r="K36" s="89"/>
+      <c r="L36" s="89"/>
+      <c r="M36" s="90"/>
     </row>
     <row r="37" spans="2:13" ht="20.100000000000001" customHeight="1">
       <c r="B37" s="13" t="s">
@@ -6248,12 +6276,12 @@
       <c r="G37" s="15">
         <v>406</v>
       </c>
-      <c r="H37" s="72"/>
-      <c r="I37" s="88"/>
-      <c r="J37" s="88"/>
-      <c r="K37" s="88"/>
-      <c r="L37" s="88"/>
-      <c r="M37" s="89"/>
+      <c r="H37" s="75"/>
+      <c r="I37" s="89"/>
+      <c r="J37" s="89"/>
+      <c r="K37" s="89"/>
+      <c r="L37" s="89"/>
+      <c r="M37" s="90"/>
     </row>
     <row r="38" spans="2:13" ht="69.95" customHeight="1">
       <c r="B38" s="13" t="s">
@@ -6274,14 +6302,14 @@
       <c r="G38" s="15">
         <v>402</v>
       </c>
-      <c r="H38" s="72" t="s">
+      <c r="H38" s="75" t="s">
         <v>56</v>
       </c>
-      <c r="I38" s="88"/>
-      <c r="J38" s="88"/>
-      <c r="K38" s="88"/>
-      <c r="L38" s="88"/>
-      <c r="M38" s="89"/>
+      <c r="I38" s="89"/>
+      <c r="J38" s="89"/>
+      <c r="K38" s="89"/>
+      <c r="L38" s="89"/>
+      <c r="M38" s="90"/>
     </row>
     <row r="39" spans="2:13" ht="20.100000000000001" customHeight="1">
       <c r="B39" s="13" t="s">
@@ -6302,12 +6330,12 @@
       <c r="G39" s="15">
         <v>357</v>
       </c>
-      <c r="H39" s="72"/>
-      <c r="I39" s="88"/>
-      <c r="J39" s="88"/>
-      <c r="K39" s="88"/>
-      <c r="L39" s="88"/>
-      <c r="M39" s="89"/>
+      <c r="H39" s="75"/>
+      <c r="I39" s="89"/>
+      <c r="J39" s="89"/>
+      <c r="K39" s="89"/>
+      <c r="L39" s="89"/>
+      <c r="M39" s="90"/>
     </row>
     <row r="40" spans="2:13" ht="20.100000000000001" customHeight="1">
       <c r="B40" s="13" t="s">
@@ -6328,12 +6356,12 @@
       <c r="G40" s="15">
         <v>321</v>
       </c>
-      <c r="H40" s="72"/>
-      <c r="I40" s="88"/>
-      <c r="J40" s="88"/>
-      <c r="K40" s="88"/>
-      <c r="L40" s="88"/>
-      <c r="M40" s="89"/>
+      <c r="H40" s="75"/>
+      <c r="I40" s="89"/>
+      <c r="J40" s="89"/>
+      <c r="K40" s="89"/>
+      <c r="L40" s="89"/>
+      <c r="M40" s="90"/>
     </row>
     <row r="41" spans="2:13" ht="42" customHeight="1">
       <c r="B41" s="13" t="s">
@@ -6354,14 +6382,14 @@
       <c r="G41" s="15">
         <v>313</v>
       </c>
-      <c r="H41" s="72" t="s">
+      <c r="H41" s="75" t="s">
         <v>60</v>
       </c>
-      <c r="I41" s="88"/>
-      <c r="J41" s="88"/>
-      <c r="K41" s="88"/>
-      <c r="L41" s="88"/>
-      <c r="M41" s="89"/>
+      <c r="I41" s="89"/>
+      <c r="J41" s="89"/>
+      <c r="K41" s="89"/>
+      <c r="L41" s="89"/>
+      <c r="M41" s="90"/>
     </row>
     <row r="42" spans="2:13" ht="20.100000000000001" customHeight="1">
       <c r="B42" s="13" t="s">
@@ -6382,12 +6410,12 @@
       <c r="G42" s="15">
         <v>287</v>
       </c>
-      <c r="H42" s="72"/>
-      <c r="I42" s="88"/>
-      <c r="J42" s="88"/>
-      <c r="K42" s="88"/>
-      <c r="L42" s="88"/>
-      <c r="M42" s="89"/>
+      <c r="H42" s="75"/>
+      <c r="I42" s="89"/>
+      <c r="J42" s="89"/>
+      <c r="K42" s="89"/>
+      <c r="L42" s="89"/>
+      <c r="M42" s="90"/>
     </row>
     <row r="43" spans="2:13" ht="42" customHeight="1">
       <c r="B43" s="13" t="s">
@@ -6408,14 +6436,14 @@
       <c r="G43" s="15">
         <v>102</v>
       </c>
-      <c r="H43" s="72" t="s">
+      <c r="H43" s="75" t="s">
         <v>63</v>
       </c>
-      <c r="I43" s="88"/>
-      <c r="J43" s="88"/>
-      <c r="K43" s="88"/>
-      <c r="L43" s="88"/>
-      <c r="M43" s="89"/>
+      <c r="I43" s="89"/>
+      <c r="J43" s="89"/>
+      <c r="K43" s="89"/>
+      <c r="L43" s="89"/>
+      <c r="M43" s="90"/>
     </row>
     <row r="44" spans="2:13" ht="20.100000000000001" customHeight="1">
       <c r="B44" s="13" t="s">
@@ -6436,12 +6464,12 @@
       <c r="G44" s="15">
         <v>101</v>
       </c>
-      <c r="H44" s="72"/>
-      <c r="I44" s="88"/>
-      <c r="J44" s="88"/>
-      <c r="K44" s="88"/>
-      <c r="L44" s="88"/>
-      <c r="M44" s="89"/>
+      <c r="H44" s="75"/>
+      <c r="I44" s="89"/>
+      <c r="J44" s="89"/>
+      <c r="K44" s="89"/>
+      <c r="L44" s="89"/>
+      <c r="M44" s="90"/>
     </row>
     <row r="45" spans="2:13" ht="27.95" customHeight="1">
       <c r="B45" s="13" t="s">
@@ -6462,14 +6490,14 @@
       <c r="G45" s="15">
         <v>68</v>
       </c>
-      <c r="H45" s="72" t="s">
+      <c r="H45" s="75" t="s">
         <v>66</v>
       </c>
-      <c r="I45" s="88"/>
-      <c r="J45" s="88"/>
-      <c r="K45" s="88"/>
-      <c r="L45" s="88"/>
-      <c r="M45" s="89"/>
+      <c r="I45" s="89"/>
+      <c r="J45" s="89"/>
+      <c r="K45" s="89"/>
+      <c r="L45" s="89"/>
+      <c r="M45" s="90"/>
     </row>
     <row r="46" spans="2:13" ht="27.95" customHeight="1">
       <c r="B46" s="13" t="s">
@@ -6490,14 +6518,14 @@
       <c r="G46" s="15">
         <v>68</v>
       </c>
-      <c r="H46" s="72" t="s">
+      <c r="H46" s="75" t="s">
         <v>66</v>
       </c>
-      <c r="I46" s="88"/>
-      <c r="J46" s="88"/>
-      <c r="K46" s="88"/>
-      <c r="L46" s="88"/>
-      <c r="M46" s="89"/>
+      <c r="I46" s="89"/>
+      <c r="J46" s="89"/>
+      <c r="K46" s="89"/>
+      <c r="L46" s="89"/>
+      <c r="M46" s="90"/>
     </row>
     <row r="47" spans="2:13" ht="42" customHeight="1">
       <c r="B47" s="13" t="s">
@@ -6518,14 +6546,14 @@
       <c r="G47" s="15">
         <v>66</v>
       </c>
-      <c r="H47" s="72" t="s">
+      <c r="H47" s="75" t="s">
         <v>68</v>
       </c>
-      <c r="I47" s="88"/>
-      <c r="J47" s="88"/>
-      <c r="K47" s="88"/>
-      <c r="L47" s="88"/>
-      <c r="M47" s="89"/>
+      <c r="I47" s="89"/>
+      <c r="J47" s="89"/>
+      <c r="K47" s="89"/>
+      <c r="L47" s="89"/>
+      <c r="M47" s="90"/>
     </row>
     <row r="48" spans="2:13" ht="20.100000000000001" customHeight="1">
       <c r="B48" s="13" t="s">
@@ -6546,12 +6574,12 @@
       <c r="G48" s="15">
         <v>66</v>
       </c>
-      <c r="H48" s="72"/>
-      <c r="I48" s="88"/>
-      <c r="J48" s="88"/>
-      <c r="K48" s="88"/>
-      <c r="L48" s="88"/>
-      <c r="M48" s="89"/>
+      <c r="H48" s="75"/>
+      <c r="I48" s="89"/>
+      <c r="J48" s="89"/>
+      <c r="K48" s="89"/>
+      <c r="L48" s="89"/>
+      <c r="M48" s="90"/>
     </row>
     <row r="49" spans="2:13" ht="42" customHeight="1">
       <c r="B49" s="13" t="s">
@@ -6572,14 +6600,14 @@
       <c r="G49" s="15">
         <v>61</v>
       </c>
-      <c r="H49" s="72" t="s">
+      <c r="H49" s="75" t="s">
         <v>71</v>
       </c>
-      <c r="I49" s="88"/>
-      <c r="J49" s="88"/>
-      <c r="K49" s="88"/>
-      <c r="L49" s="88"/>
-      <c r="M49" s="89"/>
+      <c r="I49" s="89"/>
+      <c r="J49" s="89"/>
+      <c r="K49" s="89"/>
+      <c r="L49" s="89"/>
+      <c r="M49" s="90"/>
     </row>
   </sheetData>
   <mergeCells count="28">
@@ -6648,22 +6676,22 @@
       </c>
     </row>
     <row r="4" spans="2:36" ht="17.25" customHeight="1">
-      <c r="B4" s="66" t="s">
+      <c r="B4" s="69" t="s">
         <v>73</v>
       </c>
-      <c r="C4" s="66"/>
+      <c r="C4" s="69"/>
       <c r="D4"/>
-      <c r="E4" s="67">
+      <c r="E4" s="70">
         <f ca="1">EOMONTH(TODAY(),-2)+1</f>
         <v>46266</v>
       </c>
       <c r="F4" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="J4" s="68" t="s">
+      <c r="J4" s="71" t="s">
         <v>75</v>
       </c>
-      <c r="K4" s="68"/>
+      <c r="K4" s="71"/>
       <c r="L4" s="45"/>
       <c r="M4" s="65" t="s">
         <v>76</v>
@@ -6691,12 +6719,12 @@
       <c r="Z4" s="46"/>
     </row>
     <row r="5" spans="2:36" ht="17.25" customHeight="1">
-      <c r="B5" s="66"/>
-      <c r="C5" s="66"/>
+      <c r="B5" s="69"/>
+      <c r="C5" s="69"/>
       <c r="D5"/>
-      <c r="E5" s="67"/>
-      <c r="J5" s="68"/>
-      <c r="K5" s="68"/>
+      <c r="E5" s="70"/>
+      <c r="J5" s="71"/>
+      <c r="K5" s="71"/>
       <c r="L5" s="45"/>
       <c r="M5" s="65" t="s">
         <v>81</v>
@@ -6719,31 +6747,31 @@
       </c>
     </row>
     <row r="6" spans="2:36" ht="15.75" customHeight="1">
-      <c r="B6" s="69" t="s">
+      <c r="B6" s="72" t="s">
         <v>86</v>
       </c>
-      <c r="C6" s="69" t="s">
+      <c r="C6" s="72" t="s">
         <v>87</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="72" t="s">
         <v>88</v>
       </c>
-      <c r="E6" s="69" t="s">
+      <c r="E6" s="72" t="s">
         <v>89</v>
       </c>
-      <c r="F6" s="69" t="s">
+      <c r="F6" s="72" t="s">
         <v>90</v>
       </c>
-      <c r="G6" s="69" t="s">
+      <c r="G6" s="72" t="s">
         <v>91</v>
       </c>
-      <c r="H6" s="69" t="s">
+      <c r="H6" s="72" t="s">
         <v>92</v>
       </c>
-      <c r="I6" s="69" t="s">
+      <c r="I6" s="72" t="s">
         <v>93</v>
       </c>
-      <c r="J6" s="69" t="s">
+      <c r="J6" s="72" t="s">
         <v>94</v>
       </c>
       <c r="K6" s="51" t="str">
@@ -6852,15 +6880,15 @@
       </c>
     </row>
     <row r="7" spans="2:36" ht="15.75" customHeight="1">
-      <c r="B7" s="69"/>
-      <c r="C7" s="69"/>
-      <c r="D7" s="69"/>
-      <c r="E7" s="69"/>
-      <c r="F7" s="69"/>
-      <c r="G7" s="69"/>
-      <c r="H7" s="69"/>
-      <c r="I7" s="69"/>
-      <c r="J7" s="69"/>
+      <c r="B7" s="72"/>
+      <c r="C7" s="72"/>
+      <c r="D7" s="72"/>
+      <c r="E7" s="72"/>
+      <c r="F7" s="72"/>
+      <c r="G7" s="72"/>
+      <c r="H7" s="72"/>
+      <c r="I7" s="72"/>
+      <c r="J7" s="72"/>
       <c r="K7" s="51" t="str">
         <f ca="1">INT((DAY(K8)-1)/7)+1&amp;"주"</f>
         <v>5주</v>
@@ -6967,15 +6995,15 @@
       </c>
     </row>
     <row r="8" spans="2:36" ht="20.25" customHeight="1">
-      <c r="B8" s="69"/>
-      <c r="C8" s="69"/>
-      <c r="D8" s="69"/>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="69"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="69"/>
-      <c r="J8" s="69"/>
+      <c r="B8" s="72"/>
+      <c r="C8" s="72"/>
+      <c r="D8" s="72"/>
+      <c r="E8" s="72"/>
+      <c r="F8" s="72"/>
+      <c r="G8" s="72"/>
+      <c r="H8" s="72"/>
+      <c r="I8" s="72"/>
+      <c r="J8" s="72"/>
       <c r="K8" s="52">
         <f ca="1">$E$4-WEEKDAY($E$4,3)</f>
         <v>46265</v>
@@ -7089,7 +7117,7 @@
       <c r="C9" s="54" t="s">
         <v>95</v>
       </c>
-      <c r="D9" s="85"/>
+      <c r="D9" s="66"/>
       <c r="E9" s="54" t="s">
         <v>45</v>
       </c>
@@ -7143,7 +7171,7 @@
         <v/>
       </c>
       <c r="C10" s="59"/>
-      <c r="D10" s="86"/>
+      <c r="D10" s="67"/>
       <c r="E10" s="59"/>
       <c r="F10" s="60"/>
       <c r="G10" s="60"/>
@@ -7189,7 +7217,7 @@
         <v/>
       </c>
       <c r="C11" s="59"/>
-      <c r="D11" s="86"/>
+      <c r="D11" s="67"/>
       <c r="E11" s="59"/>
       <c r="F11" s="60"/>
       <c r="G11" s="60"/>
@@ -7235,7 +7263,7 @@
         <v/>
       </c>
       <c r="C12" s="59"/>
-      <c r="D12" s="86"/>
+      <c r="D12" s="67"/>
       <c r="E12" s="59"/>
       <c r="F12" s="60"/>
       <c r="G12" s="60"/>
@@ -7281,7 +7309,7 @@
         <v/>
       </c>
       <c r="C13" s="59"/>
-      <c r="D13" s="86"/>
+      <c r="D13" s="67"/>
       <c r="E13" s="59"/>
       <c r="F13" s="60"/>
       <c r="G13" s="60"/>
@@ -7327,7 +7355,7 @@
         <v/>
       </c>
       <c r="C14" s="59"/>
-      <c r="D14" s="86"/>
+      <c r="D14" s="67"/>
       <c r="E14" s="59"/>
       <c r="F14" s="60"/>
       <c r="G14" s="60"/>
@@ -7373,7 +7401,7 @@
         <v/>
       </c>
       <c r="C15" s="59"/>
-      <c r="D15" s="86"/>
+      <c r="D15" s="67"/>
       <c r="E15" s="59"/>
       <c r="F15" s="60"/>
       <c r="G15" s="60"/>
@@ -7419,7 +7447,7 @@
         <v/>
       </c>
       <c r="C16" s="59"/>
-      <c r="D16" s="86"/>
+      <c r="D16" s="67"/>
       <c r="E16" s="59"/>
       <c r="F16" s="60"/>
       <c r="G16" s="60"/>
@@ -7465,7 +7493,7 @@
         <v/>
       </c>
       <c r="C17" s="59"/>
-      <c r="D17" s="86"/>
+      <c r="D17" s="67"/>
       <c r="E17" s="59"/>
       <c r="F17" s="60"/>
       <c r="G17" s="60"/>
@@ -7511,7 +7539,7 @@
         <v/>
       </c>
       <c r="C18" s="59"/>
-      <c r="D18" s="86"/>
+      <c r="D18" s="67"/>
       <c r="E18" s="59"/>
       <c r="F18" s="60"/>
       <c r="G18" s="60"/>
@@ -7557,7 +7585,7 @@
         <v/>
       </c>
       <c r="C19" s="59"/>
-      <c r="D19" s="86"/>
+      <c r="D19" s="67"/>
       <c r="E19" s="59"/>
       <c r="F19" s="60"/>
       <c r="G19" s="60"/>
@@ -7603,7 +7631,7 @@
         <v/>
       </c>
       <c r="C20" s="59"/>
-      <c r="D20" s="86"/>
+      <c r="D20" s="67"/>
       <c r="E20" s="59"/>
       <c r="F20" s="60"/>
       <c r="G20" s="60"/>
@@ -7649,7 +7677,7 @@
         <v/>
       </c>
       <c r="C21" s="59"/>
-      <c r="D21" s="86"/>
+      <c r="D21" s="67"/>
       <c r="E21" s="59"/>
       <c r="F21" s="60"/>
       <c r="G21" s="60"/>
@@ -7695,7 +7723,7 @@
         <v/>
       </c>
       <c r="C22" s="59"/>
-      <c r="D22" s="86"/>
+      <c r="D22" s="67"/>
       <c r="E22" s="59"/>
       <c r="F22" s="60"/>
       <c r="G22" s="60"/>
@@ -7741,7 +7769,7 @@
         <v/>
       </c>
       <c r="C23" s="59"/>
-      <c r="D23" s="86"/>
+      <c r="D23" s="67"/>
       <c r="E23" s="59"/>
       <c r="F23" s="60"/>
       <c r="G23" s="60"/>
@@ -7787,7 +7815,7 @@
         <v/>
       </c>
       <c r="C24" s="59"/>
-      <c r="D24" s="86"/>
+      <c r="D24" s="67"/>
       <c r="E24" s="59"/>
       <c r="F24" s="60"/>
       <c r="G24" s="60"/>
@@ -7833,7 +7861,7 @@
         <v/>
       </c>
       <c r="C25" s="59"/>
-      <c r="D25" s="86"/>
+      <c r="D25" s="67"/>
       <c r="E25" s="59"/>
       <c r="F25" s="60"/>
       <c r="G25" s="60"/>
@@ -7879,7 +7907,7 @@
         <v/>
       </c>
       <c r="C26" s="59"/>
-      <c r="D26" s="86"/>
+      <c r="D26" s="67"/>
       <c r="E26" s="59"/>
       <c r="F26" s="60"/>
       <c r="G26" s="60"/>
@@ -7925,7 +7953,7 @@
         <v/>
       </c>
       <c r="C27" s="59"/>
-      <c r="D27" s="86"/>
+      <c r="D27" s="67"/>
       <c r="E27" s="59"/>
       <c r="F27" s="60"/>
       <c r="G27" s="60"/>
@@ -7971,7 +7999,7 @@
         <v/>
       </c>
       <c r="C28" s="59"/>
-      <c r="D28" s="86"/>
+      <c r="D28" s="67"/>
       <c r="E28" s="59"/>
       <c r="F28" s="60"/>
       <c r="G28" s="60"/>
@@ -8017,7 +8045,7 @@
         <v/>
       </c>
       <c r="C29" s="59"/>
-      <c r="D29" s="86"/>
+      <c r="D29" s="67"/>
       <c r="E29" s="59"/>
       <c r="F29" s="60"/>
       <c r="G29" s="60"/>
@@ -8063,7 +8091,7 @@
         <v/>
       </c>
       <c r="C30" s="59"/>
-      <c r="D30" s="86"/>
+      <c r="D30" s="67"/>
       <c r="E30" s="59"/>
       <c r="F30" s="60"/>
       <c r="G30" s="60"/>
@@ -8109,7 +8137,7 @@
         <v/>
       </c>
       <c r="C31" s="59"/>
-      <c r="D31" s="86"/>
+      <c r="D31" s="67"/>
       <c r="E31" s="59"/>
       <c r="F31" s="60"/>
       <c r="G31" s="60"/>
@@ -8155,7 +8183,7 @@
         <v/>
       </c>
       <c r="C32" s="59"/>
-      <c r="D32" s="86"/>
+      <c r="D32" s="67"/>
       <c r="E32" s="59"/>
       <c r="F32" s="60"/>
       <c r="G32" s="60"/>
@@ -8201,7 +8229,7 @@
         <v/>
       </c>
       <c r="C33" s="59"/>
-      <c r="D33" s="86"/>
+      <c r="D33" s="67"/>
       <c r="E33" s="59"/>
       <c r="F33" s="60"/>
       <c r="G33" s="60"/>
@@ -8247,7 +8275,7 @@
         <v/>
       </c>
       <c r="C34" s="59"/>
-      <c r="D34" s="86"/>
+      <c r="D34" s="67"/>
       <c r="E34" s="59"/>
       <c r="F34" s="60"/>
       <c r="G34" s="60"/>
@@ -8293,7 +8321,7 @@
         <v/>
       </c>
       <c r="C35" s="59"/>
-      <c r="D35" s="86"/>
+      <c r="D35" s="67"/>
       <c r="E35" s="59"/>
       <c r="F35" s="60"/>
       <c r="G35" s="60"/>
@@ -8339,7 +8367,7 @@
         <v/>
       </c>
       <c r="C36" s="59"/>
-      <c r="D36" s="86"/>
+      <c r="D36" s="67"/>
       <c r="E36" s="59"/>
       <c r="F36" s="60"/>
       <c r="G36" s="60"/>
@@ -8385,7 +8413,7 @@
         <v/>
       </c>
       <c r="C37" s="59"/>
-      <c r="D37" s="86"/>
+      <c r="D37" s="67"/>
       <c r="E37" s="59"/>
       <c r="F37" s="60"/>
       <c r="G37" s="60"/>
@@ -8431,7 +8459,7 @@
         <v/>
       </c>
       <c r="C38" s="59"/>
-      <c r="D38" s="86"/>
+      <c r="D38" s="67"/>
       <c r="E38" s="59"/>
       <c r="F38" s="60"/>
       <c r="G38" s="60"/>
@@ -8477,7 +8505,7 @@
         <v/>
       </c>
       <c r="C39" s="59"/>
-      <c r="D39" s="86"/>
+      <c r="D39" s="67"/>
       <c r="E39" s="59"/>
       <c r="F39" s="60"/>
       <c r="G39" s="60"/>
@@ -8523,7 +8551,7 @@
         <v/>
       </c>
       <c r="C40" s="59"/>
-      <c r="D40" s="86"/>
+      <c r="D40" s="67"/>
       <c r="E40" s="59"/>
       <c r="F40" s="60"/>
       <c r="G40" s="60"/>
@@ -8569,7 +8597,7 @@
         <v/>
       </c>
       <c r="C41" s="59"/>
-      <c r="D41" s="86"/>
+      <c r="D41" s="67"/>
       <c r="E41" s="59"/>
       <c r="F41" s="60"/>
       <c r="G41" s="60"/>
@@ -8615,7 +8643,7 @@
         <v/>
       </c>
       <c r="C42" s="59"/>
-      <c r="D42" s="86"/>
+      <c r="D42" s="67"/>
       <c r="E42" s="59"/>
       <c r="F42" s="60"/>
       <c r="G42" s="60"/>
@@ -8661,7 +8689,7 @@
         <v/>
       </c>
       <c r="C43" s="59"/>
-      <c r="D43" s="86"/>
+      <c r="D43" s="67"/>
       <c r="E43" s="59"/>
       <c r="F43" s="60"/>
       <c r="G43" s="60"/>
@@ -8707,7 +8735,7 @@
         <v/>
       </c>
       <c r="C44" s="59"/>
-      <c r="D44" s="86"/>
+      <c r="D44" s="67"/>
       <c r="E44" s="59"/>
       <c r="F44" s="60"/>
       <c r="G44" s="60"/>
@@ -8753,7 +8781,7 @@
         <v/>
       </c>
       <c r="C45" s="59"/>
-      <c r="D45" s="86"/>
+      <c r="D45" s="67"/>
       <c r="E45" s="59"/>
       <c r="F45" s="60"/>
       <c r="G45" s="60"/>
@@ -8799,7 +8827,7 @@
         <v/>
       </c>
       <c r="C46" s="59"/>
-      <c r="D46" s="86"/>
+      <c r="D46" s="67"/>
       <c r="E46" s="59"/>
       <c r="F46" s="60"/>
       <c r="G46" s="60"/>
@@ -8845,7 +8873,7 @@
         <v/>
       </c>
       <c r="C47" s="59"/>
-      <c r="D47" s="86"/>
+      <c r="D47" s="67"/>
       <c r="E47" s="59"/>
       <c r="F47" s="60"/>
       <c r="G47" s="60"/>
@@ -8891,7 +8919,7 @@
         <v/>
       </c>
       <c r="C48" s="59"/>
-      <c r="D48" s="86"/>
+      <c r="D48" s="67"/>
       <c r="E48" s="59"/>
       <c r="F48" s="60"/>
       <c r="G48" s="60"/>
@@ -8937,7 +8965,7 @@
         <v/>
       </c>
       <c r="C49" s="59"/>
-      <c r="D49" s="86"/>
+      <c r="D49" s="67"/>
       <c r="E49" s="59"/>
       <c r="F49" s="60"/>
       <c r="G49" s="60"/>
@@ -8983,7 +9011,7 @@
         <v/>
       </c>
       <c r="C50" s="59"/>
-      <c r="D50" s="86"/>
+      <c r="D50" s="67"/>
       <c r="E50" s="59"/>
       <c r="F50" s="60"/>
       <c r="G50" s="60"/>
@@ -9029,7 +9057,7 @@
         <v/>
       </c>
       <c r="C51" s="59"/>
-      <c r="D51" s="86"/>
+      <c r="D51" s="67"/>
       <c r="E51" s="59"/>
       <c r="F51" s="60"/>
       <c r="G51" s="60"/>
@@ -9075,7 +9103,7 @@
         <v/>
       </c>
       <c r="C52" s="59"/>
-      <c r="D52" s="86"/>
+      <c r="D52" s="67"/>
       <c r="E52" s="59"/>
       <c r="F52" s="60"/>
       <c r="G52" s="60"/>
@@ -9121,7 +9149,7 @@
         <v/>
       </c>
       <c r="C53" s="59"/>
-      <c r="D53" s="86"/>
+      <c r="D53" s="67"/>
       <c r="E53" s="59"/>
       <c r="F53" s="60"/>
       <c r="G53" s="60"/>
@@ -9167,7 +9195,7 @@
         <v/>
       </c>
       <c r="C54" s="59"/>
-      <c r="D54" s="86"/>
+      <c r="D54" s="67"/>
       <c r="E54" s="59"/>
       <c r="F54" s="60"/>
       <c r="G54" s="60"/>
@@ -9213,7 +9241,7 @@
         <v/>
       </c>
       <c r="C55" s="59"/>
-      <c r="D55" s="86"/>
+      <c r="D55" s="67"/>
       <c r="E55" s="59"/>
       <c r="F55" s="60"/>
       <c r="G55" s="60"/>
@@ -9259,7 +9287,7 @@
         <v/>
       </c>
       <c r="C56" s="59"/>
-      <c r="D56" s="86"/>
+      <c r="D56" s="67"/>
       <c r="E56" s="59"/>
       <c r="F56" s="60"/>
       <c r="G56" s="60"/>
@@ -9305,7 +9333,7 @@
         <v/>
       </c>
       <c r="C57" s="59"/>
-      <c r="D57" s="86"/>
+      <c r="D57" s="67"/>
       <c r="E57" s="59"/>
       <c r="F57" s="60"/>
       <c r="G57" s="60"/>
@@ -9351,7 +9379,7 @@
         <v/>
       </c>
       <c r="C58" s="59"/>
-      <c r="D58" s="86"/>
+      <c r="D58" s="67"/>
       <c r="E58" s="59"/>
       <c r="F58" s="60"/>
       <c r="G58" s="60"/>
@@ -9514,18 +9542,18 @@
       <c r="A1" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="84" t="s">
+      <c r="E1" s="87" t="s">
         <v>96</v>
       </c>
-      <c r="F1" s="90"/>
-      <c r="G1" s="90"/>
-      <c r="H1" s="90"/>
-      <c r="I1" s="90"/>
-      <c r="J1" s="90"/>
-      <c r="K1" s="90"/>
-      <c r="L1" s="90"/>
-      <c r="M1" s="90"/>
-      <c r="N1" s="90"/>
+      <c r="F1" s="91"/>
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="91"/>
+      <c r="J1" s="91"/>
+      <c r="K1" s="91"/>
+      <c r="L1" s="91"/>
+      <c r="M1" s="91"/>
+      <c r="N1" s="91"/>
     </row>
     <row r="2" spans="1:50">
       <c r="A2" s="18" t="str">
@@ -9579,64 +9607,64 @@
       </c>
     </row>
     <row r="3" spans="1:50" ht="21.95" customHeight="1">
-      <c r="A3" s="81" t="s">
+      <c r="A3" s="84" t="s">
         <v>98</v>
       </c>
-      <c r="B3" s="91"/>
-      <c r="C3" s="91"/>
-      <c r="D3" s="91"/>
-      <c r="E3" s="91"/>
-      <c r="F3" s="91"/>
-      <c r="G3" s="91"/>
-      <c r="H3" s="91"/>
-      <c r="I3" s="91"/>
-      <c r="J3" s="91"/>
-      <c r="K3" s="91"/>
-      <c r="L3" s="91"/>
-      <c r="M3" s="91"/>
-      <c r="N3" s="91"/>
-      <c r="O3" s="91"/>
-      <c r="P3" s="91"/>
-      <c r="Q3" s="91"/>
-      <c r="R3" s="91"/>
-      <c r="S3" s="80" t="s">
+      <c r="B3" s="92"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
+      <c r="I3" s="92"/>
+      <c r="J3" s="92"/>
+      <c r="K3" s="92"/>
+      <c r="L3" s="92"/>
+      <c r="M3" s="92"/>
+      <c r="N3" s="92"/>
+      <c r="O3" s="92"/>
+      <c r="P3" s="92"/>
+      <c r="Q3" s="92"/>
+      <c r="R3" s="92"/>
+      <c r="S3" s="83" t="s">
         <v>99</v>
       </c>
-      <c r="T3" s="92"/>
-      <c r="U3" s="92"/>
-      <c r="V3" s="92"/>
-      <c r="W3" s="92"/>
-      <c r="X3" s="92"/>
-      <c r="Y3" s="92"/>
-      <c r="Z3" s="92"/>
-      <c r="AA3" s="92"/>
-      <c r="AB3" s="92"/>
-      <c r="AC3" s="92"/>
-      <c r="AD3" s="83" t="s">
+      <c r="T3" s="93"/>
+      <c r="U3" s="93"/>
+      <c r="V3" s="93"/>
+      <c r="W3" s="93"/>
+      <c r="X3" s="93"/>
+      <c r="Y3" s="93"/>
+      <c r="Z3" s="93"/>
+      <c r="AA3" s="93"/>
+      <c r="AB3" s="93"/>
+      <c r="AC3" s="93"/>
+      <c r="AD3" s="86" t="s">
         <v>100</v>
       </c>
-      <c r="AE3" s="93"/>
-      <c r="AF3" s="93"/>
-      <c r="AG3" s="93"/>
-      <c r="AH3" s="93"/>
-      <c r="AI3" s="93"/>
-      <c r="AJ3" s="93"/>
-      <c r="AK3" s="82" t="s">
+      <c r="AE3" s="94"/>
+      <c r="AF3" s="94"/>
+      <c r="AG3" s="94"/>
+      <c r="AH3" s="94"/>
+      <c r="AI3" s="94"/>
+      <c r="AJ3" s="94"/>
+      <c r="AK3" s="85" t="s">
         <v>101</v>
       </c>
-      <c r="AL3" s="94"/>
-      <c r="AM3" s="94"/>
-      <c r="AN3" s="94"/>
-      <c r="AO3" s="94"/>
-      <c r="AP3" s="94"/>
-      <c r="AQ3" s="94"/>
-      <c r="AR3" s="94"/>
-      <c r="AS3" s="94"/>
-      <c r="AT3" s="94"/>
-      <c r="AU3" s="94"/>
-      <c r="AV3" s="94"/>
-      <c r="AW3" s="94"/>
-      <c r="AX3" s="94"/>
+      <c r="AL3" s="95"/>
+      <c r="AM3" s="95"/>
+      <c r="AN3" s="95"/>
+      <c r="AO3" s="95"/>
+      <c r="AP3" s="95"/>
+      <c r="AQ3" s="95"/>
+      <c r="AR3" s="95"/>
+      <c r="AS3" s="95"/>
+      <c r="AT3" s="95"/>
+      <c r="AU3" s="95"/>
+      <c r="AV3" s="95"/>
+      <c r="AW3" s="95"/>
+      <c r="AX3" s="95"/>
     </row>
     <row r="4" spans="1:50" ht="63.95" customHeight="1">
       <c r="A4" s="4" t="s">
@@ -10136,23 +10164,23 @@
       </c>
       <c r="Y7" s="22">
         <f>IF($G7="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G7))</f>
+        <v>1</v>
+      </c>
+      <c r="Z7" s="27">
+        <f>IF(N($Y7)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G7))</f>
+        <v>46322</v>
+      </c>
+      <c r="AA7" s="22">
+        <f t="shared" ca="1" si="7"/>
         <v>0</v>
       </c>
-      <c r="Z7" s="27" t="str">
-        <f>IF(N($Y7)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G7))</f>
-        <v/>
-      </c>
-      <c r="AA7" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="AB7" s="27" t="str">
+      <c r="AB7" s="27">
         <f>IF($Z7="","",IF(OR(AND($T7&lt;&gt;"",N($T7)&gt;N($Z7)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G7,'Chase Log'!$E$4:$E$2000,$Z7,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G7,'Chase Log'!$E$4:$E$2000,$Z7)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G7,'Chase Log'!$E$4:$E$2000,$Z7))))</f>
-        <v/>
+        <v>46329</v>
       </c>
       <c r="AC7" s="13" t="str">
         <f ca="1">IF(OR($G7="",N($S7)&gt;=1,$C7="Live",$D7&lt;&gt;""),"",IF(AND($AB7&lt;&gt;"",N($AB7)&gt;0),IF($AB7&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($T7&lt;&gt;"",N($U7)&gt;='안내 Guide'!$D$4,OR($AA7="",N($AA7)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
-        <v/>
+        <v>Scheduled</v>
       </c>
       <c r="AD7" s="28"/>
       <c r="AE7" s="25"/>
@@ -10966,18 +10994,18 @@
       <c r="A1" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="84" t="s">
+      <c r="E1" s="87" t="s">
         <v>197</v>
       </c>
-      <c r="F1" s="90"/>
-      <c r="G1" s="90"/>
-      <c r="H1" s="90"/>
-      <c r="I1" s="90"/>
-      <c r="J1" s="90"/>
-      <c r="K1" s="90"/>
-      <c r="L1" s="90"/>
-      <c r="M1" s="90"/>
-      <c r="N1" s="90"/>
+      <c r="F1" s="91"/>
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="91"/>
+      <c r="J1" s="91"/>
+      <c r="K1" s="91"/>
+      <c r="L1" s="91"/>
+      <c r="M1" s="91"/>
+      <c r="N1" s="91"/>
     </row>
     <row r="2" spans="1:47">
       <c r="A2" s="18" t="str">
@@ -11031,61 +11059,61 @@
       </c>
     </row>
     <row r="3" spans="1:47" ht="21.95" customHeight="1">
-      <c r="A3" s="81" t="s">
+      <c r="A3" s="84" t="s">
         <v>98</v>
       </c>
-      <c r="B3" s="91"/>
-      <c r="C3" s="91"/>
-      <c r="D3" s="91"/>
-      <c r="E3" s="91"/>
-      <c r="F3" s="91"/>
-      <c r="G3" s="91"/>
-      <c r="H3" s="91"/>
-      <c r="I3" s="91"/>
-      <c r="J3" s="91"/>
-      <c r="K3" s="91"/>
-      <c r="L3" s="91"/>
-      <c r="M3" s="91"/>
-      <c r="N3" s="91"/>
-      <c r="O3" s="91"/>
-      <c r="P3" s="80" t="s">
+      <c r="B3" s="92"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
+      <c r="I3" s="92"/>
+      <c r="J3" s="92"/>
+      <c r="K3" s="92"/>
+      <c r="L3" s="92"/>
+      <c r="M3" s="92"/>
+      <c r="N3" s="92"/>
+      <c r="O3" s="92"/>
+      <c r="P3" s="83" t="s">
         <v>99</v>
       </c>
-      <c r="Q3" s="92"/>
-      <c r="R3" s="92"/>
-      <c r="S3" s="92"/>
-      <c r="T3" s="92"/>
-      <c r="U3" s="92"/>
-      <c r="V3" s="92"/>
-      <c r="W3" s="92"/>
-      <c r="X3" s="92"/>
-      <c r="Y3" s="92"/>
-      <c r="Z3" s="92"/>
-      <c r="AA3" s="83" t="s">
+      <c r="Q3" s="93"/>
+      <c r="R3" s="93"/>
+      <c r="S3" s="93"/>
+      <c r="T3" s="93"/>
+      <c r="U3" s="93"/>
+      <c r="V3" s="93"/>
+      <c r="W3" s="93"/>
+      <c r="X3" s="93"/>
+      <c r="Y3" s="93"/>
+      <c r="Z3" s="93"/>
+      <c r="AA3" s="86" t="s">
         <v>100</v>
       </c>
-      <c r="AB3" s="93"/>
-      <c r="AC3" s="93"/>
-      <c r="AD3" s="93"/>
-      <c r="AE3" s="93"/>
-      <c r="AF3" s="93"/>
-      <c r="AG3" s="93"/>
-      <c r="AH3" s="82" t="s">
+      <c r="AB3" s="94"/>
+      <c r="AC3" s="94"/>
+      <c r="AD3" s="94"/>
+      <c r="AE3" s="94"/>
+      <c r="AF3" s="94"/>
+      <c r="AG3" s="94"/>
+      <c r="AH3" s="85" t="s">
         <v>101</v>
       </c>
-      <c r="AI3" s="94"/>
-      <c r="AJ3" s="94"/>
-      <c r="AK3" s="94"/>
-      <c r="AL3" s="94"/>
-      <c r="AM3" s="94"/>
-      <c r="AN3" s="94"/>
-      <c r="AO3" s="94"/>
-      <c r="AP3" s="94"/>
-      <c r="AQ3" s="94"/>
-      <c r="AR3" s="94"/>
-      <c r="AS3" s="94"/>
-      <c r="AT3" s="94"/>
-      <c r="AU3" s="94"/>
+      <c r="AI3" s="95"/>
+      <c r="AJ3" s="95"/>
+      <c r="AK3" s="95"/>
+      <c r="AL3" s="95"/>
+      <c r="AM3" s="95"/>
+      <c r="AN3" s="95"/>
+      <c r="AO3" s="95"/>
+      <c r="AP3" s="95"/>
+      <c r="AQ3" s="95"/>
+      <c r="AR3" s="95"/>
+      <c r="AS3" s="95"/>
+      <c r="AT3" s="95"/>
+      <c r="AU3" s="95"/>
     </row>
     <row r="4" spans="1:47" ht="63.95" customHeight="1">
       <c r="A4" s="4" t="s">
@@ -11778,23 +11806,23 @@
       </c>
       <c r="V9" s="22">
         <f>IF($G9="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G9))</f>
-        <v>0</v>
-      </c>
-      <c r="W9" s="27" t="str">
+        <v>1</v>
+      </c>
+      <c r="W9" s="27">
         <f>IF(N($V9)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G9))</f>
-        <v/>
-      </c>
-      <c r="X9" s="22" t="str">
+        <v>46304</v>
+      </c>
+      <c r="X9" s="22">
         <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="Y9" s="27" t="str">
+        <v>18</v>
+      </c>
+      <c r="Y9" s="27">
         <f>IF($W9="","",IF(OR(AND($Q9&lt;&gt;"",N($Q9)&gt;N($W9)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G9,'Chase Log'!$E$4:$E$2000,$W9,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G9,'Chase Log'!$E$4:$E$2000,$W9)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G9,'Chase Log'!$E$4:$E$2000,$W9))))</f>
-        <v/>
+        <v>46311</v>
       </c>
       <c r="Z9" s="13" t="str">
         <f ca="1">IF(OR($G9="",N($P9)&gt;=1,$C9="Live",$D9&lt;&gt;""),"",IF(AND($Y9&lt;&gt;"",N($Y9)&gt;0),IF($Y9&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($Q9&lt;&gt;"",N($R9)&gt;='안내 Guide'!$D$4,OR($X9="",N($X9)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
-        <v/>
+        <v>Chase Overdue</v>
       </c>
       <c r="AA9" s="28"/>
       <c r="AB9" s="25"/>
@@ -12362,23 +12390,23 @@
       </c>
       <c r="V14" s="22">
         <f>IF($G14="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G14))</f>
-        <v>0</v>
-      </c>
-      <c r="W14" s="27" t="str">
+        <v>1</v>
+      </c>
+      <c r="W14" s="27">
         <f>IF(N($V14)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G14))</f>
-        <v/>
-      </c>
-      <c r="X14" s="22" t="str">
+        <v>46303</v>
+      </c>
+      <c r="X14" s="22">
         <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="Y14" s="27" t="str">
+        <v>19</v>
+      </c>
+      <c r="Y14" s="27">
         <f>IF($W14="","",IF(OR(AND($Q14&lt;&gt;"",N($Q14)&gt;N($W14)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G14,'Chase Log'!$E$4:$E$2000,$W14,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G14,'Chase Log'!$E$4:$E$2000,$W14)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G14,'Chase Log'!$E$4:$E$2000,$W14))))</f>
-        <v/>
+        <v>46310</v>
       </c>
       <c r="Z14" s="13" t="str">
         <f ca="1">IF(OR($G14="",N($P14)&gt;=1,$C14="Live",$D14&lt;&gt;""),"",IF(AND($Y14&lt;&gt;"",N($Y14)&gt;0),IF($Y14&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($Q14&lt;&gt;"",N($R14)&gt;='안내 Guide'!$D$4,OR($X14="",N($X14)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
-        <v/>
+        <v>Chase Overdue</v>
       </c>
       <c r="AA14" s="28"/>
       <c r="AB14" s="25"/>
@@ -13222,18 +13250,18 @@
       <c r="A1" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="84" t="s">
+      <c r="E1" s="87" t="s">
         <v>277</v>
       </c>
-      <c r="F1" s="90"/>
-      <c r="G1" s="90"/>
-      <c r="H1" s="90"/>
-      <c r="I1" s="90"/>
-      <c r="J1" s="90"/>
-      <c r="K1" s="90"/>
-      <c r="L1" s="90"/>
-      <c r="M1" s="90"/>
-      <c r="N1" s="90"/>
+      <c r="F1" s="91"/>
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="91"/>
+      <c r="J1" s="91"/>
+      <c r="K1" s="91"/>
+      <c r="L1" s="91"/>
+      <c r="M1" s="91"/>
+      <c r="N1" s="91"/>
     </row>
     <row r="2" spans="1:47">
       <c r="A2" s="18" t="str">
@@ -13287,61 +13315,61 @@
       </c>
     </row>
     <row r="3" spans="1:47" ht="21.95" customHeight="1">
-      <c r="A3" s="81" t="s">
+      <c r="A3" s="84" t="s">
         <v>98</v>
       </c>
-      <c r="B3" s="91"/>
-      <c r="C3" s="91"/>
-      <c r="D3" s="91"/>
-      <c r="E3" s="91"/>
-      <c r="F3" s="91"/>
-      <c r="G3" s="91"/>
-      <c r="H3" s="91"/>
-      <c r="I3" s="91"/>
-      <c r="J3" s="91"/>
-      <c r="K3" s="91"/>
-      <c r="L3" s="91"/>
-      <c r="M3" s="91"/>
-      <c r="N3" s="91"/>
-      <c r="O3" s="91"/>
-      <c r="P3" s="80" t="s">
+      <c r="B3" s="92"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
+      <c r="I3" s="92"/>
+      <c r="J3" s="92"/>
+      <c r="K3" s="92"/>
+      <c r="L3" s="92"/>
+      <c r="M3" s="92"/>
+      <c r="N3" s="92"/>
+      <c r="O3" s="92"/>
+      <c r="P3" s="83" t="s">
         <v>99</v>
       </c>
-      <c r="Q3" s="92"/>
-      <c r="R3" s="92"/>
-      <c r="S3" s="92"/>
-      <c r="T3" s="92"/>
-      <c r="U3" s="92"/>
-      <c r="V3" s="92"/>
-      <c r="W3" s="92"/>
-      <c r="X3" s="92"/>
-      <c r="Y3" s="92"/>
-      <c r="Z3" s="92"/>
-      <c r="AA3" s="83" t="s">
+      <c r="Q3" s="93"/>
+      <c r="R3" s="93"/>
+      <c r="S3" s="93"/>
+      <c r="T3" s="93"/>
+      <c r="U3" s="93"/>
+      <c r="V3" s="93"/>
+      <c r="W3" s="93"/>
+      <c r="X3" s="93"/>
+      <c r="Y3" s="93"/>
+      <c r="Z3" s="93"/>
+      <c r="AA3" s="86" t="s">
         <v>100</v>
       </c>
-      <c r="AB3" s="93"/>
-      <c r="AC3" s="93"/>
-      <c r="AD3" s="93"/>
-      <c r="AE3" s="93"/>
-      <c r="AF3" s="93"/>
-      <c r="AG3" s="93"/>
-      <c r="AH3" s="82" t="s">
+      <c r="AB3" s="94"/>
+      <c r="AC3" s="94"/>
+      <c r="AD3" s="94"/>
+      <c r="AE3" s="94"/>
+      <c r="AF3" s="94"/>
+      <c r="AG3" s="94"/>
+      <c r="AH3" s="85" t="s">
         <v>101</v>
       </c>
-      <c r="AI3" s="94"/>
-      <c r="AJ3" s="94"/>
-      <c r="AK3" s="94"/>
-      <c r="AL3" s="94"/>
-      <c r="AM3" s="94"/>
-      <c r="AN3" s="94"/>
-      <c r="AO3" s="94"/>
-      <c r="AP3" s="94"/>
-      <c r="AQ3" s="94"/>
-      <c r="AR3" s="94"/>
-      <c r="AS3" s="94"/>
-      <c r="AT3" s="94"/>
-      <c r="AU3" s="94"/>
+      <c r="AI3" s="95"/>
+      <c r="AJ3" s="95"/>
+      <c r="AK3" s="95"/>
+      <c r="AL3" s="95"/>
+      <c r="AM3" s="95"/>
+      <c r="AN3" s="95"/>
+      <c r="AO3" s="95"/>
+      <c r="AP3" s="95"/>
+      <c r="AQ3" s="95"/>
+      <c r="AR3" s="95"/>
+      <c r="AS3" s="95"/>
+      <c r="AT3" s="95"/>
+      <c r="AU3" s="95"/>
     </row>
     <row r="4" spans="1:47" ht="63.95" customHeight="1">
       <c r="A4" s="4" t="s">
@@ -14068,18 +14096,18 @@
       <c r="A1" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="84" t="s">
+      <c r="E1" s="87" t="s">
         <v>288</v>
       </c>
-      <c r="F1" s="90"/>
-      <c r="G1" s="90"/>
-      <c r="H1" s="90"/>
-      <c r="I1" s="90"/>
-      <c r="J1" s="90"/>
-      <c r="K1" s="90"/>
-      <c r="L1" s="90"/>
-      <c r="M1" s="90"/>
-      <c r="N1" s="90"/>
+      <c r="F1" s="91"/>
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="91"/>
+      <c r="J1" s="91"/>
+      <c r="K1" s="91"/>
+      <c r="L1" s="91"/>
+      <c r="M1" s="91"/>
+      <c r="N1" s="91"/>
     </row>
     <row r="2" spans="1:47">
       <c r="A2" s="18" t="str">
@@ -14133,61 +14161,61 @@
       </c>
     </row>
     <row r="3" spans="1:47" ht="21.95" customHeight="1">
-      <c r="A3" s="81" t="s">
+      <c r="A3" s="84" t="s">
         <v>98</v>
       </c>
-      <c r="B3" s="91"/>
-      <c r="C3" s="91"/>
-      <c r="D3" s="91"/>
-      <c r="E3" s="91"/>
-      <c r="F3" s="91"/>
-      <c r="G3" s="91"/>
-      <c r="H3" s="91"/>
-      <c r="I3" s="91"/>
-      <c r="J3" s="91"/>
-      <c r="K3" s="91"/>
-      <c r="L3" s="91"/>
-      <c r="M3" s="91"/>
-      <c r="N3" s="91"/>
-      <c r="O3" s="91"/>
-      <c r="P3" s="80" t="s">
+      <c r="B3" s="92"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
+      <c r="I3" s="92"/>
+      <c r="J3" s="92"/>
+      <c r="K3" s="92"/>
+      <c r="L3" s="92"/>
+      <c r="M3" s="92"/>
+      <c r="N3" s="92"/>
+      <c r="O3" s="92"/>
+      <c r="P3" s="83" t="s">
         <v>99</v>
       </c>
-      <c r="Q3" s="92"/>
-      <c r="R3" s="92"/>
-      <c r="S3" s="92"/>
-      <c r="T3" s="92"/>
-      <c r="U3" s="92"/>
-      <c r="V3" s="92"/>
-      <c r="W3" s="92"/>
-      <c r="X3" s="92"/>
-      <c r="Y3" s="92"/>
-      <c r="Z3" s="92"/>
-      <c r="AA3" s="83" t="s">
+      <c r="Q3" s="93"/>
+      <c r="R3" s="93"/>
+      <c r="S3" s="93"/>
+      <c r="T3" s="93"/>
+      <c r="U3" s="93"/>
+      <c r="V3" s="93"/>
+      <c r="W3" s="93"/>
+      <c r="X3" s="93"/>
+      <c r="Y3" s="93"/>
+      <c r="Z3" s="93"/>
+      <c r="AA3" s="86" t="s">
         <v>100</v>
       </c>
-      <c r="AB3" s="93"/>
-      <c r="AC3" s="93"/>
-      <c r="AD3" s="93"/>
-      <c r="AE3" s="93"/>
-      <c r="AF3" s="93"/>
-      <c r="AG3" s="93"/>
-      <c r="AH3" s="82" t="s">
+      <c r="AB3" s="94"/>
+      <c r="AC3" s="94"/>
+      <c r="AD3" s="94"/>
+      <c r="AE3" s="94"/>
+      <c r="AF3" s="94"/>
+      <c r="AG3" s="94"/>
+      <c r="AH3" s="85" t="s">
         <v>101</v>
       </c>
-      <c r="AI3" s="94"/>
-      <c r="AJ3" s="94"/>
-      <c r="AK3" s="94"/>
-      <c r="AL3" s="94"/>
-      <c r="AM3" s="94"/>
-      <c r="AN3" s="94"/>
-      <c r="AO3" s="94"/>
-      <c r="AP3" s="94"/>
-      <c r="AQ3" s="94"/>
-      <c r="AR3" s="94"/>
-      <c r="AS3" s="94"/>
-      <c r="AT3" s="94"/>
-      <c r="AU3" s="94"/>
+      <c r="AI3" s="95"/>
+      <c r="AJ3" s="95"/>
+      <c r="AK3" s="95"/>
+      <c r="AL3" s="95"/>
+      <c r="AM3" s="95"/>
+      <c r="AN3" s="95"/>
+      <c r="AO3" s="95"/>
+      <c r="AP3" s="95"/>
+      <c r="AQ3" s="95"/>
+      <c r="AR3" s="95"/>
+      <c r="AS3" s="95"/>
+      <c r="AT3" s="95"/>
+      <c r="AU3" s="95"/>
     </row>
     <row r="4" spans="1:47" ht="63.95" customHeight="1">
       <c r="A4" s="4" t="s">
@@ -16407,23 +16435,23 @@
       </c>
       <c r="V21" s="22">
         <f>IF($G21="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G21))</f>
-        <v>0</v>
-      </c>
-      <c r="W21" s="27" t="str">
+        <v>1</v>
+      </c>
+      <c r="W21" s="27">
         <f>IF(N($V21)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G21))</f>
-        <v/>
-      </c>
-      <c r="X21" s="22" t="str">
+        <v>46318</v>
+      </c>
+      <c r="X21" s="22">
         <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="Y21" s="27" t="str">
+        <v>4</v>
+      </c>
+      <c r="Y21" s="27">
         <f>IF($W21="","",IF(OR(AND($Q21&lt;&gt;"",N($Q21)&gt;N($W21)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G21,'Chase Log'!$E$4:$E$2000,$W21,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G21,'Chase Log'!$E$4:$E$2000,$W21)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G21,'Chase Log'!$E$4:$E$2000,$W21))))</f>
-        <v/>
+        <v>46325</v>
       </c>
       <c r="Z21" s="13" t="str">
         <f ca="1">IF(OR($G21="",N($P21)&gt;=1,$C21="Live",$D21&lt;&gt;""),"",IF(AND($Y21&lt;&gt;"",N($Y21)&gt;0),IF($Y21&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($Q21&lt;&gt;"",N($R21)&gt;='안내 Guide'!$D$4,OR($X21="",N($X21)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
-        <v>Chase Needed</v>
+        <v>Scheduled</v>
       </c>
       <c r="AA21" s="28">
         <v>46491</v>
@@ -18247,23 +18275,23 @@
       </c>
       <c r="V37" s="22">
         <f>IF($G37="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G37))</f>
-        <v>0</v>
-      </c>
-      <c r="W37" s="27" t="str">
+        <v>1</v>
+      </c>
+      <c r="W37" s="27">
         <f>IF(N($V37)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G37))</f>
-        <v/>
-      </c>
-      <c r="X37" s="22" t="str">
+        <v>46295</v>
+      </c>
+      <c r="X37" s="22">
         <f t="shared" ref="X37:X67" ca="1" si="15">IF($W37="","",TODAY()-$W37)</f>
-        <v/>
-      </c>
-      <c r="Y37" s="27" t="str">
+        <v>27</v>
+      </c>
+      <c r="Y37" s="27">
         <f>IF($W37="","",IF(OR(AND($Q37&lt;&gt;"",N($Q37)&gt;N($W37)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G37,'Chase Log'!$E$4:$E$2000,$W37,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G37,'Chase Log'!$E$4:$E$2000,$W37)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G37,'Chase Log'!$E$4:$E$2000,$W37))))</f>
-        <v/>
+        <v>46302</v>
       </c>
       <c r="Z37" s="13" t="str">
         <f ca="1">IF(OR($G37="",N($P37)&gt;=1,$C37="Live",$D37&lt;&gt;""),"",IF(AND($Y37&lt;&gt;"",N($Y37)&gt;0),IF($Y37&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($Q37&lt;&gt;"",N($R37)&gt;='안내 Guide'!$D$4,OR($X37="",N($X37)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
-        <v/>
+        <v>Chase Overdue</v>
       </c>
       <c r="AA37" s="28"/>
       <c r="AB37" s="25"/>
@@ -18809,23 +18837,23 @@
       </c>
       <c r="V42" s="22">
         <f>IF($G42="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G42))</f>
-        <v>0</v>
-      </c>
-      <c r="W42" s="27" t="str">
+        <v>1</v>
+      </c>
+      <c r="W42" s="27">
         <f>IF(N($V42)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G42))</f>
-        <v/>
-      </c>
-      <c r="X42" s="22" t="str">
+        <v>46320</v>
+      </c>
+      <c r="X42" s="22">
         <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-      <c r="Y42" s="27" t="str">
+        <v>2</v>
+      </c>
+      <c r="Y42" s="27">
         <f>IF($W42="","",IF(OR(AND($Q42&lt;&gt;"",N($Q42)&gt;N($W42)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G42,'Chase Log'!$E$4:$E$2000,$W42,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G42,'Chase Log'!$E$4:$E$2000,$W42)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G42,'Chase Log'!$E$4:$E$2000,$W42))))</f>
-        <v/>
+        <v>46327</v>
       </c>
       <c r="Z42" s="13" t="str">
         <f ca="1">IF(OR($G42="",N($P42)&gt;=1,$C42="Live",$D42&lt;&gt;""),"",IF(AND($Y42&lt;&gt;"",N($Y42)&gt;0),IF($Y42&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($Q42&lt;&gt;"",N($R42)&gt;='안내 Guide'!$D$4,OR($X42="",N($X42)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
-        <v/>
+        <v>Scheduled</v>
       </c>
       <c r="AA42" s="28"/>
       <c r="AB42" s="25"/>
@@ -22493,19 +22521,19 @@
       </c>
       <c r="V74" s="22">
         <f>IF($G74="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G74))</f>
+        <v>1</v>
+      </c>
+      <c r="W74" s="27">
+        <f>IF(N($V74)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G74))</f>
+        <v>46322</v>
+      </c>
+      <c r="X74" s="22">
+        <f t="shared" ca="1" si="23"/>
         <v>0</v>
       </c>
-      <c r="W74" s="27" t="str">
-        <f>IF(N($V74)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G74))</f>
-        <v/>
-      </c>
-      <c r="X74" s="22" t="str">
-        <f t="shared" ca="1" si="23"/>
-        <v/>
-      </c>
-      <c r="Y74" s="27" t="str">
+      <c r="Y74" s="27">
         <f>IF($W74="","",IF(OR(AND($Q74&lt;&gt;"",N($Q74)&gt;N($W74)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G74,'Chase Log'!$E$4:$E$2000,$W74,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G74,'Chase Log'!$E$4:$E$2000,$W74)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G74,'Chase Log'!$E$4:$E$2000,$W74))))</f>
-        <v/>
+        <v>46329</v>
       </c>
       <c r="Z74" s="13" t="str">
         <f ca="1">IF(OR($G74="",N($P74)&gt;=1,$C74="Live",$D74&lt;&gt;""),"",IF(AND($Y74&lt;&gt;"",N($Y74)&gt;0),IF($Y74&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($Q74&lt;&gt;"",N($R74)&gt;='안내 Guide'!$D$4,OR($X74="",N($X74)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
@@ -25657,19 +25685,19 @@
       </c>
       <c r="V96" s="22">
         <f>IF($G96="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G96))</f>
-        <v>0</v>
-      </c>
-      <c r="W96" s="27" t="str">
+        <v>1</v>
+      </c>
+      <c r="W96" s="27">
         <f>IF(N($V96)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G96))</f>
-        <v/>
-      </c>
-      <c r="X96" s="22" t="str">
+        <v>46312</v>
+      </c>
+      <c r="X96" s="22">
         <f t="shared" ca="1" si="23"/>
-        <v/>
-      </c>
-      <c r="Y96" s="27" t="str">
+        <v>10</v>
+      </c>
+      <c r="Y96" s="27">
         <f>IF($W96="","",IF(OR(AND($Q96&lt;&gt;"",N($Q96)&gt;N($W96)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G96,'Chase Log'!$E$4:$E$2000,$W96,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G96,'Chase Log'!$E$4:$E$2000,$W96)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G96,'Chase Log'!$E$4:$E$2000,$W96))))</f>
-        <v/>
+        <v>46319</v>
       </c>
       <c r="Z96" s="13" t="str">
         <f ca="1">IF(OR($G96="",N($P96)&gt;=1,$C96="Live",$D96&lt;&gt;""),"",IF(AND($Y96&lt;&gt;"",N($Y96)&gt;0),IF($Y96&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($Q96&lt;&gt;"",N($R96)&gt;='안내 Guide'!$D$4,OR($X96="",N($X96)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
@@ -25945,19 +25973,19 @@
       </c>
       <c r="V98" s="22">
         <f>IF($G98="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G98))</f>
-        <v>0</v>
-      </c>
-      <c r="W98" s="27" t="str">
+        <v>1</v>
+      </c>
+      <c r="W98" s="27">
         <f>IF(N($V98)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G98))</f>
-        <v/>
-      </c>
-      <c r="X98" s="22" t="str">
+        <v>46321</v>
+      </c>
+      <c r="X98" s="22">
         <f t="shared" ca="1" si="23"/>
-        <v/>
-      </c>
-      <c r="Y98" s="27" t="str">
+        <v>1</v>
+      </c>
+      <c r="Y98" s="27">
         <f>IF($W98="","",IF(OR(AND($Q98&lt;&gt;"",N($Q98)&gt;N($W98)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G98,'Chase Log'!$E$4:$E$2000,$W98,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G98,'Chase Log'!$E$4:$E$2000,$W98)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G98,'Chase Log'!$E$4:$E$2000,$W98))))</f>
-        <v/>
+        <v>46328</v>
       </c>
       <c r="Z98" s="13" t="str">
         <f ca="1">IF(OR($G98="",N($P98)&gt;=1,$C98="Live",$D98&lt;&gt;""),"",IF(AND($Y98&lt;&gt;"",N($Y98)&gt;0),IF($Y98&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($Q98&lt;&gt;"",N($R98)&gt;='안내 Guide'!$D$4,OR($X98="",N($X98)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
@@ -26159,18 +26187,18 @@
       <c r="A1" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="84" t="s">
+      <c r="E1" s="87" t="s">
         <v>529</v>
       </c>
-      <c r="F1" s="90"/>
-      <c r="G1" s="90"/>
-      <c r="H1" s="90"/>
-      <c r="I1" s="90"/>
-      <c r="J1" s="90"/>
-      <c r="K1" s="90"/>
-      <c r="L1" s="90"/>
-      <c r="M1" s="90"/>
-      <c r="N1" s="90"/>
+      <c r="F1" s="91"/>
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="91"/>
+      <c r="J1" s="91"/>
+      <c r="K1" s="91"/>
+      <c r="L1" s="91"/>
+      <c r="M1" s="91"/>
+      <c r="N1" s="91"/>
     </row>
     <row r="2" spans="1:50">
       <c r="A2" s="18" t="str">
@@ -26224,64 +26252,64 @@
       </c>
     </row>
     <row r="3" spans="1:50" ht="21.95" customHeight="1">
-      <c r="A3" s="81" t="s">
+      <c r="A3" s="84" t="s">
         <v>98</v>
       </c>
-      <c r="B3" s="91"/>
-      <c r="C3" s="91"/>
-      <c r="D3" s="91"/>
-      <c r="E3" s="91"/>
-      <c r="F3" s="91"/>
-      <c r="G3" s="91"/>
-      <c r="H3" s="91"/>
-      <c r="I3" s="91"/>
-      <c r="J3" s="91"/>
-      <c r="K3" s="91"/>
-      <c r="L3" s="91"/>
-      <c r="M3" s="91"/>
-      <c r="N3" s="91"/>
-      <c r="O3" s="91"/>
-      <c r="P3" s="91"/>
-      <c r="Q3" s="91"/>
-      <c r="R3" s="91"/>
-      <c r="S3" s="80" t="s">
+      <c r="B3" s="92"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
+      <c r="I3" s="92"/>
+      <c r="J3" s="92"/>
+      <c r="K3" s="92"/>
+      <c r="L3" s="92"/>
+      <c r="M3" s="92"/>
+      <c r="N3" s="92"/>
+      <c r="O3" s="92"/>
+      <c r="P3" s="92"/>
+      <c r="Q3" s="92"/>
+      <c r="R3" s="92"/>
+      <c r="S3" s="83" t="s">
         <v>99</v>
       </c>
-      <c r="T3" s="92"/>
-      <c r="U3" s="92"/>
-      <c r="V3" s="92"/>
-      <c r="W3" s="92"/>
-      <c r="X3" s="92"/>
-      <c r="Y3" s="92"/>
-      <c r="Z3" s="92"/>
-      <c r="AA3" s="92"/>
-      <c r="AB3" s="92"/>
-      <c r="AC3" s="92"/>
-      <c r="AD3" s="83" t="s">
+      <c r="T3" s="93"/>
+      <c r="U3" s="93"/>
+      <c r="V3" s="93"/>
+      <c r="W3" s="93"/>
+      <c r="X3" s="93"/>
+      <c r="Y3" s="93"/>
+      <c r="Z3" s="93"/>
+      <c r="AA3" s="93"/>
+      <c r="AB3" s="93"/>
+      <c r="AC3" s="93"/>
+      <c r="AD3" s="86" t="s">
         <v>100</v>
       </c>
-      <c r="AE3" s="93"/>
-      <c r="AF3" s="93"/>
-      <c r="AG3" s="93"/>
-      <c r="AH3" s="93"/>
-      <c r="AI3" s="93"/>
-      <c r="AJ3" s="93"/>
-      <c r="AK3" s="82" t="s">
+      <c r="AE3" s="94"/>
+      <c r="AF3" s="94"/>
+      <c r="AG3" s="94"/>
+      <c r="AH3" s="94"/>
+      <c r="AI3" s="94"/>
+      <c r="AJ3" s="94"/>
+      <c r="AK3" s="85" t="s">
         <v>101</v>
       </c>
-      <c r="AL3" s="94"/>
-      <c r="AM3" s="94"/>
-      <c r="AN3" s="94"/>
-      <c r="AO3" s="94"/>
-      <c r="AP3" s="94"/>
-      <c r="AQ3" s="94"/>
-      <c r="AR3" s="94"/>
-      <c r="AS3" s="94"/>
-      <c r="AT3" s="94"/>
-      <c r="AU3" s="94"/>
-      <c r="AV3" s="94"/>
-      <c r="AW3" s="94"/>
-      <c r="AX3" s="94"/>
+      <c r="AL3" s="95"/>
+      <c r="AM3" s="95"/>
+      <c r="AN3" s="95"/>
+      <c r="AO3" s="95"/>
+      <c r="AP3" s="95"/>
+      <c r="AQ3" s="95"/>
+      <c r="AR3" s="95"/>
+      <c r="AS3" s="95"/>
+      <c r="AT3" s="95"/>
+      <c r="AU3" s="95"/>
+      <c r="AV3" s="95"/>
+      <c r="AW3" s="95"/>
+      <c r="AX3" s="95"/>
     </row>
     <row r="4" spans="1:50" ht="63.95" customHeight="1">
       <c r="A4" s="4" t="s">
@@ -26516,23 +26544,23 @@
       </c>
       <c r="Y5" s="22">
         <f>IF($G5="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G5))</f>
-        <v>0</v>
-      </c>
-      <c r="Z5" s="27" t="str">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="27">
         <f>IF(N($Y5)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G5))</f>
-        <v/>
-      </c>
-      <c r="AA5" s="22" t="str">
+        <v>46317</v>
+      </c>
+      <c r="AA5" s="22">
         <f t="shared" ref="AA5:AA24" ca="1" si="7">IF($Z5="","",TODAY()-$Z5)</f>
-        <v/>
-      </c>
-      <c r="AB5" s="27" t="str">
+        <v>5</v>
+      </c>
+      <c r="AB5" s="27">
         <f>IF($Z5="","",IF(OR(AND($T5&lt;&gt;"",N($T5)&gt;N($Z5)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G5,'Chase Log'!$E$4:$E$2000,$Z5,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G5,'Chase Log'!$E$4:$E$2000,$Z5)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G5,'Chase Log'!$E$4:$E$2000,$Z5))))</f>
-        <v/>
+        <v>46324</v>
       </c>
       <c r="AC5" s="13" t="str">
         <f ca="1">IF(OR($G5="",N($S5)&gt;=1,$C5="Live",$D5&lt;&gt;""),"",IF(AND($AB5&lt;&gt;"",N($AB5)&gt;0),IF($AB5&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($T5&lt;&gt;"",N($U5)&gt;='안내 Guide'!$D$4,OR($AA5="",N($AA5)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
-        <v>Chase Needed</v>
+        <v>Scheduled</v>
       </c>
       <c r="AD5" s="28"/>
       <c r="AE5" s="25"/>
@@ -26657,15 +26685,15 @@
       </c>
       <c r="Y6" s="22">
         <f>IF($G6="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G6))</f>
-        <v>0</v>
-      </c>
-      <c r="Z6" s="27" t="str">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="27">
         <f>IF(N($Y6)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G6))</f>
-        <v/>
-      </c>
-      <c r="AA6" s="22" t="str">
+        <v>46317</v>
+      </c>
+      <c r="AA6" s="22">
         <f t="shared" ca="1" si="7"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AB6" s="27" t="str">
         <f>IF($Z6="","",IF(OR(AND($T6&lt;&gt;"",N($T6)&gt;N($Z6)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G6,'Chase Log'!$E$4:$E$2000,$Z6,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G6,'Chase Log'!$E$4:$E$2000,$Z6)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G6,'Chase Log'!$E$4:$E$2000,$Z6))))</f>
@@ -26798,23 +26826,23 @@
       </c>
       <c r="Y7" s="22">
         <f>IF($G7="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G7))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z7" s="27">
         <f>IF(N($Y7)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G7))</f>
-        <v>46300</v>
+        <v>46321</v>
       </c>
       <c r="AA7" s="22">
         <f t="shared" ca="1" si="7"/>
-        <v>22</v>
-      </c>
-      <c r="AB7" s="27" t="str">
+        <v>1</v>
+      </c>
+      <c r="AB7" s="27">
         <f>IF($Z7="","",IF(OR(AND($T7&lt;&gt;"",N($T7)&gt;N($Z7)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G7,'Chase Log'!$E$4:$E$2000,$Z7,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G7,'Chase Log'!$E$4:$E$2000,$Z7)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G7,'Chase Log'!$E$4:$E$2000,$Z7))))</f>
-        <v/>
+        <v>46328</v>
       </c>
       <c r="AC7" s="13" t="str">
         <f ca="1">IF(OR($G7="",N($S7)&gt;=1,$C7="Live",$D7&lt;&gt;""),"",IF(AND($AB7&lt;&gt;"",N($AB7)&gt;0),IF($AB7&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($T7&lt;&gt;"",N($U7)&gt;='안내 Guide'!$D$4,OR($AA7="",N($AA7)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
-        <v>Chase Needed</v>
+        <v>Scheduled</v>
       </c>
       <c r="AD7" s="28"/>
       <c r="AE7" s="25"/>
@@ -27187,23 +27215,23 @@
       </c>
       <c r="Y10" s="22">
         <f>IF($G10="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G10))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z10" s="27">
         <f>IF(N($Y10)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G10))</f>
-        <v>46300</v>
+        <v>46321</v>
       </c>
       <c r="AA10" s="22">
         <f t="shared" ca="1" si="7"/>
-        <v>22</v>
-      </c>
-      <c r="AB10" s="27" t="str">
+        <v>1</v>
+      </c>
+      <c r="AB10" s="27">
         <f>IF($Z10="","",IF(OR(AND($T10&lt;&gt;"",N($T10)&gt;N($Z10)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G10,'Chase Log'!$E$4:$E$2000,$Z10,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G10,'Chase Log'!$E$4:$E$2000,$Z10)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G10,'Chase Log'!$E$4:$E$2000,$Z10))))</f>
-        <v/>
+        <v>46328</v>
       </c>
       <c r="AC10" s="13" t="str">
         <f ca="1">IF(OR($G10="",N($S10)&gt;=1,$C10="Live",$D10&lt;&gt;""),"",IF(AND($AB10&lt;&gt;"",N($AB10)&gt;0),IF($AB10&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($T10&lt;&gt;"",N($U10)&gt;='안내 Guide'!$D$4,OR($AA10="",N($AA10)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
-        <v>Chase Needed</v>
+        <v>Scheduled</v>
       </c>
       <c r="AD10" s="28"/>
       <c r="AE10" s="25"/>
@@ -27316,23 +27344,23 @@
       </c>
       <c r="Y11" s="22">
         <f>IF($G11="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G11))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z11" s="27">
         <f>IF(N($Y11)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G11))</f>
-        <v>46300</v>
+        <v>46321</v>
       </c>
       <c r="AA11" s="22">
         <f t="shared" ca="1" si="7"/>
-        <v>22</v>
-      </c>
-      <c r="AB11" s="27" t="str">
+        <v>1</v>
+      </c>
+      <c r="AB11" s="27">
         <f>IF($Z11="","",IF(OR(AND($T11&lt;&gt;"",N($T11)&gt;N($Z11)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G11,'Chase Log'!$E$4:$E$2000,$Z11,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G11,'Chase Log'!$E$4:$E$2000,$Z11)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G11,'Chase Log'!$E$4:$E$2000,$Z11))))</f>
-        <v/>
+        <v>46328</v>
       </c>
       <c r="AC11" s="13" t="str">
         <f ca="1">IF(OR($G11="",N($S11)&gt;=1,$C11="Live",$D11&lt;&gt;""),"",IF(AND($AB11&lt;&gt;"",N($AB11)&gt;0),IF($AB11&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($T11&lt;&gt;"",N($U11)&gt;='안내 Guide'!$D$4,OR($AA11="",N($AA11)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
-        <v>Chase Needed</v>
+        <v>Scheduled</v>
       </c>
       <c r="AD11" s="28"/>
       <c r="AE11" s="25"/>
@@ -27697,23 +27725,23 @@
       </c>
       <c r="Y14" s="22">
         <f>IF($G14="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G14))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z14" s="27">
         <f>IF(N($Y14)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G14))</f>
-        <v>46300</v>
+        <v>46317</v>
       </c>
       <c r="AA14" s="22">
         <f t="shared" ca="1" si="7"/>
-        <v>22</v>
-      </c>
-      <c r="AB14" s="27" t="str">
+        <v>5</v>
+      </c>
+      <c r="AB14" s="27">
         <f>IF($Z14="","",IF(OR(AND($T14&lt;&gt;"",N($T14)&gt;N($Z14)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G14,'Chase Log'!$E$4:$E$2000,$Z14,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G14,'Chase Log'!$E$4:$E$2000,$Z14)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G14,'Chase Log'!$E$4:$E$2000,$Z14))))</f>
-        <v/>
+        <v>46324</v>
       </c>
       <c r="AC14" s="13" t="str">
         <f ca="1">IF(OR($G14="",N($S14)&gt;=1,$C14="Live",$D14&lt;&gt;""),"",IF(AND($AB14&lt;&gt;"",N($AB14)&gt;0),IF($AB14&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($T14&lt;&gt;"",N($U14)&gt;='안내 Guide'!$D$4,OR($AA14="",N($AA14)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
-        <v>Chase Needed</v>
+        <v>Scheduled</v>
       </c>
       <c r="AD14" s="28"/>
       <c r="AE14" s="25"/>
@@ -27826,23 +27854,23 @@
       </c>
       <c r="Y15" s="22">
         <f>IF($G15="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G15))</f>
-        <v>0</v>
-      </c>
-      <c r="Z15" s="27" t="str">
+        <v>1</v>
+      </c>
+      <c r="Z15" s="27">
         <f>IF(N($Y15)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G15))</f>
-        <v/>
-      </c>
-      <c r="AA15" s="22" t="str">
+        <v>46321</v>
+      </c>
+      <c r="AA15" s="22">
         <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="AB15" s="27" t="str">
+        <v>1</v>
+      </c>
+      <c r="AB15" s="27">
         <f>IF($Z15="","",IF(OR(AND($T15&lt;&gt;"",N($T15)&gt;N($Z15)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G15,'Chase Log'!$E$4:$E$2000,$Z15,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G15,'Chase Log'!$E$4:$E$2000,$Z15)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G15,'Chase Log'!$E$4:$E$2000,$Z15))))</f>
-        <v/>
+        <v>46328</v>
       </c>
       <c r="AC15" s="13" t="str">
         <f ca="1">IF(OR($G15="",N($S15)&gt;=1,$C15="Live",$D15&lt;&gt;""),"",IF(AND($AB15&lt;&gt;"",N($AB15)&gt;0),IF($AB15&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($T15&lt;&gt;"",N($U15)&gt;='안내 Guide'!$D$4,OR($AA15="",N($AA15)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
-        <v/>
+        <v>Scheduled</v>
       </c>
       <c r="AD15" s="28"/>
       <c r="AE15" s="25"/>
@@ -29184,7 +29212,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr defaultRowHeight="17.45"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -29993,6 +30021,436 @@
       <c r="J28" s="28"/>
       <c r="K28" s="31" t="s">
         <v>601</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29">
+        <v>26</v>
+      </c>
+      <c r="B29" t="s">
+        <v>360</v>
+      </c>
+      <c r="C29" t="s">
+        <v>608</v>
+      </c>
+      <c r="E29" s="68">
+        <v>46295</v>
+      </c>
+      <c r="F29" t="s">
+        <v>609</v>
+      </c>
+      <c r="H29" t="s">
+        <v>610</v>
+      </c>
+      <c r="I29" t="s">
+        <v>600</v>
+      </c>
+      <c r="J29" s="68">
+        <v>46302</v>
+      </c>
+      <c r="K29" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30">
+        <v>27</v>
+      </c>
+      <c r="B30" t="s">
+        <v>246</v>
+      </c>
+      <c r="C30" t="s">
+        <v>247</v>
+      </c>
+      <c r="E30" s="68">
+        <v>46303</v>
+      </c>
+      <c r="F30" t="s">
+        <v>609</v>
+      </c>
+      <c r="H30" t="s">
+        <v>610</v>
+      </c>
+      <c r="I30" t="s">
+        <v>600</v>
+      </c>
+      <c r="J30" s="68">
+        <v>46310</v>
+      </c>
+      <c r="K30" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31">
+        <v>28</v>
+      </c>
+      <c r="B31" t="s">
+        <v>225</v>
+      </c>
+      <c r="C31" t="s">
+        <v>210</v>
+      </c>
+      <c r="E31" s="68">
+        <v>46304</v>
+      </c>
+      <c r="F31" t="s">
+        <v>609</v>
+      </c>
+      <c r="H31" t="s">
+        <v>610</v>
+      </c>
+      <c r="I31" t="s">
+        <v>600</v>
+      </c>
+      <c r="J31" s="68">
+        <v>46311</v>
+      </c>
+      <c r="K31" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32">
+        <v>29</v>
+      </c>
+      <c r="B32" t="s">
+        <v>522</v>
+      </c>
+      <c r="C32" t="s">
+        <v>201</v>
+      </c>
+      <c r="D32" t="s">
+        <v>611</v>
+      </c>
+      <c r="E32" s="68">
+        <v>46312</v>
+      </c>
+      <c r="F32" t="s">
+        <v>609</v>
+      </c>
+      <c r="H32" t="s">
+        <v>610</v>
+      </c>
+      <c r="I32" t="s">
+        <v>600</v>
+      </c>
+      <c r="J32" s="68">
+        <v>46319</v>
+      </c>
+      <c r="K32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33">
+        <v>30</v>
+      </c>
+      <c r="B33" t="s">
+        <v>556</v>
+      </c>
+      <c r="C33" t="s">
+        <v>201</v>
+      </c>
+      <c r="D33" t="s">
+        <v>612</v>
+      </c>
+      <c r="E33" s="68">
+        <v>46317</v>
+      </c>
+      <c r="F33" t="s">
+        <v>609</v>
+      </c>
+      <c r="H33" t="s">
+        <v>610</v>
+      </c>
+      <c r="I33" t="s">
+        <v>600</v>
+      </c>
+      <c r="J33" s="68">
+        <v>46324</v>
+      </c>
+      <c r="K33" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34">
+        <v>31</v>
+      </c>
+      <c r="B34" t="s">
+        <v>534</v>
+      </c>
+      <c r="C34" t="s">
+        <v>201</v>
+      </c>
+      <c r="D34" t="s">
+        <v>613</v>
+      </c>
+      <c r="E34" s="68">
+        <v>46317</v>
+      </c>
+      <c r="F34" t="s">
+        <v>609</v>
+      </c>
+      <c r="H34" t="s">
+        <v>610</v>
+      </c>
+      <c r="I34" t="s">
+        <v>600</v>
+      </c>
+      <c r="J34" s="68">
+        <v>46324</v>
+      </c>
+      <c r="K34" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35">
+        <v>32</v>
+      </c>
+      <c r="B35" t="s">
+        <v>326</v>
+      </c>
+      <c r="C35" t="s">
+        <v>201</v>
+      </c>
+      <c r="D35" t="s">
+        <v>614</v>
+      </c>
+      <c r="E35" s="68">
+        <v>46318</v>
+      </c>
+      <c r="F35" t="s">
+        <v>609</v>
+      </c>
+      <c r="H35" t="s">
+        <v>610</v>
+      </c>
+      <c r="I35" t="s">
+        <v>600</v>
+      </c>
+      <c r="J35" s="68">
+        <v>46325</v>
+      </c>
+      <c r="K35" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36">
+        <v>33</v>
+      </c>
+      <c r="B36" t="s">
+        <v>377</v>
+      </c>
+      <c r="C36" t="s">
+        <v>608</v>
+      </c>
+      <c r="E36" s="68">
+        <v>46320</v>
+      </c>
+      <c r="F36" t="s">
+        <v>609</v>
+      </c>
+      <c r="H36" t="s">
+        <v>610</v>
+      </c>
+      <c r="I36" t="s">
+        <v>600</v>
+      </c>
+      <c r="J36" s="68">
+        <v>46327</v>
+      </c>
+      <c r="K36" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37">
+        <v>34</v>
+      </c>
+      <c r="B37" t="s">
+        <v>561</v>
+      </c>
+      <c r="C37" t="s">
+        <v>252</v>
+      </c>
+      <c r="E37" s="68">
+        <v>46321</v>
+      </c>
+      <c r="F37" t="s">
+        <v>609</v>
+      </c>
+      <c r="H37" t="s">
+        <v>610</v>
+      </c>
+      <c r="I37" t="s">
+        <v>600</v>
+      </c>
+      <c r="J37" s="68">
+        <v>46328</v>
+      </c>
+      <c r="K37" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38">
+        <v>35</v>
+      </c>
+      <c r="B38" t="s">
+        <v>538</v>
+      </c>
+      <c r="C38" t="s">
+        <v>201</v>
+      </c>
+      <c r="D38" t="s">
+        <v>615</v>
+      </c>
+      <c r="E38" s="68">
+        <v>46321</v>
+      </c>
+      <c r="F38" t="s">
+        <v>609</v>
+      </c>
+      <c r="H38" t="s">
+        <v>610</v>
+      </c>
+      <c r="I38" t="s">
+        <v>600</v>
+      </c>
+      <c r="J38" s="68">
+        <v>46328</v>
+      </c>
+      <c r="K38" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39">
+        <v>36</v>
+      </c>
+      <c r="B39" t="s">
+        <v>65</v>
+      </c>
+      <c r="C39" t="s">
+        <v>201</v>
+      </c>
+      <c r="D39" t="s">
+        <v>612</v>
+      </c>
+      <c r="E39" s="68">
+        <v>46321</v>
+      </c>
+      <c r="F39" t="s">
+        <v>609</v>
+      </c>
+      <c r="H39" t="s">
+        <v>610</v>
+      </c>
+      <c r="I39" t="s">
+        <v>600</v>
+      </c>
+      <c r="J39" s="68">
+        <v>46328</v>
+      </c>
+      <c r="K39" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40">
+        <v>37</v>
+      </c>
+      <c r="B40" t="s">
+        <v>526</v>
+      </c>
+      <c r="C40" t="s">
+        <v>201</v>
+      </c>
+      <c r="D40" t="s">
+        <v>611</v>
+      </c>
+      <c r="E40" s="68">
+        <v>46321</v>
+      </c>
+      <c r="F40" t="s">
+        <v>609</v>
+      </c>
+      <c r="H40" t="s">
+        <v>610</v>
+      </c>
+      <c r="I40" t="s">
+        <v>600</v>
+      </c>
+      <c r="J40" s="68">
+        <v>46328</v>
+      </c>
+      <c r="K40" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41">
+        <v>38</v>
+      </c>
+      <c r="B41" t="s">
+        <v>452</v>
+      </c>
+      <c r="C41" t="s">
+        <v>201</v>
+      </c>
+      <c r="D41" t="s">
+        <v>611</v>
+      </c>
+      <c r="E41" s="68">
+        <v>46322</v>
+      </c>
+      <c r="F41" t="s">
+        <v>609</v>
+      </c>
+      <c r="H41" t="s">
+        <v>610</v>
+      </c>
+      <c r="I41" t="s">
+        <v>600</v>
+      </c>
+      <c r="J41" s="68">
+        <v>46329</v>
+      </c>
+      <c r="K41" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42">
+        <v>39</v>
+      </c>
+      <c r="B42" t="s">
+        <v>172</v>
+      </c>
+      <c r="C42" t="s">
+        <v>616</v>
+      </c>
+      <c r="E42" s="68">
+        <v>46322</v>
+      </c>
+      <c r="F42" t="s">
+        <v>609</v>
+      </c>
+      <c r="H42" t="s">
+        <v>610</v>
+      </c>
+      <c r="I42" t="s">
+        <v>600</v>
+      </c>
+      <c r="J42" s="68">
+        <v>46329</v>
+      </c>
+      <c r="K42" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -30014,26 +30472,26 @@
   <sheetData>
     <row r="1" spans="1:4" ht="19.899999999999999">
       <c r="A1" s="34" t="s">
-        <v>608</v>
+        <v>617</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="B3" s="35" t="s">
-        <v>609</v>
+        <v>618</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>610</v>
+        <v>619</v>
       </c>
       <c r="D3" s="35" t="s">
-        <v>611</v>
+        <v>620</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="B4" s="36" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>613</v>
+        <v>622</v>
       </c>
       <c r="D4" s="38">
         <v>7</v>
@@ -30041,13 +30499,13 @@
     </row>
     <row r="5" spans="1:4" ht="45.95" customHeight="1">
       <c r="B5" s="36" t="s">
-        <v>614</v>
+        <v>623</v>
       </c>
       <c r="C5" s="39" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="D5" s="39" t="s">
-        <v>616</v>
+        <v>625</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="45.95" customHeight="1">
@@ -30055,109 +30513,109 @@
         <v>12</v>
       </c>
       <c r="C6" s="39" t="s">
-        <v>617</v>
+        <v>626</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>618</v>
+        <v>627</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="45.95" customHeight="1">
       <c r="B7" s="36" t="s">
-        <v>619</v>
+        <v>628</v>
       </c>
       <c r="C7" s="39" t="s">
-        <v>620</v>
+        <v>629</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>621</v>
+        <v>630</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="45.95" customHeight="1">
       <c r="B8" s="36" t="s">
-        <v>622</v>
+        <v>631</v>
       </c>
       <c r="C8" s="39" t="s">
-        <v>623</v>
+        <v>632</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>624</v>
+        <v>633</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="45.95" customHeight="1">
       <c r="B9" s="36" t="s">
-        <v>625</v>
+        <v>634</v>
       </c>
       <c r="C9" s="39" t="s">
-        <v>626</v>
+        <v>635</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>627</v>
+        <v>636</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="45.95" customHeight="1">
       <c r="B10" s="36" t="s">
-        <v>628</v>
+        <v>637</v>
       </c>
       <c r="C10" s="39" t="s">
-        <v>629</v>
+        <v>638</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="45.95" customHeight="1">
       <c r="B11" s="36" t="s">
-        <v>631</v>
+        <v>640</v>
       </c>
       <c r="C11" s="39" t="s">
-        <v>632</v>
+        <v>641</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>633</v>
+        <v>642</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="45.95" customHeight="1">
       <c r="B12" s="36" t="s">
-        <v>634</v>
+        <v>643</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>635</v>
+        <v>644</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>636</v>
+        <v>645</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="45.95" customHeight="1">
       <c r="B13" s="36" t="s">
-        <v>637</v>
+        <v>646</v>
       </c>
       <c r="C13" s="39" t="s">
-        <v>638</v>
+        <v>647</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>639</v>
+        <v>648</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="45.95" customHeight="1">
       <c r="B14" s="36" t="s">
-        <v>640</v>
+        <v>649</v>
       </c>
       <c r="C14" s="39" t="s">
-        <v>641</v>
+        <v>650</v>
       </c>
       <c r="D14" s="39" t="s">
-        <v>642</v>
+        <v>651</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="45.95" customHeight="1">
       <c r="B15" s="36" t="s">
-        <v>643</v>
+        <v>652</v>
       </c>
       <c r="C15" s="39" t="s">
-        <v>644</v>
+        <v>653</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>645</v>
+        <v>654</v>
       </c>
     </row>
   </sheetData>

--- a/data/Dev_Schedule.xlsx
+++ b/data/Dev_Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ohmylab-my.sharepoint.com/personal/cb_park_ohmyhotel_com/Documents/Microsoft Teams 채팅 파일/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="547" documentId="13_ncr:1_{0F904C33-17B9-4CDF-A4CC-3C44E91FED1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E53712F8-2095-44FC-B93C-DC1F71480FFA}"/>
+  <xr:revisionPtr revIDLastSave="553" documentId="13_ncr:1_{0F904C33-17B9-4CDF-A4CC-3C44E91FED1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35532CF3-9D65-46BA-885B-91D553C21AF5}"/>
   <bookViews>
     <workbookView xWindow="-38400" yWindow="0" windowWidth="29250" windowHeight="15480" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2724" uniqueCount="673">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3435" uniqueCount="736">
   <si>
     <t>API 연동 개발 트래커 — 대시보드  ·  API Integration Tracker — Dashboard</t>
   </si>
@@ -2077,6 +2077,195 @@
   </si>
   <si>
     <t>Boney Mittal</t>
+  </si>
+  <si>
+    <t>Charlie | Veturis.com</t>
+  </si>
+  <si>
+    <t>Lee, Marie (Agoda)</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>라이브 키 오픈 (OMH 측) · Live Key Open</t>
+  </si>
+  <si>
+    <t>NGUYỄN TRẦN HẠNH NGUYÊN - MDS - Expert - Project Management</t>
+  </si>
+  <si>
+    <t>Kevin</t>
+  </si>
+  <si>
+    <t>Ida Ayu Agung Dwi Cahyantari</t>
+  </si>
+  <si>
+    <t>linhtq</t>
+  </si>
+  <si>
+    <t>Jesvin Chan</t>
+  </si>
+  <si>
+    <t>StayLah Tech</t>
+  </si>
+  <si>
+    <t>YASHIKA  TANEJA</t>
+  </si>
+  <si>
+    <t>Bui Thanh Tu</t>
+  </si>
+  <si>
+    <t>Sonali Jena</t>
+  </si>
+  <si>
+    <t>care</t>
+  </si>
+  <si>
+    <t>kimdoan.dao</t>
+  </si>
+  <si>
+    <t>Apurva Dubey</t>
+  </si>
+  <si>
+    <t>Thanh Thanh Mustgo.vn</t>
+  </si>
+  <si>
+    <t>huyen.pham</t>
+  </si>
+  <si>
+    <t>Switching</t>
+  </si>
+  <si>
+    <t>Neelanjan | RezLive.com - CR</t>
+  </si>
+  <si>
+    <t>info.del</t>
+  </si>
+  <si>
+    <t>support</t>
+  </si>
+  <si>
+    <t>Shinde, Mansi/LT/TCIL</t>
+  </si>
+  <si>
+    <t>dulich.sgn</t>
+  </si>
+  <si>
+    <t>hotro</t>
+  </si>
+  <si>
+    <t>tauseefahmeds</t>
+  </si>
+  <si>
+    <t>Nguyen Van Nha</t>
+  </si>
+  <si>
+    <t>giang.th.nguyen</t>
+  </si>
+  <si>
+    <t>Jagat Negi</t>
+  </si>
+  <si>
+    <t>계약 체결 · Contract Signed</t>
+  </si>
+  <si>
+    <t>Trang Nguyen - Chudu24</t>
+  </si>
+  <si>
+    <t>Bella He</t>
+  </si>
+  <si>
+    <t>Two-way</t>
+  </si>
+  <si>
+    <t>Christine Reyes</t>
+  </si>
+  <si>
+    <t>Shasha Yang</t>
+  </si>
+  <si>
+    <t>thuong.luu</t>
+  </si>
+  <si>
+    <t>Nora Blasco Esteban</t>
+  </si>
+  <si>
+    <t>라이브 테스트 · Live Test</t>
+  </si>
+  <si>
+    <t>Ace Zhou (周丽娟) | Shiji</t>
+  </si>
+  <si>
+    <t>Traveloka 3PS Commercial</t>
+  </si>
+  <si>
+    <t>postmaster</t>
+  </si>
+  <si>
+    <t>Group Veturis China</t>
+  </si>
+  <si>
+    <t>Seth Zhang</t>
+  </si>
+  <si>
+    <t>CHEN, Doris</t>
+  </si>
+  <si>
+    <t>Rungrot Kongphukham (Bank)</t>
+  </si>
+  <si>
+    <t>김은식</t>
+  </si>
+  <si>
+    <t>Celine Angelia</t>
+  </si>
+  <si>
+    <t>Shirley Liu</t>
+  </si>
+  <si>
+    <t>Tauseef Ahmed Siddiqui</t>
+  </si>
+  <si>
+    <t>Victor BARUS</t>
+  </si>
+  <si>
+    <t>dicky</t>
+  </si>
+  <si>
+    <t>Dicky Andriansyah</t>
+  </si>
+  <si>
+    <t>Shirley Liu | Pax2night</t>
+  </si>
+  <si>
+    <t>Aatif Khan</t>
+  </si>
+  <si>
+    <t>Virat Suptawornkul</t>
+  </si>
+  <si>
+    <t>kai.wei</t>
+  </si>
+  <si>
+    <t>allie.zhang</t>
+  </si>
+  <si>
+    <t>nisa</t>
+  </si>
+  <si>
+    <t>Jungyun Kwon</t>
+  </si>
+  <si>
+    <t>侯权</t>
+  </si>
+  <si>
+    <t>Sandra CICUENDEZ</t>
+  </si>
+  <si>
+    <t>anitya.mittal</t>
+  </si>
+  <si>
+    <t>트립토파즈 류소정_Sage</t>
   </si>
   <si>
     <t>읽는 법 · 입력 규칙  /  How to read · how to update</t>
@@ -5403,7 +5592,7 @@
       <c r="M5" s="88"/>
       <c r="N5" s="78">
         <f ca="1">COUNTIF('스위칭 업체 Switch vendors'!$AC$5:$AC$400,"Chase Overdue")+COUNTIF('스위칭 업체 Switch vendors'!$AC$5:$AC$400,"Chase Needed")+COUNTIF('스위칭 연동 Switching'!$Z$5:$Z$400,"Chase Overdue")+COUNTIF('스위칭 연동 Switching'!$Z$5:$Z$400,"Chase Needed")+COUNTIF('서드파티 연동 3rd Party'!$Z$5:$Z$399,"Chase Overdue")+COUNTIF('서드파티 연동 3rd Party'!$Z$5:$Z$399,"Chase Needed")+COUNTIF('우리가 공급사 OMH Supply'!$Z$5:$Z$399,"Chase Overdue")+COUNTIF('우리가 공급사 OMH Supply'!$Z$5:$Z$399,"Chase Needed")+COUNTIF('상호연동 Two-way'!$AC$5:$AC$400,"Chase Overdue")+COUNTIF('상호연동 Two-way'!$AC$5:$AC$400,"Chase Needed")</f>
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="O5" s="88"/>
     </row>
@@ -6111,7 +6300,7 @@
       </c>
       <c r="W23" s="12">
         <f ca="1">COUNTIFS('스위칭 업체 Switch vendors'!$P$5:$P$400,$O23,'스위칭 업체 Switch vendors'!$AC$5:$AC$400,"Chase Overdue")+COUNTIFS('스위칭 업체 Switch vendors'!$P$5:$P$400,$O23,'스위칭 업체 Switch vendors'!$AC$5:$AC$400,"Chase Needed")+COUNTIFS('스위칭 연동 Switching'!$M$5:$M$400,$O23,'스위칭 연동 Switching'!$Z$5:$Z$400,"Chase Overdue")+COUNTIFS('스위칭 연동 Switching'!$M$5:$M$400,$O23,'스위칭 연동 Switching'!$Z$5:$Z$400,"Chase Needed")+COUNTIFS('서드파티 연동 3rd Party'!$M$5:$M$399,$O23,'서드파티 연동 3rd Party'!$Z$5:$Z$399,"Chase Overdue")+COUNTIFS('서드파티 연동 3rd Party'!$M$5:$M$399,$O23,'서드파티 연동 3rd Party'!$Z$5:$Z$399,"Chase Needed")+COUNTIFS('우리가 공급사 OMH Supply'!$M$5:$M$399,$O23,'우리가 공급사 OMH Supply'!$Z$5:$Z$399,"Chase Overdue")+COUNTIFS('우리가 공급사 OMH Supply'!$M$5:$M$399,$O23,'우리가 공급사 OMH Supply'!$Z$5:$Z$399,"Chase Needed")+COUNTIFS('상호연동 Two-way'!$P$5:$P$400,$O23,'상호연동 Two-way'!$AC$5:$AC$400,"Chase Overdue")+COUNTIFS('상호연동 Two-way'!$P$5:$P$400,$O23,'상호연동 Two-way'!$AC$5:$AC$400,"Chase Needed")</f>
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="15:23">
@@ -6148,7 +6337,7 @@
       </c>
       <c r="W24" s="12">
         <f ca="1">COUNTIFS('스위칭 업체 Switch vendors'!$P$5:$P$400,$O24,'스위칭 업체 Switch vendors'!$AC$5:$AC$400,"Chase Overdue")+COUNTIFS('스위칭 업체 Switch vendors'!$P$5:$P$400,$O24,'스위칭 업체 Switch vendors'!$AC$5:$AC$400,"Chase Needed")+COUNTIFS('스위칭 연동 Switching'!$M$5:$M$400,$O24,'스위칭 연동 Switching'!$Z$5:$Z$400,"Chase Overdue")+COUNTIFS('스위칭 연동 Switching'!$M$5:$M$400,$O24,'스위칭 연동 Switching'!$Z$5:$Z$400,"Chase Needed")+COUNTIFS('서드파티 연동 3rd Party'!$M$5:$M$399,$O24,'서드파티 연동 3rd Party'!$Z$5:$Z$399,"Chase Overdue")+COUNTIFS('서드파티 연동 3rd Party'!$M$5:$M$399,$O24,'서드파티 연동 3rd Party'!$Z$5:$Z$399,"Chase Needed")+COUNTIFS('우리가 공급사 OMH Supply'!$M$5:$M$399,$O24,'우리가 공급사 OMH Supply'!$Z$5:$Z$399,"Chase Overdue")+COUNTIFS('우리가 공급사 OMH Supply'!$M$5:$M$399,$O24,'우리가 공급사 OMH Supply'!$Z$5:$Z$399,"Chase Needed")+COUNTIFS('상호연동 Two-way'!$P$5:$P$400,$O24,'상호연동 Two-way'!$AC$5:$AC$400,"Chase Overdue")+COUNTIFS('상호연동 Two-way'!$P$5:$P$400,$O24,'상호연동 Two-way'!$AC$5:$AC$400,"Chase Needed")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="15:23">
@@ -9976,23 +10165,23 @@
       </c>
       <c r="Y5" s="22">
         <f>IF($G5="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G5))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z5" s="27">
         <f>IF(N($Y5)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G5))</f>
-        <v>46300</v>
+        <v>46303</v>
       </c>
       <c r="AA5" s="22">
         <f t="shared" ref="AA5:AA12" ca="1" si="7">IF($Z5="","",TODAY()-$Z5)</f>
-        <v>25</v>
-      </c>
-      <c r="AB5" s="27" t="str">
+        <v>22</v>
+      </c>
+      <c r="AB5" s="27">
         <f>IF($Z5="","",IF(OR(AND($T5&lt;&gt;"",N($T5)&gt;N($Z5)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G5,'Chase Log'!$E$4:$E$2000,$Z5,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G5,'Chase Log'!$E$4:$E$2000,$Z5)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G5,'Chase Log'!$E$4:$E$2000,$Z5))))</f>
-        <v/>
+        <v>46310</v>
       </c>
       <c r="AC5" s="13" t="str">
         <f ca="1">IF(OR($G5="",N($S5)&gt;=1,$C5="Live",$D5&lt;&gt;""),"",IF(AND($AB5&lt;&gt;"",N($AB5)&gt;0),IF($AB5&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($T5&lt;&gt;"",N($U5)&gt;='안내 Guide'!$D$4,OR($AA5="",N($AA5)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
-        <v>Chase Needed</v>
+        <v>Chase Overdue</v>
       </c>
       <c r="AD5" s="28">
         <v>46302</v>
@@ -10242,7 +10431,7 @@
       </c>
       <c r="Y7" s="22">
         <f>IF($G7="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G7))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z7" s="27">
         <f>IF(N($Y7)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G7))</f>
@@ -11526,23 +11715,23 @@
       </c>
       <c r="V6" s="22">
         <f>IF($G6="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G6))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W6" s="27">
         <f>IF(N($V6)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G6))</f>
-        <v>46300</v>
+        <v>46321</v>
       </c>
       <c r="X6" s="22">
         <f t="shared" ca="1" si="7"/>
-        <v>25</v>
-      </c>
-      <c r="Y6" s="27" t="str">
+        <v>4</v>
+      </c>
+      <c r="Y6" s="27">
         <f>IF($W6="","",IF(OR(AND($Q6&lt;&gt;"",N($Q6)&gt;N($W6)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G6,'Chase Log'!$E$4:$E$2000,$W6,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G6,'Chase Log'!$E$4:$E$2000,$W6)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G6,'Chase Log'!$E$4:$E$2000,$W6))))</f>
-        <v/>
+        <v>46328</v>
       </c>
       <c r="Z6" s="13" t="str">
         <f ca="1">IF(OR($G6="",N($P6)&gt;=1,$C6="Live",$D6&lt;&gt;""),"",IF(AND($Y6&lt;&gt;"",N($Y6)&gt;0),IF($Y6&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($Q6&lt;&gt;"",N($R6)&gt;='안내 Guide'!$D$4,OR($X6="",N($X6)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
-        <v>Chase Needed</v>
+        <v>Scheduled</v>
       </c>
       <c r="AA6" s="28"/>
       <c r="AB6" s="25"/>
@@ -11884,7 +12073,7 @@
       </c>
       <c r="V9" s="22">
         <f>IF($G9="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G9))</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W9" s="27">
         <f>IF(N($V9)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G9))</f>
@@ -12350,23 +12539,23 @@
       </c>
       <c r="V13" s="22">
         <f>IF($G13="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G13))</f>
-        <v>0</v>
-      </c>
-      <c r="W13" s="27" t="str">
+        <v>1</v>
+      </c>
+      <c r="W13" s="27">
         <f>IF(N($V13)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G13))</f>
-        <v/>
-      </c>
-      <c r="X13" s="22" t="str">
+        <v>46323</v>
+      </c>
+      <c r="X13" s="22">
         <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="Y13" s="27" t="str">
+        <v>2</v>
+      </c>
+      <c r="Y13" s="27">
         <f>IF($W13="","",IF(OR(AND($Q13&lt;&gt;"",N($Q13)&gt;N($W13)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G13,'Chase Log'!$E$4:$E$2000,$W13,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G13,'Chase Log'!$E$4:$E$2000,$W13)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G13,'Chase Log'!$E$4:$E$2000,$W13))))</f>
-        <v/>
+        <v>46330</v>
       </c>
       <c r="Z13" s="13" t="str">
         <f ca="1">IF(OR($G13="",N($P13)&gt;=1,$C13="Live",$D13&lt;&gt;""),"",IF(AND($Y13&lt;&gt;"",N($Y13)&gt;0),IF($Y13&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($Q13&lt;&gt;"",N($R13)&gt;='안내 Guide'!$D$4,OR($X13="",N($X13)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
-        <v/>
+        <v>Scheduled</v>
       </c>
       <c r="AA13" s="28"/>
       <c r="AB13" s="25"/>
@@ -12468,19 +12657,19 @@
       </c>
       <c r="V14" s="22">
         <f>IF($G14="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G14))</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W14" s="27">
         <f>IF(N($V14)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G14))</f>
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="X14" s="22">
         <f t="shared" ca="1" si="7"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y14" s="27">
         <f>IF($W14="","",IF(OR(AND($Q14&lt;&gt;"",N($Q14)&gt;N($W14)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G14,'Chase Log'!$E$4:$E$2000,$W14,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G14,'Chase Log'!$E$4:$E$2000,$W14)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G14,'Chase Log'!$E$4:$E$2000,$W14))))</f>
-        <v>46331</v>
+        <v>46332</v>
       </c>
       <c r="Z14" s="13" t="str">
         <f ca="1">IF(OR($G14="",N($P14)&gt;=1,$C14="Live",$D14&lt;&gt;""),"",IF(AND($Y14&lt;&gt;"",N($Y14)&gt;0),IF($Y14&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($Q14&lt;&gt;"",N($R14)&gt;='안내 Guide'!$D$4,OR($X14="",N($X14)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
@@ -12586,23 +12775,23 @@
       </c>
       <c r="V15" s="22">
         <f>IF($G15="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G15))</f>
-        <v>0</v>
-      </c>
-      <c r="W15" s="27" t="str">
+        <v>4</v>
+      </c>
+      <c r="W15" s="27">
         <f>IF(N($V15)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G15))</f>
-        <v/>
-      </c>
-      <c r="X15" s="22" t="str">
+        <v>46323</v>
+      </c>
+      <c r="X15" s="22">
         <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="Y15" s="27" t="str">
+        <v>2</v>
+      </c>
+      <c r="Y15" s="27">
         <f>IF($W15="","",IF(OR(AND($Q15&lt;&gt;"",N($Q15)&gt;N($W15)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G15,'Chase Log'!$E$4:$E$2000,$W15,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G15,'Chase Log'!$E$4:$E$2000,$W15)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G15,'Chase Log'!$E$4:$E$2000,$W15))))</f>
-        <v/>
+        <v>46330</v>
       </c>
       <c r="Z15" s="13" t="str">
         <f ca="1">IF(OR($G15="",N($P15)&gt;=1,$C15="Live",$D15&lt;&gt;""),"",IF(AND($Y15&lt;&gt;"",N($Y15)&gt;0),IF($Y15&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($Q15&lt;&gt;"",N($R15)&gt;='안내 Guide'!$D$4,OR($X15="",N($X15)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
-        <v/>
+        <v>Scheduled</v>
       </c>
       <c r="AA15" s="28"/>
       <c r="AB15" s="25"/>
@@ -12698,23 +12887,23 @@
       </c>
       <c r="V16" s="22">
         <f>IF($G16="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G16))</f>
-        <v>0</v>
-      </c>
-      <c r="W16" s="27" t="str">
+        <v>1</v>
+      </c>
+      <c r="W16" s="27">
         <f>IF(N($V16)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G16))</f>
-        <v/>
-      </c>
-      <c r="X16" s="22" t="str">
+        <v>46323</v>
+      </c>
+      <c r="X16" s="22">
         <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="Y16" s="27" t="str">
+        <v>2</v>
+      </c>
+      <c r="Y16" s="27">
         <f>IF($W16="","",IF(OR(AND($Q16&lt;&gt;"",N($Q16)&gt;N($W16)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G16,'Chase Log'!$E$4:$E$2000,$W16,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G16,'Chase Log'!$E$4:$E$2000,$W16)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G16,'Chase Log'!$E$4:$E$2000,$W16))))</f>
-        <v/>
+        <v>46330</v>
       </c>
       <c r="Z16" s="13" t="str">
         <f ca="1">IF(OR($G16="",N($P16)&gt;=1,$C16="Live",$D16&lt;&gt;""),"",IF(AND($Y16&lt;&gt;"",N($Y16)&gt;0),IF($Y16&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($Q16&lt;&gt;"",N($R16)&gt;='안내 Guide'!$D$4,OR($X16="",N($X16)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
-        <v/>
+        <v>Scheduled</v>
       </c>
       <c r="AA16" s="28"/>
       <c r="AB16" s="25"/>
@@ -12810,23 +12999,23 @@
       </c>
       <c r="V17" s="22">
         <f>IF($G17="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G17))</f>
-        <v>0</v>
-      </c>
-      <c r="W17" s="27" t="str">
+        <v>1</v>
+      </c>
+      <c r="W17" s="27">
         <f>IF(N($V17)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G17))</f>
-        <v/>
-      </c>
-      <c r="X17" s="22" t="str">
+        <v>46300</v>
+      </c>
+      <c r="X17" s="22">
         <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="Y17" s="27" t="str">
+        <v>25</v>
+      </c>
+      <c r="Y17" s="27">
         <f>IF($W17="","",IF(OR(AND($Q17&lt;&gt;"",N($Q17)&gt;N($W17)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G17,'Chase Log'!$E$4:$E$2000,$W17,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G17,'Chase Log'!$E$4:$E$2000,$W17)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G17,'Chase Log'!$E$4:$E$2000,$W17))))</f>
-        <v/>
+        <v>46307</v>
       </c>
       <c r="Z17" s="13" t="str">
         <f ca="1">IF(OR($G17="",N($P17)&gt;=1,$C17="Live",$D17&lt;&gt;""),"",IF(AND($Y17&lt;&gt;"",N($Y17)&gt;0),IF($Y17&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($Q17&lt;&gt;"",N($R17)&gt;='안내 Guide'!$D$4,OR($X17="",N($X17)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
-        <v/>
+        <v>Chase Overdue</v>
       </c>
       <c r="AA17" s="28"/>
       <c r="AB17" s="25"/>
@@ -12920,23 +13109,23 @@
       </c>
       <c r="V18" s="22">
         <f>IF($G18="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G18))</f>
-        <v>0</v>
-      </c>
-      <c r="W18" s="27" t="str">
+        <v>4</v>
+      </c>
+      <c r="W18" s="27">
         <f>IF(N($V18)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G18))</f>
-        <v/>
-      </c>
-      <c r="X18" s="22" t="str">
+        <v>46324</v>
+      </c>
+      <c r="X18" s="22">
         <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="Y18" s="27" t="str">
+        <v>1</v>
+      </c>
+      <c r="Y18" s="27">
         <f>IF($W18="","",IF(OR(AND($Q18&lt;&gt;"",N($Q18)&gt;N($W18)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G18,'Chase Log'!$E$4:$E$2000,$W18,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G18,'Chase Log'!$E$4:$E$2000,$W18)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G18,'Chase Log'!$E$4:$E$2000,$W18))))</f>
-        <v/>
+        <v>46331</v>
       </c>
       <c r="Z18" s="13" t="str">
         <f ca="1">IF(OR($G18="",N($P18)&gt;=1,$C18="Live",$D18&lt;&gt;""),"",IF(AND($Y18&lt;&gt;"",N($Y18)&gt;0),IF($Y18&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($Q18&lt;&gt;"",N($R18)&gt;='안내 Guide'!$D$4,OR($X18="",N($X18)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
-        <v/>
+        <v>Scheduled</v>
       </c>
       <c r="AA18" s="28"/>
       <c r="AB18" s="25"/>
@@ -13032,23 +13221,23 @@
       </c>
       <c r="V19" s="22">
         <f>IF($G19="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G19))</f>
-        <v>0</v>
-      </c>
-      <c r="W19" s="27" t="str">
+        <v>2</v>
+      </c>
+      <c r="W19" s="27">
         <f>IF(N($V19)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G19))</f>
-        <v/>
-      </c>
-      <c r="X19" s="22" t="str">
+        <v>46302</v>
+      </c>
+      <c r="X19" s="22">
         <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="Y19" s="27" t="str">
+        <v>23</v>
+      </c>
+      <c r="Y19" s="27">
         <f>IF($W19="","",IF(OR(AND($Q19&lt;&gt;"",N($Q19)&gt;N($W19)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G19,'Chase Log'!$E$4:$E$2000,$W19,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G19,'Chase Log'!$E$4:$E$2000,$W19)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G19,'Chase Log'!$E$4:$E$2000,$W19))))</f>
-        <v/>
+        <v>46309</v>
       </c>
       <c r="Z19" s="13" t="str">
         <f ca="1">IF(OR($G19="",N($P19)&gt;=1,$C19="Live",$D19&lt;&gt;""),"",IF(AND($Y19&lt;&gt;"",N($Y19)&gt;0),IF($Y19&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($Q19&lt;&gt;"",N($R19)&gt;='안내 Guide'!$D$4,OR($X19="",N($X19)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
-        <v/>
+        <v>Chase Overdue</v>
       </c>
       <c r="AA19" s="28"/>
       <c r="AB19" s="25"/>
@@ -13996,23 +14185,23 @@
       </c>
       <c r="V8" s="22">
         <f>IF($G8="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G8))</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="27" t="str">
+        <v>3</v>
+      </c>
+      <c r="W8" s="27">
         <f>IF(N($V8)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G8))</f>
-        <v/>
-      </c>
-      <c r="X8" s="22" t="str">
+        <v>46323</v>
+      </c>
+      <c r="X8" s="22">
         <f ca="1">IF($W8="","",TODAY()-$W8)</f>
-        <v/>
-      </c>
-      <c r="Y8" s="27" t="str">
+        <v>2</v>
+      </c>
+      <c r="Y8" s="27">
         <f>IF($W8="","",IF(OR(AND($Q8&lt;&gt;"",N($Q8)&gt;N($W8)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G8,'Chase Log'!$E$4:$E$2000,$W8,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G8,'Chase Log'!$E$4:$E$2000,$W8)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G8,'Chase Log'!$E$4:$E$2000,$W8))))</f>
-        <v/>
+        <v>46330</v>
       </c>
       <c r="Z8" s="13" t="str">
         <f ca="1">IF(OR($G8="",N($P8)&gt;=1,$C8="Live",$D8&lt;&gt;""),"",IF(AND($Y8&lt;&gt;"",N($Y8)&gt;0),IF($Y8&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($Q8&lt;&gt;"",N($R8)&gt;='안내 Guide'!$D$4,OR($X8="",N($X8)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
-        <v/>
+        <v>Scheduled</v>
       </c>
       <c r="AA8" s="28"/>
       <c r="AB8" s="25"/>
@@ -14644,23 +14833,23 @@
       </c>
       <c r="V6" s="22">
         <f>IF($G6="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G6))</f>
-        <v>0</v>
-      </c>
-      <c r="W6" s="27" t="str">
+        <v>2</v>
+      </c>
+      <c r="W6" s="27">
         <f>IF(N($V6)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G6))</f>
-        <v/>
-      </c>
-      <c r="X6" s="22" t="str">
+        <v>46297</v>
+      </c>
+      <c r="X6" s="22">
         <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="Y6" s="27" t="str">
+        <v>28</v>
+      </c>
+      <c r="Y6" s="27">
         <f>IF($W6="","",IF(OR(AND($Q6&lt;&gt;"",N($Q6)&gt;N($W6)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G6,'Chase Log'!$E$4:$E$2000,$W6,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G6,'Chase Log'!$E$4:$E$2000,$W6)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G6,'Chase Log'!$E$4:$E$2000,$W6))))</f>
-        <v/>
+        <v>46304</v>
       </c>
       <c r="Z6" s="13" t="str">
         <f ca="1">IF(OR($G6="",N($P6)&gt;=1,$C6="Live",$D6&lt;&gt;""),"",IF(AND($Y6&lt;&gt;"",N($Y6)&gt;0),IF($Y6&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($Q6&lt;&gt;"",N($R6)&gt;='안내 Guide'!$D$4,OR($X6="",N($X6)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
-        <v>Chase Needed</v>
+        <v>Chase Overdue</v>
       </c>
       <c r="AA6" s="28">
         <v>46372</v>
@@ -16516,7 +16705,7 @@
       </c>
       <c r="V21" s="22">
         <f>IF($G21="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G21))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W21" s="27">
         <f>IF(N($V21)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G21))</f>
@@ -17896,23 +18085,23 @@
       </c>
       <c r="V33" s="22">
         <f>IF($G33="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G33))</f>
-        <v>0</v>
-      </c>
-      <c r="W33" s="27" t="str">
+        <v>1</v>
+      </c>
+      <c r="W33" s="27">
         <f>IF(N($V33)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G33))</f>
-        <v/>
-      </c>
-      <c r="X33" s="22" t="str">
+        <v>46300</v>
+      </c>
+      <c r="X33" s="22">
         <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="Y33" s="27" t="str">
+        <v>25</v>
+      </c>
+      <c r="Y33" s="27">
         <f>IF($W33="","",IF(OR(AND($Q33&lt;&gt;"",N($Q33)&gt;N($W33)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G33,'Chase Log'!$E$4:$E$2000,$W33,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G33,'Chase Log'!$E$4:$E$2000,$W33)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G33,'Chase Log'!$E$4:$E$2000,$W33))))</f>
-        <v/>
+        <v>46307</v>
       </c>
       <c r="Z33" s="13" t="str">
         <f ca="1">IF(OR($G33="",N($P33)&gt;=1,$C33="Live",$D33&lt;&gt;""),"",IF(AND($Y33&lt;&gt;"",N($Y33)&gt;0),IF($Y33&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($Q33&lt;&gt;"",N($R33)&gt;='안내 Guide'!$D$4,OR($X33="",N($X33)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
-        <v/>
+        <v>Chase Overdue</v>
       </c>
       <c r="AA33" s="28">
         <v>46400</v>
@@ -18018,23 +18207,23 @@
       </c>
       <c r="V34" s="22">
         <f>IF($G34="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G34))</f>
-        <v>0</v>
-      </c>
-      <c r="W34" s="27" t="str">
+        <v>1</v>
+      </c>
+      <c r="W34" s="27">
         <f>IF(N($V34)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G34))</f>
-        <v/>
-      </c>
-      <c r="X34" s="22" t="str">
+        <v>46301</v>
+      </c>
+      <c r="X34" s="22">
         <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="Y34" s="27" t="str">
+        <v>24</v>
+      </c>
+      <c r="Y34" s="27">
         <f>IF($W34="","",IF(OR(AND($Q34&lt;&gt;"",N($Q34)&gt;N($W34)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G34,'Chase Log'!$E$4:$E$2000,$W34,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G34,'Chase Log'!$E$4:$E$2000,$W34)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G34,'Chase Log'!$E$4:$E$2000,$W34))))</f>
-        <v/>
+        <v>46308</v>
       </c>
       <c r="Z34" s="13" t="str">
         <f ca="1">IF(OR($G34="",N($P34)&gt;=1,$C34="Live",$D34&lt;&gt;""),"",IF(AND($Y34&lt;&gt;"",N($Y34)&gt;0),IF($Y34&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($Q34&lt;&gt;"",N($R34)&gt;='안내 Guide'!$D$4,OR($X34="",N($X34)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
-        <v/>
+        <v>Chase Overdue</v>
       </c>
       <c r="AA34" s="28"/>
       <c r="AB34" s="25"/>
@@ -18922,7 +19111,7 @@
       </c>
       <c r="V42" s="22">
         <f>IF($G42="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G42))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W42" s="27">
         <f>IF(N($V42)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G42))</f>
@@ -19594,23 +19783,23 @@
       </c>
       <c r="V48" s="22">
         <f>IF($G48="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G48))</f>
-        <v>0</v>
-      </c>
-      <c r="W48" s="27" t="str">
+        <v>1</v>
+      </c>
+      <c r="W48" s="27">
         <f>IF(N($V48)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G48))</f>
-        <v/>
-      </c>
-      <c r="X48" s="22" t="str">
+        <v>46300</v>
+      </c>
+      <c r="X48" s="22">
         <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-      <c r="Y48" s="27" t="str">
+        <v>25</v>
+      </c>
+      <c r="Y48" s="27">
         <f>IF($W48="","",IF(OR(AND($Q48&lt;&gt;"",N($Q48)&gt;N($W48)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G48,'Chase Log'!$E$4:$E$2000,$W48,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G48,'Chase Log'!$E$4:$E$2000,$W48)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G48,'Chase Log'!$E$4:$E$2000,$W48))))</f>
-        <v/>
+        <v>46307</v>
       </c>
       <c r="Z48" s="13" t="str">
         <f ca="1">IF(OR($G48="",N($P48)&gt;=1,$C48="Live",$D48&lt;&gt;""),"",IF(AND($Y48&lt;&gt;"",N($Y48)&gt;0),IF($Y48&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($Q48&lt;&gt;"",N($R48)&gt;='안내 Guide'!$D$4,OR($X48="",N($X48)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
-        <v/>
+        <v>Chase Overdue</v>
       </c>
       <c r="AA48" s="28"/>
       <c r="AB48" s="25"/>
@@ -19706,23 +19895,23 @@
       </c>
       <c r="V49" s="22">
         <f>IF($G49="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G49))</f>
-        <v>0</v>
-      </c>
-      <c r="W49" s="27" t="str">
+        <v>2</v>
+      </c>
+      <c r="W49" s="27">
         <f>IF(N($V49)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G49))</f>
-        <v/>
-      </c>
-      <c r="X49" s="22" t="str">
+        <v>46313</v>
+      </c>
+      <c r="X49" s="22">
         <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-      <c r="Y49" s="27" t="str">
+        <v>12</v>
+      </c>
+      <c r="Y49" s="27">
         <f>IF($W49="","",IF(OR(AND($Q49&lt;&gt;"",N($Q49)&gt;N($W49)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G49,'Chase Log'!$E$4:$E$2000,$W49,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G49,'Chase Log'!$E$4:$E$2000,$W49)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G49,'Chase Log'!$E$4:$E$2000,$W49))))</f>
-        <v/>
+        <v>46320</v>
       </c>
       <c r="Z49" s="13" t="str">
         <f ca="1">IF(OR($G49="",N($P49)&gt;=1,$C49="Live",$D49&lt;&gt;""),"",IF(AND($Y49&lt;&gt;"",N($Y49)&gt;0),IF($Y49&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($Q49&lt;&gt;"",N($R49)&gt;='안내 Guide'!$D$4,OR($X49="",N($X49)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
-        <v/>
+        <v>Chase Overdue</v>
       </c>
       <c r="AA49" s="28"/>
       <c r="AB49" s="25"/>
@@ -19930,23 +20119,23 @@
       </c>
       <c r="V51" s="22">
         <f>IF($G51="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G51))</f>
-        <v>0</v>
-      </c>
-      <c r="W51" s="27" t="str">
+        <v>1</v>
+      </c>
+      <c r="W51" s="27">
         <f>IF(N($V51)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G51))</f>
-        <v/>
-      </c>
-      <c r="X51" s="22" t="str">
+        <v>46300</v>
+      </c>
+      <c r="X51" s="22">
         <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-      <c r="Y51" s="27" t="str">
+        <v>25</v>
+      </c>
+      <c r="Y51" s="27">
         <f>IF($W51="","",IF(OR(AND($Q51&lt;&gt;"",N($Q51)&gt;N($W51)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G51,'Chase Log'!$E$4:$E$2000,$W51,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G51,'Chase Log'!$E$4:$E$2000,$W51)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G51,'Chase Log'!$E$4:$E$2000,$W51))))</f>
-        <v/>
+        <v>46307</v>
       </c>
       <c r="Z51" s="13" t="str">
         <f ca="1">IF(OR($G51="",N($P51)&gt;=1,$C51="Live",$D51&lt;&gt;""),"",IF(AND($Y51&lt;&gt;"",N($Y51)&gt;0),IF($Y51&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($Q51&lt;&gt;"",N($R51)&gt;='안내 Guide'!$D$4,OR($X51="",N($X51)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
-        <v/>
+        <v>Chase Overdue</v>
       </c>
       <c r="AA51" s="28"/>
       <c r="AB51" s="25"/>
@@ -20040,23 +20229,23 @@
       </c>
       <c r="V52" s="22">
         <f>IF($G52="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G52))</f>
-        <v>0</v>
-      </c>
-      <c r="W52" s="27" t="str">
+        <v>1</v>
+      </c>
+      <c r="W52" s="27">
         <f>IF(N($V52)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G52))</f>
-        <v/>
-      </c>
-      <c r="X52" s="22" t="str">
+        <v>46300</v>
+      </c>
+      <c r="X52" s="22">
         <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-      <c r="Y52" s="27" t="str">
+        <v>25</v>
+      </c>
+      <c r="Y52" s="27">
         <f>IF($W52="","",IF(OR(AND($Q52&lt;&gt;"",N($Q52)&gt;N($W52)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G52,'Chase Log'!$E$4:$E$2000,$W52,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G52,'Chase Log'!$E$4:$E$2000,$W52)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G52,'Chase Log'!$E$4:$E$2000,$W52))))</f>
-        <v/>
+        <v>46307</v>
       </c>
       <c r="Z52" s="13" t="str">
         <f ca="1">IF(OR($G52="",N($P52)&gt;=1,$C52="Live",$D52&lt;&gt;""),"",IF(AND($Y52&lt;&gt;"",N($Y52)&gt;0),IF($Y52&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($Q52&lt;&gt;"",N($R52)&gt;='안내 Guide'!$D$4,OR($X52="",N($X52)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
-        <v/>
+        <v>Chase Overdue</v>
       </c>
       <c r="AA52" s="28"/>
       <c r="AB52" s="25"/>
@@ -20150,23 +20339,23 @@
       </c>
       <c r="V53" s="22">
         <f>IF($G53="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G53))</f>
-        <v>0</v>
-      </c>
-      <c r="W53" s="27" t="str">
+        <v>1</v>
+      </c>
+      <c r="W53" s="27">
         <f>IF(N($V53)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G53))</f>
-        <v/>
-      </c>
-      <c r="X53" s="22" t="str">
+        <v>46297</v>
+      </c>
+      <c r="X53" s="22">
         <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-      <c r="Y53" s="27" t="str">
+        <v>28</v>
+      </c>
+      <c r="Y53" s="27">
         <f>IF($W53="","",IF(OR(AND($Q53&lt;&gt;"",N($Q53)&gt;N($W53)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G53,'Chase Log'!$E$4:$E$2000,$W53,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G53,'Chase Log'!$E$4:$E$2000,$W53)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G53,'Chase Log'!$E$4:$E$2000,$W53))))</f>
-        <v/>
+        <v>46304</v>
       </c>
       <c r="Z53" s="13" t="str">
         <f ca="1">IF(OR($G53="",N($P53)&gt;=1,$C53="Live",$D53&lt;&gt;""),"",IF(AND($Y53&lt;&gt;"",N($Y53)&gt;0),IF($Y53&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($Q53&lt;&gt;"",N($R53)&gt;='안내 Guide'!$D$4,OR($X53="",N($X53)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
-        <v/>
+        <v>Chase Overdue</v>
       </c>
       <c r="AA53" s="28"/>
       <c r="AB53" s="25"/>
@@ -20262,23 +20451,23 @@
       </c>
       <c r="V54" s="22">
         <f>IF($G54="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G54))</f>
-        <v>0</v>
-      </c>
-      <c r="W54" s="27" t="str">
+        <v>1</v>
+      </c>
+      <c r="W54" s="27">
         <f>IF(N($V54)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G54))</f>
-        <v/>
-      </c>
-      <c r="X54" s="22" t="str">
+        <v>46300</v>
+      </c>
+      <c r="X54" s="22">
         <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-      <c r="Y54" s="27" t="str">
+        <v>25</v>
+      </c>
+      <c r="Y54" s="27">
         <f>IF($W54="","",IF(OR(AND($Q54&lt;&gt;"",N($Q54)&gt;N($W54)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G54,'Chase Log'!$E$4:$E$2000,$W54,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G54,'Chase Log'!$E$4:$E$2000,$W54)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G54,'Chase Log'!$E$4:$E$2000,$W54))))</f>
-        <v/>
+        <v>46307</v>
       </c>
       <c r="Z54" s="13" t="str">
         <f ca="1">IF(OR($G54="",N($P54)&gt;=1,$C54="Live",$D54&lt;&gt;""),"",IF(AND($Y54&lt;&gt;"",N($Y54)&gt;0),IF($Y54&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($Q54&lt;&gt;"",N($R54)&gt;='안내 Guide'!$D$4,OR($X54="",N($X54)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
-        <v/>
+        <v>Chase Overdue</v>
       </c>
       <c r="AA54" s="28"/>
       <c r="AB54" s="25"/>
@@ -20372,23 +20561,23 @@
       </c>
       <c r="V55" s="22">
         <f>IF($G55="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G55))</f>
-        <v>0</v>
-      </c>
-      <c r="W55" s="27" t="str">
+        <v>1</v>
+      </c>
+      <c r="W55" s="27">
         <f>IF(N($V55)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G55))</f>
-        <v/>
-      </c>
-      <c r="X55" s="22" t="str">
+        <v>46300</v>
+      </c>
+      <c r="X55" s="22">
         <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-      <c r="Y55" s="27" t="str">
+        <v>25</v>
+      </c>
+      <c r="Y55" s="27">
         <f>IF($W55="","",IF(OR(AND($Q55&lt;&gt;"",N($Q55)&gt;N($W55)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G55,'Chase Log'!$E$4:$E$2000,$W55,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G55,'Chase Log'!$E$4:$E$2000,$W55)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G55,'Chase Log'!$E$4:$E$2000,$W55))))</f>
-        <v/>
+        <v>46307</v>
       </c>
       <c r="Z55" s="13" t="str">
         <f ca="1">IF(OR($G55="",N($P55)&gt;=1,$C55="Live",$D55&lt;&gt;""),"",IF(AND($Y55&lt;&gt;"",N($Y55)&gt;0),IF($Y55&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($Q55&lt;&gt;"",N($R55)&gt;='안내 Guide'!$D$4,OR($X55="",N($X55)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
-        <v/>
+        <v>Chase Overdue</v>
       </c>
       <c r="AA55" s="28"/>
       <c r="AB55" s="25"/>
@@ -20482,23 +20671,23 @@
       </c>
       <c r="V56" s="22">
         <f>IF($G56="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G56))</f>
-        <v>0</v>
-      </c>
-      <c r="W56" s="27" t="str">
+        <v>1</v>
+      </c>
+      <c r="W56" s="27">
         <f>IF(N($V56)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G56))</f>
-        <v/>
-      </c>
-      <c r="X56" s="22" t="str">
+        <v>46300</v>
+      </c>
+      <c r="X56" s="22">
         <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-      <c r="Y56" s="27" t="str">
+        <v>25</v>
+      </c>
+      <c r="Y56" s="27">
         <f>IF($W56="","",IF(OR(AND($Q56&lt;&gt;"",N($Q56)&gt;N($W56)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G56,'Chase Log'!$E$4:$E$2000,$W56,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G56,'Chase Log'!$E$4:$E$2000,$W56)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G56,'Chase Log'!$E$4:$E$2000,$W56))))</f>
-        <v/>
+        <v>46307</v>
       </c>
       <c r="Z56" s="13" t="str">
         <f ca="1">IF(OR($G56="",N($P56)&gt;=1,$C56="Live",$D56&lt;&gt;""),"",IF(AND($Y56&lt;&gt;"",N($Y56)&gt;0),IF($Y56&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($Q56&lt;&gt;"",N($R56)&gt;='안내 Guide'!$D$4,OR($X56="",N($X56)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
-        <v/>
+        <v>Chase Overdue</v>
       </c>
       <c r="AA56" s="28"/>
       <c r="AB56" s="25"/>
@@ -20592,23 +20781,23 @@
       </c>
       <c r="V57" s="22">
         <f>IF($G57="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G57))</f>
-        <v>0</v>
-      </c>
-      <c r="W57" s="27" t="str">
+        <v>1</v>
+      </c>
+      <c r="W57" s="27">
         <f>IF(N($V57)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G57))</f>
-        <v/>
-      </c>
-      <c r="X57" s="22" t="str">
+        <v>46300</v>
+      </c>
+      <c r="X57" s="22">
         <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-      <c r="Y57" s="27" t="str">
+        <v>25</v>
+      </c>
+      <c r="Y57" s="27">
         <f>IF($W57="","",IF(OR(AND($Q57&lt;&gt;"",N($Q57)&gt;N($W57)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G57,'Chase Log'!$E$4:$E$2000,$W57,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G57,'Chase Log'!$E$4:$E$2000,$W57)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G57,'Chase Log'!$E$4:$E$2000,$W57))))</f>
-        <v/>
+        <v>46307</v>
       </c>
       <c r="Z57" s="13" t="str">
         <f ca="1">IF(OR($G57="",N($P57)&gt;=1,$C57="Live",$D57&lt;&gt;""),"",IF(AND($Y57&lt;&gt;"",N($Y57)&gt;0),IF($Y57&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($Q57&lt;&gt;"",N($R57)&gt;='안내 Guide'!$D$4,OR($X57="",N($X57)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
-        <v/>
+        <v>Chase Overdue</v>
       </c>
       <c r="AA57" s="28"/>
       <c r="AB57" s="25"/>
@@ -20702,23 +20891,23 @@
       </c>
       <c r="V58" s="22">
         <f>IF($G58="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G58))</f>
-        <v>0</v>
-      </c>
-      <c r="W58" s="27" t="str">
+        <v>1</v>
+      </c>
+      <c r="W58" s="27">
         <f>IF(N($V58)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G58))</f>
-        <v/>
-      </c>
-      <c r="X58" s="22" t="str">
+        <v>46300</v>
+      </c>
+      <c r="X58" s="22">
         <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-      <c r="Y58" s="27" t="str">
+        <v>25</v>
+      </c>
+      <c r="Y58" s="27">
         <f>IF($W58="","",IF(OR(AND($Q58&lt;&gt;"",N($Q58)&gt;N($W58)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G58,'Chase Log'!$E$4:$E$2000,$W58,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G58,'Chase Log'!$E$4:$E$2000,$W58)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G58,'Chase Log'!$E$4:$E$2000,$W58))))</f>
-        <v/>
+        <v>46307</v>
       </c>
       <c r="Z58" s="13" t="str">
         <f ca="1">IF(OR($G58="",N($P58)&gt;=1,$C58="Live",$D58&lt;&gt;""),"",IF(AND($Y58&lt;&gt;"",N($Y58)&gt;0),IF($Y58&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($Q58&lt;&gt;"",N($R58)&gt;='안내 Guide'!$D$4,OR($X58="",N($X58)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
-        <v/>
+        <v>Chase Overdue</v>
       </c>
       <c r="AA58" s="28"/>
       <c r="AB58" s="25"/>
@@ -20812,23 +21001,23 @@
       </c>
       <c r="V59" s="22">
         <f>IF($G59="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G59))</f>
-        <v>0</v>
-      </c>
-      <c r="W59" s="27" t="str">
+        <v>1</v>
+      </c>
+      <c r="W59" s="27">
         <f>IF(N($V59)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G59))</f>
-        <v/>
-      </c>
-      <c r="X59" s="22" t="str">
+        <v>46300</v>
+      </c>
+      <c r="X59" s="22">
         <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-      <c r="Y59" s="27" t="str">
+        <v>25</v>
+      </c>
+      <c r="Y59" s="27">
         <f>IF($W59="","",IF(OR(AND($Q59&lt;&gt;"",N($Q59)&gt;N($W59)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G59,'Chase Log'!$E$4:$E$2000,$W59,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G59,'Chase Log'!$E$4:$E$2000,$W59)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G59,'Chase Log'!$E$4:$E$2000,$W59))))</f>
-        <v/>
+        <v>46307</v>
       </c>
       <c r="Z59" s="13" t="str">
         <f ca="1">IF(OR($G59="",N($P59)&gt;=1,$C59="Live",$D59&lt;&gt;""),"",IF(AND($Y59&lt;&gt;"",N($Y59)&gt;0),IF($Y59&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($Q59&lt;&gt;"",N($R59)&gt;='안내 Guide'!$D$4,OR($X59="",N($X59)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
-        <v/>
+        <v>Chase Overdue</v>
       </c>
       <c r="AA59" s="28"/>
       <c r="AB59" s="25"/>
@@ -20922,23 +21111,23 @@
       </c>
       <c r="V60" s="22">
         <f>IF($G60="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G60))</f>
-        <v>0</v>
-      </c>
-      <c r="W60" s="27" t="str">
+        <v>1</v>
+      </c>
+      <c r="W60" s="27">
         <f>IF(N($V60)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G60))</f>
-        <v/>
-      </c>
-      <c r="X60" s="22" t="str">
+        <v>46300</v>
+      </c>
+      <c r="X60" s="22">
         <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-      <c r="Y60" s="27" t="str">
+        <v>25</v>
+      </c>
+      <c r="Y60" s="27">
         <f>IF($W60="","",IF(OR(AND($Q60&lt;&gt;"",N($Q60)&gt;N($W60)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G60,'Chase Log'!$E$4:$E$2000,$W60,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G60,'Chase Log'!$E$4:$E$2000,$W60)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G60,'Chase Log'!$E$4:$E$2000,$W60))))</f>
-        <v/>
+        <v>46307</v>
       </c>
       <c r="Z60" s="13" t="str">
         <f ca="1">IF(OR($G60="",N($P60)&gt;=1,$C60="Live",$D60&lt;&gt;""),"",IF(AND($Y60&lt;&gt;"",N($Y60)&gt;0),IF($Y60&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($Q60&lt;&gt;"",N($R60)&gt;='안내 Guide'!$D$4,OR($X60="",N($X60)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
-        <v/>
+        <v>Chase Overdue</v>
       </c>
       <c r="AA60" s="28"/>
       <c r="AB60" s="25"/>
@@ -21142,15 +21331,15 @@
       </c>
       <c r="V62" s="22">
         <f>IF($G62="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G62))</f>
-        <v>0</v>
-      </c>
-      <c r="W62" s="27" t="str">
+        <v>1</v>
+      </c>
+      <c r="W62" s="27">
         <f>IF(N($V62)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G62))</f>
-        <v/>
-      </c>
-      <c r="X62" s="22" t="str">
+        <v>46300</v>
+      </c>
+      <c r="X62" s="22">
         <f t="shared" ca="1" si="15"/>
-        <v/>
+        <v>25</v>
       </c>
       <c r="Y62" s="27" t="str">
         <f>IF($W62="","",IF(OR(AND($Q62&lt;&gt;"",N($Q62)&gt;N($W62)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G62,'Chase Log'!$E$4:$E$2000,$W62,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G62,'Chase Log'!$E$4:$E$2000,$W62)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G62,'Chase Log'!$E$4:$E$2000,$W62))))</f>
@@ -21364,23 +21553,23 @@
       </c>
       <c r="V64" s="22">
         <f>IF($G64="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G64))</f>
-        <v>0</v>
-      </c>
-      <c r="W64" s="27" t="str">
+        <v>1</v>
+      </c>
+      <c r="W64" s="27">
         <f>IF(N($V64)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G64))</f>
-        <v/>
-      </c>
-      <c r="X64" s="22" t="str">
+        <v>46300</v>
+      </c>
+      <c r="X64" s="22">
         <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-      <c r="Y64" s="27" t="str">
+        <v>25</v>
+      </c>
+      <c r="Y64" s="27">
         <f>IF($W64="","",IF(OR(AND($Q64&lt;&gt;"",N($Q64)&gt;N($W64)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G64,'Chase Log'!$E$4:$E$2000,$W64,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G64,'Chase Log'!$E$4:$E$2000,$W64)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G64,'Chase Log'!$E$4:$E$2000,$W64))))</f>
-        <v/>
+        <v>46307</v>
       </c>
       <c r="Z64" s="13" t="str">
         <f ca="1">IF(OR($G64="",N($P64)&gt;=1,$C64="Live",$D64&lt;&gt;""),"",IF(AND($Y64&lt;&gt;"",N($Y64)&gt;0),IF($Y64&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($Q64&lt;&gt;"",N($R64)&gt;='안내 Guide'!$D$4,OR($X64="",N($X64)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
-        <v/>
+        <v>Chase Overdue</v>
       </c>
       <c r="AA64" s="28"/>
       <c r="AB64" s="25"/>
@@ -21476,23 +21665,23 @@
       </c>
       <c r="V65" s="22">
         <f>IF($G65="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G65))</f>
-        <v>0</v>
-      </c>
-      <c r="W65" s="27" t="str">
+        <v>1</v>
+      </c>
+      <c r="W65" s="27">
         <f>IF(N($V65)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G65))</f>
-        <v/>
-      </c>
-      <c r="X65" s="22" t="str">
+        <v>46300</v>
+      </c>
+      <c r="X65" s="22">
         <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-      <c r="Y65" s="27" t="str">
+        <v>25</v>
+      </c>
+      <c r="Y65" s="27">
         <f>IF($W65="","",IF(OR(AND($Q65&lt;&gt;"",N($Q65)&gt;N($W65)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G65,'Chase Log'!$E$4:$E$2000,$W65,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G65,'Chase Log'!$E$4:$E$2000,$W65)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G65,'Chase Log'!$E$4:$E$2000,$W65))))</f>
-        <v/>
+        <v>46307</v>
       </c>
       <c r="Z65" s="13" t="str">
         <f ca="1">IF(OR($G65="",N($P65)&gt;=1,$C65="Live",$D65&lt;&gt;""),"",IF(AND($Y65&lt;&gt;"",N($Y65)&gt;0),IF($Y65&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($Q65&lt;&gt;"",N($R65)&gt;='안내 Guide'!$D$4,OR($X65="",N($X65)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
-        <v/>
+        <v>Chase Overdue</v>
       </c>
       <c r="AA65" s="28"/>
       <c r="AB65" s="25"/>
@@ -21586,23 +21775,23 @@
       </c>
       <c r="V66" s="22">
         <f>IF($G66="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G66))</f>
-        <v>0</v>
-      </c>
-      <c r="W66" s="27" t="str">
+        <v>1</v>
+      </c>
+      <c r="W66" s="27">
         <f>IF(N($V66)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G66))</f>
-        <v/>
-      </c>
-      <c r="X66" s="22" t="str">
+        <v>46300</v>
+      </c>
+      <c r="X66" s="22">
         <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-      <c r="Y66" s="27" t="str">
+        <v>25</v>
+      </c>
+      <c r="Y66" s="27">
         <f>IF($W66="","",IF(OR(AND($Q66&lt;&gt;"",N($Q66)&gt;N($W66)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G66,'Chase Log'!$E$4:$E$2000,$W66,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G66,'Chase Log'!$E$4:$E$2000,$W66)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G66,'Chase Log'!$E$4:$E$2000,$W66))))</f>
-        <v/>
+        <v>46307</v>
       </c>
       <c r="Z66" s="13" t="str">
         <f ca="1">IF(OR($G66="",N($P66)&gt;=1,$C66="Live",$D66&lt;&gt;""),"",IF(AND($Y66&lt;&gt;"",N($Y66)&gt;0),IF($Y66&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($Q66&lt;&gt;"",N($R66)&gt;='안내 Guide'!$D$4,OR($X66="",N($X66)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
-        <v/>
+        <v>Chase Overdue</v>
       </c>
       <c r="AA66" s="28"/>
       <c r="AB66" s="25"/>
@@ -21696,23 +21885,23 @@
       </c>
       <c r="V67" s="22">
         <f>IF($G67="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G67))</f>
-        <v>0</v>
-      </c>
-      <c r="W67" s="27" t="str">
+        <v>1</v>
+      </c>
+      <c r="W67" s="27">
         <f>IF(N($V67)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G67))</f>
-        <v/>
-      </c>
-      <c r="X67" s="22" t="str">
+        <v>46300</v>
+      </c>
+      <c r="X67" s="22">
         <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-      <c r="Y67" s="27" t="str">
+        <v>25</v>
+      </c>
+      <c r="Y67" s="27">
         <f>IF($W67="","",IF(OR(AND($Q67&lt;&gt;"",N($Q67)&gt;N($W67)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G67,'Chase Log'!$E$4:$E$2000,$W67,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G67,'Chase Log'!$E$4:$E$2000,$W67)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G67,'Chase Log'!$E$4:$E$2000,$W67))))</f>
-        <v/>
+        <v>46307</v>
       </c>
       <c r="Z67" s="13" t="str">
         <f ca="1">IF(OR($G67="",N($P67)&gt;=1,$C67="Live",$D67&lt;&gt;""),"",IF(AND($Y67&lt;&gt;"",N($Y67)&gt;0),IF($Y67&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($Q67&lt;&gt;"",N($R67)&gt;='안내 Guide'!$D$4,OR($X67="",N($X67)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
-        <v/>
+        <v>Chase Overdue</v>
       </c>
       <c r="AA67" s="28"/>
       <c r="AB67" s="25"/>
@@ -21918,23 +22107,23 @@
       </c>
       <c r="V69" s="22">
         <f>IF($G69="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G69))</f>
+        <v>4</v>
+      </c>
+      <c r="W69" s="27">
+        <f>IF(N($V69)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G69))</f>
+        <v>46325</v>
+      </c>
+      <c r="X69" s="22">
+        <f t="shared" ca="1" si="23"/>
         <v>0</v>
       </c>
-      <c r="W69" s="27" t="str">
-        <f>IF(N($V69)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G69))</f>
-        <v/>
-      </c>
-      <c r="X69" s="22" t="str">
-        <f t="shared" ca="1" si="23"/>
-        <v/>
-      </c>
-      <c r="Y69" s="27" t="str">
+      <c r="Y69" s="27">
         <f>IF($W69="","",IF(OR(AND($Q69&lt;&gt;"",N($Q69)&gt;N($W69)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G69,'Chase Log'!$E$4:$E$2000,$W69,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G69,'Chase Log'!$E$4:$E$2000,$W69)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G69,'Chase Log'!$E$4:$E$2000,$W69))))</f>
-        <v/>
+        <v>46332</v>
       </c>
       <c r="Z69" s="13" t="str">
         <f ca="1">IF(OR($G69="",N($P69)&gt;=1,$C69="Live",$D69&lt;&gt;""),"",IF(AND($Y69&lt;&gt;"",N($Y69)&gt;0),IF($Y69&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($Q69&lt;&gt;"",N($R69)&gt;='안내 Guide'!$D$4,OR($X69="",N($X69)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
-        <v/>
+        <v>Scheduled</v>
       </c>
       <c r="AA69" s="28"/>
       <c r="AB69" s="25"/>
@@ -22894,19 +23083,19 @@
       </c>
       <c r="V76" s="22">
         <f>IF($G76="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G76))</f>
-        <v>0</v>
-      </c>
-      <c r="W76" s="27" t="str">
+        <v>1</v>
+      </c>
+      <c r="W76" s="27">
         <f>IF(N($V76)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G76))</f>
-        <v/>
-      </c>
-      <c r="X76" s="22" t="str">
+        <v>46324</v>
+      </c>
+      <c r="X76" s="22">
         <f t="shared" ca="1" si="23"/>
-        <v/>
-      </c>
-      <c r="Y76" s="27" t="str">
+        <v>1</v>
+      </c>
+      <c r="Y76" s="27">
         <f>IF($W76="","",IF(OR(AND($Q76&lt;&gt;"",N($Q76)&gt;N($W76)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G76,'Chase Log'!$E$4:$E$2000,$W76,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G76,'Chase Log'!$E$4:$E$2000,$W76)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G76,'Chase Log'!$E$4:$E$2000,$W76))))</f>
-        <v/>
+        <v>46331</v>
       </c>
       <c r="Z76" s="13" t="str">
         <f ca="1">IF(OR($G76="",N($P76)&gt;=1,$C76="Live",$D76&lt;&gt;""),"",IF(AND($Y76&lt;&gt;"",N($Y76)&gt;0),IF($Y76&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($Q76&lt;&gt;"",N($R76)&gt;='안내 Guide'!$D$4,OR($X76="",N($X76)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
@@ -24184,19 +24373,19 @@
       </c>
       <c r="V85" s="22">
         <f>IF($G85="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G85))</f>
-        <v>0</v>
-      </c>
-      <c r="W85" s="27" t="str">
+        <v>1</v>
+      </c>
+      <c r="W85" s="27">
         <f>IF(N($V85)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G85))</f>
-        <v/>
-      </c>
-      <c r="X85" s="22" t="str">
+        <v>46324</v>
+      </c>
+      <c r="X85" s="22">
         <f t="shared" ca="1" si="23"/>
-        <v/>
-      </c>
-      <c r="Y85" s="27" t="str">
+        <v>1</v>
+      </c>
+      <c r="Y85" s="27">
         <f>IF($W85="","",IF(OR(AND($Q85&lt;&gt;"",N($Q85)&gt;N($W85)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G85,'Chase Log'!$E$4:$E$2000,$W85,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G85,'Chase Log'!$E$4:$E$2000,$W85)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G85,'Chase Log'!$E$4:$E$2000,$W85))))</f>
-        <v/>
+        <v>46331</v>
       </c>
       <c r="Z85" s="13" t="str">
         <f ca="1">IF(OR($G85="",N($P85)&gt;=1,$C85="Live",$D85&lt;&gt;""),"",IF(AND($Y85&lt;&gt;"",N($Y85)&gt;0),IF($Y85&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($Q85&lt;&gt;"",N($R85)&gt;='안내 Guide'!$D$4,OR($X85="",N($X85)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
@@ -25482,19 +25671,19 @@
       </c>
       <c r="V94" s="22">
         <f>IF($G94="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G94))</f>
-        <v>0</v>
-      </c>
-      <c r="W94" s="27" t="str">
+        <v>1</v>
+      </c>
+      <c r="W94" s="27">
         <f>IF(N($V94)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G94))</f>
-        <v/>
-      </c>
-      <c r="X94" s="22" t="str">
+        <v>46323</v>
+      </c>
+      <c r="X94" s="22">
         <f t="shared" ca="1" si="23"/>
-        <v/>
-      </c>
-      <c r="Y94" s="27" t="str">
+        <v>2</v>
+      </c>
+      <c r="Y94" s="27">
         <f>IF($W94="","",IF(OR(AND($Q94&lt;&gt;"",N($Q94)&gt;N($W94)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G94,'Chase Log'!$E$4:$E$2000,$W94,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G94,'Chase Log'!$E$4:$E$2000,$W94)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G94,'Chase Log'!$E$4:$E$2000,$W94))))</f>
-        <v/>
+        <v>46330</v>
       </c>
       <c r="Z94" s="13" t="str">
         <f ca="1">IF(OR($G94="",N($P94)&gt;=1,$C94="Live",$D94&lt;&gt;""),"",IF(AND($Y94&lt;&gt;"",N($Y94)&gt;0),IF($Y94&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($Q94&lt;&gt;"",N($R94)&gt;='안내 Guide'!$D$4,OR($X94="",N($X94)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
@@ -25770,19 +25959,19 @@
       </c>
       <c r="V96" s="22">
         <f>IF($G96="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G96))</f>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="W96" s="27">
         <f>IF(N($V96)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G96))</f>
-        <v>46312</v>
+        <v>46325</v>
       </c>
       <c r="X96" s="22">
         <f t="shared" ca="1" si="23"/>
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Y96" s="27">
         <f>IF($W96="","",IF(OR(AND($Q96&lt;&gt;"",N($Q96)&gt;N($W96)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G96,'Chase Log'!$E$4:$E$2000,$W96,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G96,'Chase Log'!$E$4:$E$2000,$W96)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G96,'Chase Log'!$E$4:$E$2000,$W96))))</f>
-        <v>46319</v>
+        <v>46332</v>
       </c>
       <c r="Z96" s="13" t="str">
         <f ca="1">IF(OR($G96="",N($P96)&gt;=1,$C96="Live",$D96&lt;&gt;""),"",IF(AND($Y96&lt;&gt;"",N($Y96)&gt;0),IF($Y96&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($Q96&lt;&gt;"",N($R96)&gt;='안내 Guide'!$D$4,OR($X96="",N($X96)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
@@ -26058,7 +26247,7 @@
       </c>
       <c r="V98" s="22">
         <f>IF($G98="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G98))</f>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="W98" s="27">
         <f>IF(N($V98)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G98))</f>
@@ -26629,7 +26818,7 @@
       </c>
       <c r="Y5" s="22">
         <f>IF($G5="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G5))</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Z5" s="27">
         <f>IF(N($Y5)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G5))</f>
@@ -26770,7 +26959,7 @@
       </c>
       <c r="Y6" s="22">
         <f>IF($G6="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G6))</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Z6" s="27">
         <f>IF(N($Y6)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G6))</f>
@@ -26911,7 +27100,7 @@
       </c>
       <c r="Y7" s="22">
         <f>IF($G7="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G7))</f>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Z7" s="27">
         <f>IF(N($Y7)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G7))</f>
@@ -27042,23 +27231,23 @@
       </c>
       <c r="Y8" s="22">
         <f>IF($G8="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G8))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z8" s="27">
         <f>IF(N($Y8)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G8))</f>
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="AA8" s="22">
         <f t="shared" ca="1" si="7"/>
-        <v>25</v>
-      </c>
-      <c r="AB8" s="27" t="str">
+        <v>24</v>
+      </c>
+      <c r="AB8" s="27">
         <f>IF($Z8="","",IF(OR(AND($T8&lt;&gt;"",N($T8)&gt;N($Z8)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G8,'Chase Log'!$E$4:$E$2000,$Z8,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G8,'Chase Log'!$E$4:$E$2000,$Z8)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G8,'Chase Log'!$E$4:$E$2000,$Z8))))</f>
-        <v/>
+        <v>46308</v>
       </c>
       <c r="AC8" s="13" t="str">
         <f ca="1">IF(OR($G8="",N($S8)&gt;=1,$C8="Live",$D8&lt;&gt;""),"",IF(AND($AB8&lt;&gt;"",N($AB8)&gt;0),IF($AB8&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($T8&lt;&gt;"",N($U8)&gt;='안내 Guide'!$D$4,OR($AA8="",N($AA8)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
-        <v>Chase Needed</v>
+        <v>Chase Overdue</v>
       </c>
       <c r="AD8" s="28"/>
       <c r="AE8" s="25"/>
@@ -27300,19 +27489,19 @@
       </c>
       <c r="Y10" s="22">
         <f>IF($G10="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G10))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z10" s="27">
         <f>IF(N($Y10)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G10))</f>
-        <v>46321</v>
+        <v>46324</v>
       </c>
       <c r="AA10" s="22">
         <f t="shared" ca="1" si="7"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AB10" s="27">
         <f>IF($Z10="","",IF(OR(AND($T10&lt;&gt;"",N($T10)&gt;N($Z10)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G10,'Chase Log'!$E$4:$E$2000,$Z10,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G10,'Chase Log'!$E$4:$E$2000,$Z10)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G10,'Chase Log'!$E$4:$E$2000,$Z10))))</f>
-        <v>46328</v>
+        <v>46331</v>
       </c>
       <c r="AC10" s="13" t="str">
         <f ca="1">IF(OR($G10="",N($S10)&gt;=1,$C10="Live",$D10&lt;&gt;""),"",IF(AND($AB10&lt;&gt;"",N($AB10)&gt;0),IF($AB10&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($T10&lt;&gt;"",N($U10)&gt;='안내 Guide'!$D$4,OR($AA10="",N($AA10)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
@@ -27429,19 +27618,19 @@
       </c>
       <c r="Y11" s="22">
         <f>IF($G11="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G11))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z11" s="27">
         <f>IF(N($Y11)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G11))</f>
-        <v>46321</v>
+        <v>46324</v>
       </c>
       <c r="AA11" s="22">
         <f t="shared" ca="1" si="7"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AB11" s="27">
         <f>IF($Z11="","",IF(OR(AND($T11&lt;&gt;"",N($T11)&gt;N($Z11)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G11,'Chase Log'!$E$4:$E$2000,$Z11,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G11,'Chase Log'!$E$4:$E$2000,$Z11)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G11,'Chase Log'!$E$4:$E$2000,$Z11))))</f>
-        <v>46328</v>
+        <v>46331</v>
       </c>
       <c r="AC11" s="13" t="str">
         <f ca="1">IF(OR($G11="",N($S11)&gt;=1,$C11="Live",$D11&lt;&gt;""),"",IF(AND($AB11&lt;&gt;"",N($AB11)&gt;0),IF($AB11&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($T11&lt;&gt;"",N($U11)&gt;='안내 Guide'!$D$4,OR($AA11="",N($AA11)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
@@ -27558,23 +27747,23 @@
       </c>
       <c r="Y12" s="22">
         <f>IF($G12="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G12))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z12" s="27">
         <f>IF(N($Y12)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G12))</f>
-        <v>46300</v>
+        <v>46323</v>
       </c>
       <c r="AA12" s="22">
         <f t="shared" ca="1" si="7"/>
-        <v>25</v>
-      </c>
-      <c r="AB12" s="27" t="str">
+        <v>2</v>
+      </c>
+      <c r="AB12" s="27">
         <f>IF($Z12="","",IF(OR(AND($T12&lt;&gt;"",N($T12)&gt;N($Z12)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G12,'Chase Log'!$E$4:$E$2000,$Z12,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G12,'Chase Log'!$E$4:$E$2000,$Z12)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G12,'Chase Log'!$E$4:$E$2000,$Z12))))</f>
-        <v/>
+        <v>46330</v>
       </c>
       <c r="AC12" s="13" t="str">
         <f ca="1">IF(OR($G12="",N($S12)&gt;=1,$C12="Live",$D12&lt;&gt;""),"",IF(AND($AB12&lt;&gt;"",N($AB12)&gt;0),IF($AB12&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($T12&lt;&gt;"",N($U12)&gt;='안내 Guide'!$D$4,OR($AA12="",N($AA12)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
-        <v>Chase Needed</v>
+        <v>Scheduled</v>
       </c>
       <c r="AD12" s="28"/>
       <c r="AE12" s="25"/>
@@ -27687,23 +27876,23 @@
       </c>
       <c r="Y13" s="22">
         <f>IF($G13="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G13))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z13" s="27">
         <f>IF(N($Y13)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G13))</f>
-        <v>46300</v>
+        <v>46324</v>
       </c>
       <c r="AA13" s="22">
         <f t="shared" ca="1" si="7"/>
-        <v>25</v>
-      </c>
-      <c r="AB13" s="27" t="str">
+        <v>1</v>
+      </c>
+      <c r="AB13" s="27">
         <f>IF($Z13="","",IF(OR(AND($T13&lt;&gt;"",N($T13)&gt;N($Z13)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G13,'Chase Log'!$E$4:$E$2000,$Z13,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G13,'Chase Log'!$E$4:$E$2000,$Z13)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G13,'Chase Log'!$E$4:$E$2000,$Z13))))</f>
-        <v/>
+        <v>46331</v>
       </c>
       <c r="AC13" s="13" t="str">
         <f ca="1">IF(OR($G13="",N($S13)&gt;=1,$C13="Live",$D13&lt;&gt;""),"",IF(AND($AB13&lt;&gt;"",N($AB13)&gt;0),IF($AB13&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($T13&lt;&gt;"",N($U13)&gt;='안내 Guide'!$D$4,OR($AA13="",N($AA13)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
-        <v>Chase Needed</v>
+        <v>Scheduled</v>
       </c>
       <c r="AD13" s="28"/>
       <c r="AE13" s="25"/>
@@ -27810,7 +27999,7 @@
       </c>
       <c r="Y14" s="22">
         <f>IF($G14="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G14))</f>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Z14" s="27">
         <f>IF(N($Y14)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G14))</f>
@@ -27939,19 +28128,19 @@
       </c>
       <c r="Y15" s="22">
         <f>IF($G15="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G15))</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Z15" s="27">
         <f>IF(N($Y15)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G15))</f>
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="AA15" s="22">
         <f t="shared" ca="1" si="7"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB15" s="27">
         <f>IF($Z15="","",IF(OR(AND($T15&lt;&gt;"",N($T15)&gt;N($Z15)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G15,'Chase Log'!$E$4:$E$2000,$Z15,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G15,'Chase Log'!$E$4:$E$2000,$Z15)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G15,'Chase Log'!$E$4:$E$2000,$Z15))))</f>
-        <v>46331</v>
+        <v>46332</v>
       </c>
       <c r="AC15" s="13" t="str">
         <f ca="1">IF(OR($G15="",N($S15)&gt;=1,$C15="Live",$D15&lt;&gt;""),"",IF(AND($AB15&lt;&gt;"",N($AB15)&gt;0),IF($AB15&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($T15&lt;&gt;"",N($U15)&gt;='안내 Guide'!$D$4,OR($AA15="",N($AA15)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
@@ -28556,23 +28745,23 @@
       </c>
       <c r="Y20" s="22">
         <f>IF($G20="","",COUNTIF('Chase Log'!$B$4:$B$2000,$G20))</f>
-        <v>0</v>
-      </c>
-      <c r="Z20" s="27" t="str">
+        <v>1</v>
+      </c>
+      <c r="Z20" s="27">
         <f>IF(N($Y20)=0,"",_xlfn.MAXIFS('Chase Log'!$E$4:$E$2000,'Chase Log'!$B$4:$B$2000,$G20))</f>
-        <v/>
-      </c>
-      <c r="AA20" s="22" t="str">
+        <v>46301</v>
+      </c>
+      <c r="AA20" s="22">
         <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="AB20" s="27" t="str">
+        <v>24</v>
+      </c>
+      <c r="AB20" s="27">
         <f>IF($Z20="","",IF(OR(AND($T20&lt;&gt;"",N($T20)&gt;N($Z20)),COUNTIFS('Chase Log'!$B$4:$B$2000,$G20,'Chase Log'!$E$4:$E$2000,$Z20,'Chase Log'!$I$4:$I$2000,"Y")&gt;0),"",IF(_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G20,'Chase Log'!$E$4:$E$2000,$Z20)=0,"",_xlfn.MAXIFS('Chase Log'!$J$4:$J$2000,'Chase Log'!$B$4:$B$2000,$G20,'Chase Log'!$E$4:$E$2000,$Z20))))</f>
-        <v/>
+        <v>46308</v>
       </c>
       <c r="AC20" s="13" t="str">
         <f ca="1">IF(OR($G20="",N($S20)&gt;=1,$C20="Live",$D20&lt;&gt;""),"",IF(AND($AB20&lt;&gt;"",N($AB20)&gt;0),IF($AB20&lt;TODAY(),"Chase Overdue","Scheduled"),IF(AND($T20&lt;&gt;"",N($U20)&gt;='안내 Guide'!$D$4,OR($AA20="",N($AA20)&gt;='안내 Guide'!$D$4)),"Chase Needed","")))</f>
-        <v/>
+        <v>Chase Overdue</v>
       </c>
       <c r="AD20" s="28"/>
       <c r="AE20" s="25"/>
@@ -29297,7 +29486,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:K44"/>
+  <dimension ref="A1:K140"/>
   <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -30642,6 +30831,3147 @@
       </c>
       <c r="K44" t="s">
         <v>41</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45">
+        <v>42</v>
+      </c>
+      <c r="B45" t="s">
+        <v>65</v>
+      </c>
+      <c r="C45" t="s">
+        <v>206</v>
+      </c>
+      <c r="D45" t="s">
+        <v>620</v>
+      </c>
+      <c r="E45" s="68">
+        <v>46324</v>
+      </c>
+      <c r="F45" t="s">
+        <v>613</v>
+      </c>
+      <c r="G45" t="s">
+        <v>630</v>
+      </c>
+      <c r="H45" t="s">
+        <v>615</v>
+      </c>
+      <c r="I45" t="s">
+        <v>604</v>
+      </c>
+      <c r="J45" s="68">
+        <v>46331</v>
+      </c>
+      <c r="K45" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46">
+        <v>43</v>
+      </c>
+      <c r="B46" t="s">
+        <v>565</v>
+      </c>
+      <c r="C46" t="s">
+        <v>257</v>
+      </c>
+      <c r="E46" s="68">
+        <v>46325</v>
+      </c>
+      <c r="F46" t="s">
+        <v>613</v>
+      </c>
+      <c r="G46" t="s">
+        <v>627</v>
+      </c>
+      <c r="H46" t="s">
+        <v>615</v>
+      </c>
+      <c r="I46" t="s">
+        <v>604</v>
+      </c>
+      <c r="J46" s="68">
+        <v>46332</v>
+      </c>
+      <c r="K46" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47">
+        <v>44</v>
+      </c>
+      <c r="B47" t="s">
+        <v>526</v>
+      </c>
+      <c r="C47" t="s">
+        <v>206</v>
+      </c>
+      <c r="D47" t="s">
+        <v>618</v>
+      </c>
+      <c r="E47" s="68">
+        <v>46325</v>
+      </c>
+      <c r="F47" t="s">
+        <v>613</v>
+      </c>
+      <c r="G47" t="s">
+        <v>619</v>
+      </c>
+      <c r="H47" t="s">
+        <v>615</v>
+      </c>
+      <c r="I47" t="s">
+        <v>604</v>
+      </c>
+      <c r="J47" s="68">
+        <v>46332</v>
+      </c>
+      <c r="K47" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="A48">
+        <v>45</v>
+      </c>
+      <c r="B48" t="s">
+        <v>251</v>
+      </c>
+      <c r="C48" t="s">
+        <v>252</v>
+      </c>
+      <c r="E48" s="68">
+        <v>46325</v>
+      </c>
+      <c r="F48" t="s">
+        <v>613</v>
+      </c>
+      <c r="G48" t="s">
+        <v>635</v>
+      </c>
+      <c r="H48" t="s">
+        <v>615</v>
+      </c>
+      <c r="I48" t="s">
+        <v>604</v>
+      </c>
+      <c r="J48" s="68">
+        <v>46332</v>
+      </c>
+      <c r="K48" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="A49">
+        <v>46</v>
+      </c>
+      <c r="B49" t="s">
+        <v>526</v>
+      </c>
+      <c r="C49" t="s">
+        <v>206</v>
+      </c>
+      <c r="D49" t="s">
+        <v>618</v>
+      </c>
+      <c r="E49" s="68">
+        <v>46296</v>
+      </c>
+      <c r="F49" t="s">
+        <v>613</v>
+      </c>
+      <c r="G49" t="s">
+        <v>636</v>
+      </c>
+      <c r="H49" t="s">
+        <v>615</v>
+      </c>
+      <c r="I49" t="s">
+        <v>637</v>
+      </c>
+      <c r="J49" s="68"/>
+      <c r="K49" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50">
+        <v>47</v>
+      </c>
+      <c r="B50" t="s">
+        <v>299</v>
+      </c>
+      <c r="C50" t="s">
+        <v>206</v>
+      </c>
+      <c r="D50" t="s">
+        <v>638</v>
+      </c>
+      <c r="E50" s="68">
+        <v>46296</v>
+      </c>
+      <c r="F50" t="s">
+        <v>613</v>
+      </c>
+      <c r="G50" t="s">
+        <v>639</v>
+      </c>
+      <c r="H50" t="s">
+        <v>615</v>
+      </c>
+      <c r="I50" t="s">
+        <v>604</v>
+      </c>
+      <c r="J50" s="68">
+        <v>46303</v>
+      </c>
+      <c r="K50" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51">
+        <v>48</v>
+      </c>
+      <c r="B51" t="s">
+        <v>560</v>
+      </c>
+      <c r="C51" t="s">
+        <v>206</v>
+      </c>
+      <c r="D51" t="s">
+        <v>620</v>
+      </c>
+      <c r="E51" s="68">
+        <v>46296</v>
+      </c>
+      <c r="F51" t="s">
+        <v>613</v>
+      </c>
+      <c r="G51" t="s">
+        <v>621</v>
+      </c>
+      <c r="H51" t="s">
+        <v>615</v>
+      </c>
+      <c r="I51" t="s">
+        <v>604</v>
+      </c>
+      <c r="J51" s="68">
+        <v>46303</v>
+      </c>
+      <c r="K51" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="A52">
+        <v>49</v>
+      </c>
+      <c r="B52" t="s">
+        <v>538</v>
+      </c>
+      <c r="C52" t="s">
+        <v>206</v>
+      </c>
+      <c r="D52" t="s">
+        <v>622</v>
+      </c>
+      <c r="E52" s="68">
+        <v>46296</v>
+      </c>
+      <c r="F52" t="s">
+        <v>613</v>
+      </c>
+      <c r="G52" t="s">
+        <v>640</v>
+      </c>
+      <c r="H52" t="s">
+        <v>615</v>
+      </c>
+      <c r="I52" t="s">
+        <v>604</v>
+      </c>
+      <c r="J52" s="68">
+        <v>46303</v>
+      </c>
+      <c r="K52" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11">
+      <c r="A53">
+        <v>50</v>
+      </c>
+      <c r="B53" t="s">
+        <v>530</v>
+      </c>
+      <c r="C53" t="s">
+        <v>206</v>
+      </c>
+      <c r="D53" t="s">
+        <v>618</v>
+      </c>
+      <c r="E53" s="68">
+        <v>46296</v>
+      </c>
+      <c r="F53" t="s">
+        <v>613</v>
+      </c>
+      <c r="G53" t="s">
+        <v>641</v>
+      </c>
+      <c r="H53" t="s">
+        <v>615</v>
+      </c>
+      <c r="I53" t="s">
+        <v>637</v>
+      </c>
+      <c r="J53" s="68"/>
+      <c r="K53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11">
+      <c r="A54">
+        <v>51</v>
+      </c>
+      <c r="B54" t="s">
+        <v>251</v>
+      </c>
+      <c r="C54" t="s">
+        <v>252</v>
+      </c>
+      <c r="E54" s="68">
+        <v>46296</v>
+      </c>
+      <c r="F54" t="s">
+        <v>613</v>
+      </c>
+      <c r="G54" t="s">
+        <v>635</v>
+      </c>
+      <c r="H54" t="s">
+        <v>615</v>
+      </c>
+      <c r="I54" t="s">
+        <v>604</v>
+      </c>
+      <c r="J54" s="68">
+        <v>46303</v>
+      </c>
+      <c r="K54" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11">
+      <c r="A55">
+        <v>52</v>
+      </c>
+      <c r="B55" t="s">
+        <v>415</v>
+      </c>
+      <c r="C55" t="s">
+        <v>612</v>
+      </c>
+      <c r="E55" s="68">
+        <v>46297</v>
+      </c>
+      <c r="F55" t="s">
+        <v>613</v>
+      </c>
+      <c r="G55" t="s">
+        <v>642</v>
+      </c>
+      <c r="H55" t="s">
+        <v>615</v>
+      </c>
+      <c r="I55" t="s">
+        <v>604</v>
+      </c>
+      <c r="J55" s="68">
+        <v>46304</v>
+      </c>
+      <c r="K55" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11">
+      <c r="A56">
+        <v>53</v>
+      </c>
+      <c r="B56" t="s">
+        <v>299</v>
+      </c>
+      <c r="C56" t="s">
+        <v>206</v>
+      </c>
+      <c r="D56" t="s">
+        <v>638</v>
+      </c>
+      <c r="E56" s="68">
+        <v>46297</v>
+      </c>
+      <c r="F56" t="s">
+        <v>613</v>
+      </c>
+      <c r="G56" t="s">
+        <v>639</v>
+      </c>
+      <c r="H56" t="s">
+        <v>615</v>
+      </c>
+      <c r="I56" t="s">
+        <v>604</v>
+      </c>
+      <c r="J56" s="68">
+        <v>46304</v>
+      </c>
+      <c r="K56" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11">
+      <c r="A57">
+        <v>54</v>
+      </c>
+      <c r="B57" t="s">
+        <v>542</v>
+      </c>
+      <c r="C57" t="s">
+        <v>206</v>
+      </c>
+      <c r="D57" t="s">
+        <v>628</v>
+      </c>
+      <c r="E57" s="68">
+        <v>46297</v>
+      </c>
+      <c r="F57" t="s">
+        <v>613</v>
+      </c>
+      <c r="G57" t="s">
+        <v>643</v>
+      </c>
+      <c r="H57" t="s">
+        <v>615</v>
+      </c>
+      <c r="I57" t="s">
+        <v>637</v>
+      </c>
+      <c r="J57" s="68"/>
+      <c r="K57" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11">
+      <c r="A58">
+        <v>55</v>
+      </c>
+      <c r="B58" t="s">
+        <v>538</v>
+      </c>
+      <c r="C58" t="s">
+        <v>206</v>
+      </c>
+      <c r="D58" t="s">
+        <v>622</v>
+      </c>
+      <c r="E58" s="68">
+        <v>46297</v>
+      </c>
+      <c r="F58" t="s">
+        <v>613</v>
+      </c>
+      <c r="G58" t="s">
+        <v>644</v>
+      </c>
+      <c r="H58" t="s">
+        <v>615</v>
+      </c>
+      <c r="I58" t="s">
+        <v>604</v>
+      </c>
+      <c r="J58" s="68">
+        <v>46304</v>
+      </c>
+      <c r="K58" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11">
+      <c r="A59">
+        <v>56</v>
+      </c>
+      <c r="B59" t="s">
+        <v>177</v>
+      </c>
+      <c r="C59" t="s">
+        <v>633</v>
+      </c>
+      <c r="E59" s="68">
+        <v>46297</v>
+      </c>
+      <c r="F59" t="s">
+        <v>613</v>
+      </c>
+      <c r="G59" t="s">
+        <v>645</v>
+      </c>
+      <c r="H59" t="s">
+        <v>615</v>
+      </c>
+      <c r="I59" t="s">
+        <v>637</v>
+      </c>
+      <c r="J59" s="68"/>
+      <c r="K59" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11">
+      <c r="A60">
+        <v>57</v>
+      </c>
+      <c r="B60" t="s">
+        <v>402</v>
+      </c>
+      <c r="C60" t="s">
+        <v>612</v>
+      </c>
+      <c r="E60" s="68">
+        <v>46300</v>
+      </c>
+      <c r="F60" t="s">
+        <v>613</v>
+      </c>
+      <c r="G60" t="s">
+        <v>646</v>
+      </c>
+      <c r="H60" t="s">
+        <v>615</v>
+      </c>
+      <c r="I60" t="s">
+        <v>604</v>
+      </c>
+      <c r="J60" s="68">
+        <v>46307</v>
+      </c>
+      <c r="K60" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11">
+      <c r="A61">
+        <v>58</v>
+      </c>
+      <c r="B61" t="s">
+        <v>426</v>
+      </c>
+      <c r="C61" t="s">
+        <v>612</v>
+      </c>
+      <c r="E61" s="68">
+        <v>46300</v>
+      </c>
+      <c r="F61" t="s">
+        <v>613</v>
+      </c>
+      <c r="G61" t="s">
+        <v>647</v>
+      </c>
+      <c r="H61" t="s">
+        <v>615</v>
+      </c>
+      <c r="I61" t="s">
+        <v>637</v>
+      </c>
+      <c r="J61" s="68"/>
+      <c r="K61" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11">
+      <c r="A62">
+        <v>59</v>
+      </c>
+      <c r="B62" t="s">
+        <v>413</v>
+      </c>
+      <c r="C62" t="s">
+        <v>612</v>
+      </c>
+      <c r="E62" s="68">
+        <v>46300</v>
+      </c>
+      <c r="F62" t="s">
+        <v>613</v>
+      </c>
+      <c r="G62" t="s">
+        <v>648</v>
+      </c>
+      <c r="H62" t="s">
+        <v>615</v>
+      </c>
+      <c r="I62" t="s">
+        <v>604</v>
+      </c>
+      <c r="J62" s="68">
+        <v>46307</v>
+      </c>
+      <c r="K62" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11">
+      <c r="A63">
+        <v>60</v>
+      </c>
+      <c r="B63" t="s">
+        <v>414</v>
+      </c>
+      <c r="C63" t="s">
+        <v>612</v>
+      </c>
+      <c r="E63" s="68">
+        <v>46300</v>
+      </c>
+      <c r="F63" t="s">
+        <v>613</v>
+      </c>
+      <c r="G63" t="s">
+        <v>616</v>
+      </c>
+      <c r="H63" t="s">
+        <v>615</v>
+      </c>
+      <c r="I63" t="s">
+        <v>604</v>
+      </c>
+      <c r="J63" s="68">
+        <v>46307</v>
+      </c>
+      <c r="K63" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11">
+      <c r="A64">
+        <v>61</v>
+      </c>
+      <c r="B64" t="s">
+        <v>418</v>
+      </c>
+      <c r="C64" t="s">
+        <v>612</v>
+      </c>
+      <c r="E64" s="68">
+        <v>46300</v>
+      </c>
+      <c r="F64" t="s">
+        <v>613</v>
+      </c>
+      <c r="G64" t="s">
+        <v>649</v>
+      </c>
+      <c r="H64" t="s">
+        <v>615</v>
+      </c>
+      <c r="I64" t="s">
+        <v>604</v>
+      </c>
+      <c r="J64" s="68">
+        <v>46307</v>
+      </c>
+      <c r="K64" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11">
+      <c r="A65">
+        <v>62</v>
+      </c>
+      <c r="B65" t="s">
+        <v>330</v>
+      </c>
+      <c r="C65" t="s">
+        <v>206</v>
+      </c>
+      <c r="D65" t="s">
+        <v>624</v>
+      </c>
+      <c r="E65" s="68">
+        <v>46300</v>
+      </c>
+      <c r="F65" t="s">
+        <v>613</v>
+      </c>
+      <c r="G65" t="s">
+        <v>650</v>
+      </c>
+      <c r="H65" t="s">
+        <v>615</v>
+      </c>
+      <c r="I65" t="s">
+        <v>604</v>
+      </c>
+      <c r="J65" s="68">
+        <v>46307</v>
+      </c>
+      <c r="K65" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11">
+      <c r="A66">
+        <v>63</v>
+      </c>
+      <c r="B66" t="s">
+        <v>430</v>
+      </c>
+      <c r="C66" t="s">
+        <v>612</v>
+      </c>
+      <c r="E66" s="68">
+        <v>46300</v>
+      </c>
+      <c r="F66" t="s">
+        <v>613</v>
+      </c>
+      <c r="G66" t="s">
+        <v>616</v>
+      </c>
+      <c r="H66" t="s">
+        <v>615</v>
+      </c>
+      <c r="I66" t="s">
+        <v>604</v>
+      </c>
+      <c r="J66" s="68">
+        <v>46307</v>
+      </c>
+      <c r="K66" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11">
+      <c r="A67">
+        <v>64</v>
+      </c>
+      <c r="B67" t="s">
+        <v>419</v>
+      </c>
+      <c r="C67" t="s">
+        <v>612</v>
+      </c>
+      <c r="E67" s="68">
+        <v>46300</v>
+      </c>
+      <c r="F67" t="s">
+        <v>613</v>
+      </c>
+      <c r="G67" t="s">
+        <v>651</v>
+      </c>
+      <c r="H67" t="s">
+        <v>615</v>
+      </c>
+      <c r="I67" t="s">
+        <v>604</v>
+      </c>
+      <c r="J67" s="68">
+        <v>46307</v>
+      </c>
+      <c r="K67" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11">
+      <c r="A68">
+        <v>65</v>
+      </c>
+      <c r="B68" t="s">
+        <v>420</v>
+      </c>
+      <c r="C68" t="s">
+        <v>612</v>
+      </c>
+      <c r="E68" s="68">
+        <v>46300</v>
+      </c>
+      <c r="F68" t="s">
+        <v>613</v>
+      </c>
+      <c r="G68" t="s">
+        <v>652</v>
+      </c>
+      <c r="H68" t="s">
+        <v>615</v>
+      </c>
+      <c r="I68" t="s">
+        <v>604</v>
+      </c>
+      <c r="J68" s="68">
+        <v>46307</v>
+      </c>
+      <c r="K68" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11">
+      <c r="A69">
+        <v>66</v>
+      </c>
+      <c r="B69" t="s">
+        <v>265</v>
+      </c>
+      <c r="C69" t="s">
+        <v>653</v>
+      </c>
+      <c r="E69" s="68">
+        <v>46300</v>
+      </c>
+      <c r="F69" t="s">
+        <v>613</v>
+      </c>
+      <c r="G69" t="s">
+        <v>654</v>
+      </c>
+      <c r="H69" t="s">
+        <v>615</v>
+      </c>
+      <c r="I69" t="s">
+        <v>604</v>
+      </c>
+      <c r="J69" s="68">
+        <v>46307</v>
+      </c>
+      <c r="K69" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11">
+      <c r="A70">
+        <v>67</v>
+      </c>
+      <c r="B70" t="s">
+        <v>433</v>
+      </c>
+      <c r="C70" t="s">
+        <v>612</v>
+      </c>
+      <c r="E70" s="68">
+        <v>46300</v>
+      </c>
+      <c r="F70" t="s">
+        <v>613</v>
+      </c>
+      <c r="G70" t="s">
+        <v>655</v>
+      </c>
+      <c r="H70" t="s">
+        <v>615</v>
+      </c>
+      <c r="I70" t="s">
+        <v>604</v>
+      </c>
+      <c r="J70" s="68">
+        <v>46307</v>
+      </c>
+      <c r="K70" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11">
+      <c r="A71">
+        <v>68</v>
+      </c>
+      <c r="B71" t="s">
+        <v>421</v>
+      </c>
+      <c r="C71" t="s">
+        <v>612</v>
+      </c>
+      <c r="E71" s="68">
+        <v>46300</v>
+      </c>
+      <c r="F71" t="s">
+        <v>613</v>
+      </c>
+      <c r="G71" t="s">
+        <v>656</v>
+      </c>
+      <c r="H71" t="s">
+        <v>615</v>
+      </c>
+      <c r="I71" t="s">
+        <v>604</v>
+      </c>
+      <c r="J71" s="68">
+        <v>46307</v>
+      </c>
+      <c r="K71" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11">
+      <c r="A72">
+        <v>69</v>
+      </c>
+      <c r="B72" t="s">
+        <v>434</v>
+      </c>
+      <c r="C72" t="s">
+        <v>612</v>
+      </c>
+      <c r="E72" s="68">
+        <v>46300</v>
+      </c>
+      <c r="F72" t="s">
+        <v>613</v>
+      </c>
+      <c r="G72" t="s">
+        <v>657</v>
+      </c>
+      <c r="H72" t="s">
+        <v>615</v>
+      </c>
+      <c r="I72" t="s">
+        <v>604</v>
+      </c>
+      <c r="J72" s="68">
+        <v>46307</v>
+      </c>
+      <c r="K72" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11">
+      <c r="A73">
+        <v>70</v>
+      </c>
+      <c r="B73" t="s">
+        <v>422</v>
+      </c>
+      <c r="C73" t="s">
+        <v>612</v>
+      </c>
+      <c r="E73" s="68">
+        <v>46300</v>
+      </c>
+      <c r="F73" t="s">
+        <v>613</v>
+      </c>
+      <c r="G73" t="s">
+        <v>658</v>
+      </c>
+      <c r="H73" t="s">
+        <v>615</v>
+      </c>
+      <c r="I73" t="s">
+        <v>604</v>
+      </c>
+      <c r="J73" s="68">
+        <v>46307</v>
+      </c>
+      <c r="K73" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11">
+      <c r="A74">
+        <v>71</v>
+      </c>
+      <c r="B74" t="s">
+        <v>423</v>
+      </c>
+      <c r="C74" t="s">
+        <v>612</v>
+      </c>
+      <c r="E74" s="68">
+        <v>46300</v>
+      </c>
+      <c r="F74" t="s">
+        <v>613</v>
+      </c>
+      <c r="G74" t="s">
+        <v>659</v>
+      </c>
+      <c r="H74" t="s">
+        <v>615</v>
+      </c>
+      <c r="I74" t="s">
+        <v>604</v>
+      </c>
+      <c r="J74" s="68">
+        <v>46307</v>
+      </c>
+      <c r="K74" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11">
+      <c r="A75">
+        <v>72</v>
+      </c>
+      <c r="B75" t="s">
+        <v>270</v>
+      </c>
+      <c r="C75" t="s">
+        <v>653</v>
+      </c>
+      <c r="E75" s="68">
+        <v>46300</v>
+      </c>
+      <c r="F75" t="s">
+        <v>613</v>
+      </c>
+      <c r="G75" t="s">
+        <v>660</v>
+      </c>
+      <c r="H75" t="s">
+        <v>615</v>
+      </c>
+      <c r="I75" t="s">
+        <v>604</v>
+      </c>
+      <c r="J75" s="68">
+        <v>46307</v>
+      </c>
+      <c r="K75" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11">
+      <c r="A76">
+        <v>73</v>
+      </c>
+      <c r="B76" t="s">
+        <v>349</v>
+      </c>
+      <c r="C76" t="s">
+        <v>206</v>
+      </c>
+      <c r="E76" s="68">
+        <v>46300</v>
+      </c>
+      <c r="F76" t="s">
+        <v>613</v>
+      </c>
+      <c r="G76" t="s">
+        <v>661</v>
+      </c>
+      <c r="H76" t="s">
+        <v>615</v>
+      </c>
+      <c r="I76" t="s">
+        <v>604</v>
+      </c>
+      <c r="J76" s="68">
+        <v>46307</v>
+      </c>
+      <c r="K76" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11">
+      <c r="A77">
+        <v>74</v>
+      </c>
+      <c r="B77" t="s">
+        <v>424</v>
+      </c>
+      <c r="C77" t="s">
+        <v>612</v>
+      </c>
+      <c r="E77" s="68">
+        <v>46300</v>
+      </c>
+      <c r="F77" t="s">
+        <v>613</v>
+      </c>
+      <c r="G77" t="s">
+        <v>662</v>
+      </c>
+      <c r="H77" t="s">
+        <v>615</v>
+      </c>
+      <c r="I77" t="s">
+        <v>604</v>
+      </c>
+      <c r="J77" s="68">
+        <v>46307</v>
+      </c>
+      <c r="K77" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11">
+      <c r="A78">
+        <v>75</v>
+      </c>
+      <c r="B78" t="s">
+        <v>435</v>
+      </c>
+      <c r="C78" t="s">
+        <v>612</v>
+      </c>
+      <c r="E78" s="68">
+        <v>46300</v>
+      </c>
+      <c r="F78" t="s">
+        <v>613</v>
+      </c>
+      <c r="G78" t="s">
+        <v>663</v>
+      </c>
+      <c r="H78" t="s">
+        <v>615</v>
+      </c>
+      <c r="I78" t="s">
+        <v>604</v>
+      </c>
+      <c r="J78" s="68">
+        <v>46307</v>
+      </c>
+      <c r="K78" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11">
+      <c r="A79">
+        <v>76</v>
+      </c>
+      <c r="B79" t="s">
+        <v>59</v>
+      </c>
+      <c r="C79" t="s">
+        <v>206</v>
+      </c>
+      <c r="D79" t="s">
+        <v>664</v>
+      </c>
+      <c r="E79" s="68">
+        <v>46301</v>
+      </c>
+      <c r="F79" t="s">
+        <v>613</v>
+      </c>
+      <c r="G79" t="s">
+        <v>665</v>
+      </c>
+      <c r="H79" t="s">
+        <v>615</v>
+      </c>
+      <c r="I79" t="s">
+        <v>604</v>
+      </c>
+      <c r="J79" s="68">
+        <v>46308</v>
+      </c>
+      <c r="K79" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11">
+      <c r="A80">
+        <v>77</v>
+      </c>
+      <c r="B80" t="s">
+        <v>352</v>
+      </c>
+      <c r="C80" t="s">
+        <v>206</v>
+      </c>
+      <c r="E80" s="68">
+        <v>46301</v>
+      </c>
+      <c r="F80" t="s">
+        <v>613</v>
+      </c>
+      <c r="G80" t="s">
+        <v>666</v>
+      </c>
+      <c r="H80" t="s">
+        <v>615</v>
+      </c>
+      <c r="I80" t="s">
+        <v>604</v>
+      </c>
+      <c r="J80" s="68">
+        <v>46308</v>
+      </c>
+      <c r="K80" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11">
+      <c r="A81">
+        <v>78</v>
+      </c>
+      <c r="B81" t="s">
+        <v>230</v>
+      </c>
+      <c r="C81" t="s">
+        <v>215</v>
+      </c>
+      <c r="E81" s="68">
+        <v>46301</v>
+      </c>
+      <c r="F81" t="s">
+        <v>613</v>
+      </c>
+      <c r="G81" t="s">
+        <v>617</v>
+      </c>
+      <c r="H81" t="s">
+        <v>615</v>
+      </c>
+      <c r="I81" t="s">
+        <v>604</v>
+      </c>
+      <c r="J81" s="68">
+        <v>46308</v>
+      </c>
+      <c r="K81" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11">
+      <c r="A82">
+        <v>79</v>
+      </c>
+      <c r="B82" t="s">
+        <v>581</v>
+      </c>
+      <c r="C82" t="s">
+        <v>667</v>
+      </c>
+      <c r="E82" s="68">
+        <v>46301</v>
+      </c>
+      <c r="F82" t="s">
+        <v>613</v>
+      </c>
+      <c r="G82" t="s">
+        <v>668</v>
+      </c>
+      <c r="H82" t="s">
+        <v>615</v>
+      </c>
+      <c r="I82" t="s">
+        <v>604</v>
+      </c>
+      <c r="J82" s="68">
+        <v>46308</v>
+      </c>
+      <c r="K82" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11">
+      <c r="A83">
+        <v>80</v>
+      </c>
+      <c r="B83" t="s">
+        <v>274</v>
+      </c>
+      <c r="C83" t="s">
+        <v>653</v>
+      </c>
+      <c r="E83" s="68">
+        <v>46301</v>
+      </c>
+      <c r="F83" t="s">
+        <v>613</v>
+      </c>
+      <c r="G83" t="s">
+        <v>669</v>
+      </c>
+      <c r="H83" t="s">
+        <v>615</v>
+      </c>
+      <c r="I83" t="s">
+        <v>637</v>
+      </c>
+      <c r="J83" s="68"/>
+      <c r="K83" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11">
+      <c r="A84">
+        <v>81</v>
+      </c>
+      <c r="B84" t="s">
+        <v>405</v>
+      </c>
+      <c r="C84" t="s">
+        <v>612</v>
+      </c>
+      <c r="E84" s="68">
+        <v>46302</v>
+      </c>
+      <c r="F84" t="s">
+        <v>613</v>
+      </c>
+      <c r="G84" t="s">
+        <v>670</v>
+      </c>
+      <c r="H84" t="s">
+        <v>615</v>
+      </c>
+      <c r="I84" t="s">
+        <v>604</v>
+      </c>
+      <c r="J84" s="68">
+        <v>46309</v>
+      </c>
+      <c r="K84" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11">
+      <c r="A85">
+        <v>82</v>
+      </c>
+      <c r="B85" t="s">
+        <v>230</v>
+      </c>
+      <c r="C85" t="s">
+        <v>215</v>
+      </c>
+      <c r="E85" s="68">
+        <v>46302</v>
+      </c>
+      <c r="F85" t="s">
+        <v>613</v>
+      </c>
+      <c r="G85" t="s">
+        <v>617</v>
+      </c>
+      <c r="H85" t="s">
+        <v>615</v>
+      </c>
+      <c r="I85" t="s">
+        <v>604</v>
+      </c>
+      <c r="J85" s="68">
+        <v>46309</v>
+      </c>
+      <c r="K85" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11">
+      <c r="A86">
+        <v>83</v>
+      </c>
+      <c r="B86" t="s">
+        <v>560</v>
+      </c>
+      <c r="C86" t="s">
+        <v>206</v>
+      </c>
+      <c r="D86" t="s">
+        <v>620</v>
+      </c>
+      <c r="E86" s="68">
+        <v>46302</v>
+      </c>
+      <c r="F86" t="s">
+        <v>613</v>
+      </c>
+      <c r="G86" t="s">
+        <v>621</v>
+      </c>
+      <c r="H86" t="s">
+        <v>615</v>
+      </c>
+      <c r="I86" t="s">
+        <v>604</v>
+      </c>
+      <c r="J86" s="68">
+        <v>46309</v>
+      </c>
+      <c r="K86" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11">
+      <c r="A87">
+        <v>84</v>
+      </c>
+      <c r="B87" t="s">
+        <v>542</v>
+      </c>
+      <c r="C87" t="s">
+        <v>206</v>
+      </c>
+      <c r="D87" t="s">
+        <v>628</v>
+      </c>
+      <c r="E87" s="68">
+        <v>46302</v>
+      </c>
+      <c r="F87" t="s">
+        <v>613</v>
+      </c>
+      <c r="G87" t="s">
+        <v>643</v>
+      </c>
+      <c r="H87" t="s">
+        <v>615</v>
+      </c>
+      <c r="I87" t="s">
+        <v>637</v>
+      </c>
+      <c r="J87" s="68"/>
+      <c r="K87" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11">
+      <c r="A88">
+        <v>85</v>
+      </c>
+      <c r="B88" t="s">
+        <v>256</v>
+      </c>
+      <c r="C88" t="s">
+        <v>257</v>
+      </c>
+      <c r="E88" s="68">
+        <v>46302</v>
+      </c>
+      <c r="F88" t="s">
+        <v>613</v>
+      </c>
+      <c r="G88" t="s">
+        <v>671</v>
+      </c>
+      <c r="H88" t="s">
+        <v>615</v>
+      </c>
+      <c r="I88" t="s">
+        <v>604</v>
+      </c>
+      <c r="J88" s="68">
+        <v>46309</v>
+      </c>
+      <c r="K88" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11">
+      <c r="A89">
+        <v>86</v>
+      </c>
+      <c r="B89" t="s">
+        <v>274</v>
+      </c>
+      <c r="C89" t="s">
+        <v>653</v>
+      </c>
+      <c r="E89" s="68">
+        <v>46302</v>
+      </c>
+      <c r="F89" t="s">
+        <v>613</v>
+      </c>
+      <c r="G89" t="s">
+        <v>669</v>
+      </c>
+      <c r="H89" t="s">
+        <v>615</v>
+      </c>
+      <c r="I89" t="s">
+        <v>604</v>
+      </c>
+      <c r="J89" s="68">
+        <v>46309</v>
+      </c>
+      <c r="K89" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11">
+      <c r="A90">
+        <v>87</v>
+      </c>
+      <c r="B90" t="s">
+        <v>526</v>
+      </c>
+      <c r="C90" t="s">
+        <v>206</v>
+      </c>
+      <c r="D90" t="s">
+        <v>618</v>
+      </c>
+      <c r="E90" s="68">
+        <v>46303</v>
+      </c>
+      <c r="F90" t="s">
+        <v>613</v>
+      </c>
+      <c r="G90" t="s">
+        <v>636</v>
+      </c>
+      <c r="H90" t="s">
+        <v>615</v>
+      </c>
+      <c r="I90" t="s">
+        <v>637</v>
+      </c>
+      <c r="J90" s="68"/>
+      <c r="K90" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11">
+      <c r="A91">
+        <v>88</v>
+      </c>
+      <c r="B91" t="s">
+        <v>230</v>
+      </c>
+      <c r="C91" t="s">
+        <v>215</v>
+      </c>
+      <c r="E91" s="68">
+        <v>46303</v>
+      </c>
+      <c r="F91" t="s">
+        <v>613</v>
+      </c>
+      <c r="G91" t="s">
+        <v>617</v>
+      </c>
+      <c r="H91" t="s">
+        <v>615</v>
+      </c>
+      <c r="I91" t="s">
+        <v>604</v>
+      </c>
+      <c r="J91" s="68">
+        <v>46310</v>
+      </c>
+      <c r="K91" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11">
+      <c r="A92">
+        <v>89</v>
+      </c>
+      <c r="B92" t="s">
+        <v>154</v>
+      </c>
+      <c r="C92" t="s">
+        <v>159</v>
+      </c>
+      <c r="D92" t="s">
+        <v>672</v>
+      </c>
+      <c r="E92" s="68">
+        <v>46303</v>
+      </c>
+      <c r="F92" t="s">
+        <v>613</v>
+      </c>
+      <c r="G92" t="s">
+        <v>673</v>
+      </c>
+      <c r="H92" t="s">
+        <v>615</v>
+      </c>
+      <c r="I92" t="s">
+        <v>604</v>
+      </c>
+      <c r="J92" s="68">
+        <v>46310</v>
+      </c>
+      <c r="K92" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11">
+      <c r="A93">
+        <v>90</v>
+      </c>
+      <c r="B93" t="s">
+        <v>381</v>
+      </c>
+      <c r="C93" t="s">
+        <v>612</v>
+      </c>
+      <c r="E93" s="68">
+        <v>46303</v>
+      </c>
+      <c r="F93" t="s">
+        <v>613</v>
+      </c>
+      <c r="G93" t="s">
+        <v>626</v>
+      </c>
+      <c r="H93" t="s">
+        <v>615</v>
+      </c>
+      <c r="I93" t="s">
+        <v>637</v>
+      </c>
+      <c r="J93" s="68"/>
+      <c r="K93" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11">
+      <c r="A94">
+        <v>91</v>
+      </c>
+      <c r="B94" t="s">
+        <v>530</v>
+      </c>
+      <c r="C94" t="s">
+        <v>206</v>
+      </c>
+      <c r="D94" t="s">
+        <v>618</v>
+      </c>
+      <c r="E94" s="68">
+        <v>46303</v>
+      </c>
+      <c r="F94" t="s">
+        <v>613</v>
+      </c>
+      <c r="G94" t="s">
+        <v>674</v>
+      </c>
+      <c r="H94" t="s">
+        <v>615</v>
+      </c>
+      <c r="I94" t="s">
+        <v>637</v>
+      </c>
+      <c r="J94" s="68"/>
+      <c r="K94" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11">
+      <c r="A95">
+        <v>92</v>
+      </c>
+      <c r="B95" t="s">
+        <v>526</v>
+      </c>
+      <c r="C95" t="s">
+        <v>206</v>
+      </c>
+      <c r="D95" t="s">
+        <v>618</v>
+      </c>
+      <c r="E95" s="68">
+        <v>46304</v>
+      </c>
+      <c r="F95" t="s">
+        <v>613</v>
+      </c>
+      <c r="G95" t="s">
+        <v>636</v>
+      </c>
+      <c r="H95" t="s">
+        <v>615</v>
+      </c>
+      <c r="I95" t="s">
+        <v>637</v>
+      </c>
+      <c r="J95" s="68"/>
+      <c r="K95" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11">
+      <c r="A96">
+        <v>93</v>
+      </c>
+      <c r="B96" t="s">
+        <v>560</v>
+      </c>
+      <c r="C96" t="s">
+        <v>206</v>
+      </c>
+      <c r="D96" t="s">
+        <v>620</v>
+      </c>
+      <c r="E96" s="68">
+        <v>46304</v>
+      </c>
+      <c r="F96" t="s">
+        <v>613</v>
+      </c>
+      <c r="G96" t="s">
+        <v>621</v>
+      </c>
+      <c r="H96" t="s">
+        <v>615</v>
+      </c>
+      <c r="I96" t="s">
+        <v>604</v>
+      </c>
+      <c r="J96" s="68">
+        <v>46311</v>
+      </c>
+      <c r="K96" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11">
+      <c r="A97">
+        <v>94</v>
+      </c>
+      <c r="B97" t="s">
+        <v>542</v>
+      </c>
+      <c r="C97" t="s">
+        <v>206</v>
+      </c>
+      <c r="D97" t="s">
+        <v>628</v>
+      </c>
+      <c r="E97" s="68">
+        <v>46304</v>
+      </c>
+      <c r="F97" t="s">
+        <v>613</v>
+      </c>
+      <c r="G97" t="s">
+        <v>643</v>
+      </c>
+      <c r="H97" t="s">
+        <v>615</v>
+      </c>
+      <c r="I97" t="s">
+        <v>637</v>
+      </c>
+      <c r="J97" s="68"/>
+      <c r="K97" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11">
+      <c r="A98">
+        <v>95</v>
+      </c>
+      <c r="B98" t="s">
+        <v>560</v>
+      </c>
+      <c r="C98" t="s">
+        <v>206</v>
+      </c>
+      <c r="D98" t="s">
+        <v>620</v>
+      </c>
+      <c r="E98" s="68">
+        <v>46307</v>
+      </c>
+      <c r="F98" t="s">
+        <v>613</v>
+      </c>
+      <c r="G98" t="s">
+        <v>621</v>
+      </c>
+      <c r="H98" t="s">
+        <v>615</v>
+      </c>
+      <c r="I98" t="s">
+        <v>604</v>
+      </c>
+      <c r="J98" s="68">
+        <v>46314</v>
+      </c>
+      <c r="K98" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11">
+      <c r="A99">
+        <v>96</v>
+      </c>
+      <c r="B99" t="s">
+        <v>526</v>
+      </c>
+      <c r="C99" t="s">
+        <v>206</v>
+      </c>
+      <c r="D99" t="s">
+        <v>618</v>
+      </c>
+      <c r="E99" s="68">
+        <v>46308</v>
+      </c>
+      <c r="F99" t="s">
+        <v>613</v>
+      </c>
+      <c r="G99" t="s">
+        <v>675</v>
+      </c>
+      <c r="H99" t="s">
+        <v>615</v>
+      </c>
+      <c r="I99" t="s">
+        <v>637</v>
+      </c>
+      <c r="J99" s="68"/>
+      <c r="K99" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11">
+      <c r="A100">
+        <v>97</v>
+      </c>
+      <c r="B100" t="s">
+        <v>530</v>
+      </c>
+      <c r="C100" t="s">
+        <v>206</v>
+      </c>
+      <c r="D100" t="s">
+        <v>618</v>
+      </c>
+      <c r="E100" s="68">
+        <v>46308</v>
+      </c>
+      <c r="F100" t="s">
+        <v>613</v>
+      </c>
+      <c r="G100" t="s">
+        <v>674</v>
+      </c>
+      <c r="H100" t="s">
+        <v>615</v>
+      </c>
+      <c r="I100" t="s">
+        <v>637</v>
+      </c>
+      <c r="J100" s="68"/>
+      <c r="K100" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11">
+      <c r="A101">
+        <v>98</v>
+      </c>
+      <c r="B101" t="s">
+        <v>526</v>
+      </c>
+      <c r="C101" t="s">
+        <v>206</v>
+      </c>
+      <c r="D101" t="s">
+        <v>618</v>
+      </c>
+      <c r="E101" s="68">
+        <v>46309</v>
+      </c>
+      <c r="F101" t="s">
+        <v>613</v>
+      </c>
+      <c r="G101" t="s">
+        <v>675</v>
+      </c>
+      <c r="H101" t="s">
+        <v>615</v>
+      </c>
+      <c r="I101" t="s">
+        <v>637</v>
+      </c>
+      <c r="J101" s="68"/>
+      <c r="K101" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11">
+      <c r="A102">
+        <v>99</v>
+      </c>
+      <c r="B102" t="s">
+        <v>542</v>
+      </c>
+      <c r="C102" t="s">
+        <v>206</v>
+      </c>
+      <c r="D102" t="s">
+        <v>628</v>
+      </c>
+      <c r="E102" s="68">
+        <v>46309</v>
+      </c>
+      <c r="F102" t="s">
+        <v>613</v>
+      </c>
+      <c r="G102" t="s">
+        <v>643</v>
+      </c>
+      <c r="H102" t="s">
+        <v>615</v>
+      </c>
+      <c r="I102" t="s">
+        <v>637</v>
+      </c>
+      <c r="J102" s="68"/>
+      <c r="K102" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11">
+      <c r="A103">
+        <v>100</v>
+      </c>
+      <c r="B103" t="s">
+        <v>530</v>
+      </c>
+      <c r="C103" t="s">
+        <v>206</v>
+      </c>
+      <c r="D103" t="s">
+        <v>618</v>
+      </c>
+      <c r="E103" s="68">
+        <v>46309</v>
+      </c>
+      <c r="F103" t="s">
+        <v>613</v>
+      </c>
+      <c r="G103" t="s">
+        <v>631</v>
+      </c>
+      <c r="H103" t="s">
+        <v>615</v>
+      </c>
+      <c r="I103" t="s">
+        <v>637</v>
+      </c>
+      <c r="J103" s="68"/>
+      <c r="K103" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11">
+      <c r="A104">
+        <v>101</v>
+      </c>
+      <c r="B104" t="s">
+        <v>251</v>
+      </c>
+      <c r="C104" t="s">
+        <v>252</v>
+      </c>
+      <c r="E104" s="68">
+        <v>46309</v>
+      </c>
+      <c r="F104" t="s">
+        <v>613</v>
+      </c>
+      <c r="G104" t="s">
+        <v>676</v>
+      </c>
+      <c r="H104" t="s">
+        <v>615</v>
+      </c>
+      <c r="I104" t="s">
+        <v>604</v>
+      </c>
+      <c r="J104" s="68">
+        <v>46316</v>
+      </c>
+      <c r="K104" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11">
+      <c r="A105">
+        <v>102</v>
+      </c>
+      <c r="B105" t="s">
+        <v>405</v>
+      </c>
+      <c r="C105" t="s">
+        <v>612</v>
+      </c>
+      <c r="E105" s="68">
+        <v>46313</v>
+      </c>
+      <c r="F105" t="s">
+        <v>613</v>
+      </c>
+      <c r="G105" t="s">
+        <v>670</v>
+      </c>
+      <c r="H105" t="s">
+        <v>615</v>
+      </c>
+      <c r="I105" t="s">
+        <v>604</v>
+      </c>
+      <c r="J105" s="68">
+        <v>46320</v>
+      </c>
+      <c r="K105" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11">
+      <c r="A106">
+        <v>103</v>
+      </c>
+      <c r="B106" t="s">
+        <v>330</v>
+      </c>
+      <c r="C106" t="s">
+        <v>206</v>
+      </c>
+      <c r="D106" t="s">
+        <v>624</v>
+      </c>
+      <c r="E106" s="68">
+        <v>46313</v>
+      </c>
+      <c r="F106" t="s">
+        <v>613</v>
+      </c>
+      <c r="G106" t="s">
+        <v>650</v>
+      </c>
+      <c r="H106" t="s">
+        <v>615</v>
+      </c>
+      <c r="I106" t="s">
+        <v>604</v>
+      </c>
+      <c r="J106" s="68">
+        <v>46320</v>
+      </c>
+      <c r="K106" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11">
+      <c r="A107">
+        <v>104</v>
+      </c>
+      <c r="B107" t="s">
+        <v>560</v>
+      </c>
+      <c r="C107" t="s">
+        <v>206</v>
+      </c>
+      <c r="D107" t="s">
+        <v>620</v>
+      </c>
+      <c r="E107" s="68">
+        <v>46313</v>
+      </c>
+      <c r="F107" t="s">
+        <v>613</v>
+      </c>
+      <c r="G107" t="s">
+        <v>677</v>
+      </c>
+      <c r="H107" t="s">
+        <v>615</v>
+      </c>
+      <c r="I107" t="s">
+        <v>604</v>
+      </c>
+      <c r="J107" s="68">
+        <v>46320</v>
+      </c>
+      <c r="K107" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11">
+      <c r="A108">
+        <v>105</v>
+      </c>
+      <c r="B108" t="s">
+        <v>542</v>
+      </c>
+      <c r="C108" t="s">
+        <v>206</v>
+      </c>
+      <c r="D108" t="s">
+        <v>628</v>
+      </c>
+      <c r="E108" s="68">
+        <v>46313</v>
+      </c>
+      <c r="F108" t="s">
+        <v>613</v>
+      </c>
+      <c r="G108" t="s">
+        <v>643</v>
+      </c>
+      <c r="H108" t="s">
+        <v>615</v>
+      </c>
+      <c r="I108" t="s">
+        <v>637</v>
+      </c>
+      <c r="J108" s="68"/>
+      <c r="K108" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11">
+      <c r="A109">
+        <v>106</v>
+      </c>
+      <c r="B109" t="s">
+        <v>292</v>
+      </c>
+      <c r="C109" t="s">
+        <v>257</v>
+      </c>
+      <c r="E109" s="68">
+        <v>46314</v>
+      </c>
+      <c r="F109" t="s">
+        <v>613</v>
+      </c>
+      <c r="G109" t="s">
+        <v>678</v>
+      </c>
+      <c r="H109" t="s">
+        <v>615</v>
+      </c>
+      <c r="I109" t="s">
+        <v>604</v>
+      </c>
+      <c r="J109" s="68">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11">
+      <c r="A110">
+        <v>107</v>
+      </c>
+      <c r="B110" t="s">
+        <v>565</v>
+      </c>
+      <c r="C110" t="s">
+        <v>257</v>
+      </c>
+      <c r="E110" s="68">
+        <v>46314</v>
+      </c>
+      <c r="F110" t="s">
+        <v>613</v>
+      </c>
+      <c r="G110" t="s">
+        <v>627</v>
+      </c>
+      <c r="H110" t="s">
+        <v>615</v>
+      </c>
+      <c r="I110" t="s">
+        <v>604</v>
+      </c>
+      <c r="J110" s="68">
+        <v>46321</v>
+      </c>
+      <c r="K110" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11">
+      <c r="A111">
+        <v>108</v>
+      </c>
+      <c r="B111" t="s">
+        <v>64</v>
+      </c>
+      <c r="C111" t="s">
+        <v>257</v>
+      </c>
+      <c r="D111" t="s">
+        <v>620</v>
+      </c>
+      <c r="E111" s="68">
+        <v>46314</v>
+      </c>
+      <c r="F111" t="s">
+        <v>613</v>
+      </c>
+      <c r="G111" t="s">
+        <v>679</v>
+      </c>
+      <c r="H111" t="s">
+        <v>615</v>
+      </c>
+      <c r="I111" t="s">
+        <v>637</v>
+      </c>
+      <c r="J111" s="68"/>
+      <c r="K111" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11">
+      <c r="A112">
+        <v>109</v>
+      </c>
+      <c r="B112" t="s">
+        <v>381</v>
+      </c>
+      <c r="C112" t="s">
+        <v>612</v>
+      </c>
+      <c r="E112" s="68">
+        <v>46314</v>
+      </c>
+      <c r="F112" t="s">
+        <v>613</v>
+      </c>
+      <c r="G112" t="s">
+        <v>680</v>
+      </c>
+      <c r="H112" t="s">
+        <v>615</v>
+      </c>
+      <c r="I112" t="s">
+        <v>604</v>
+      </c>
+      <c r="J112" s="68">
+        <v>46321</v>
+      </c>
+      <c r="K112" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11">
+      <c r="A113">
+        <v>110</v>
+      </c>
+      <c r="B113" t="s">
+        <v>65</v>
+      </c>
+      <c r="C113" t="s">
+        <v>206</v>
+      </c>
+      <c r="D113" t="s">
+        <v>620</v>
+      </c>
+      <c r="E113" s="68">
+        <v>46314</v>
+      </c>
+      <c r="F113" t="s">
+        <v>613</v>
+      </c>
+      <c r="G113" t="s">
+        <v>681</v>
+      </c>
+      <c r="H113" t="s">
+        <v>615</v>
+      </c>
+      <c r="I113" t="s">
+        <v>604</v>
+      </c>
+      <c r="J113" s="68">
+        <v>46321</v>
+      </c>
+      <c r="K113" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11">
+      <c r="A114">
+        <v>111</v>
+      </c>
+      <c r="B114" t="s">
+        <v>565</v>
+      </c>
+      <c r="C114" t="s">
+        <v>257</v>
+      </c>
+      <c r="E114" s="68">
+        <v>46315</v>
+      </c>
+      <c r="F114" t="s">
+        <v>613</v>
+      </c>
+      <c r="G114" t="s">
+        <v>627</v>
+      </c>
+      <c r="H114" t="s">
+        <v>615</v>
+      </c>
+      <c r="I114" t="s">
+        <v>604</v>
+      </c>
+      <c r="J114" s="68">
+        <v>46322</v>
+      </c>
+      <c r="K114" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11">
+      <c r="A115">
+        <v>112</v>
+      </c>
+      <c r="B115" t="s">
+        <v>212</v>
+      </c>
+      <c r="C115" t="s">
+        <v>215</v>
+      </c>
+      <c r="D115" t="s">
+        <v>620</v>
+      </c>
+      <c r="E115" s="68">
+        <v>46315</v>
+      </c>
+      <c r="F115" t="s">
+        <v>613</v>
+      </c>
+      <c r="G115" t="s">
+        <v>682</v>
+      </c>
+      <c r="H115" t="s">
+        <v>615</v>
+      </c>
+      <c r="I115" t="s">
+        <v>604</v>
+      </c>
+      <c r="J115" s="68">
+        <v>46322</v>
+      </c>
+      <c r="K115" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11">
+      <c r="A116">
+        <v>113</v>
+      </c>
+      <c r="B116" t="s">
+        <v>538</v>
+      </c>
+      <c r="C116" t="s">
+        <v>206</v>
+      </c>
+      <c r="D116" t="s">
+        <v>622</v>
+      </c>
+      <c r="E116" s="68">
+        <v>46315</v>
+      </c>
+      <c r="F116" t="s">
+        <v>613</v>
+      </c>
+      <c r="G116" t="s">
+        <v>623</v>
+      </c>
+      <c r="H116" t="s">
+        <v>615</v>
+      </c>
+      <c r="I116" t="s">
+        <v>604</v>
+      </c>
+      <c r="J116" s="68">
+        <v>46322</v>
+      </c>
+      <c r="K116" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11">
+      <c r="A117">
+        <v>114</v>
+      </c>
+      <c r="B117" t="s">
+        <v>256</v>
+      </c>
+      <c r="C117" t="s">
+        <v>257</v>
+      </c>
+      <c r="E117" s="68">
+        <v>46315</v>
+      </c>
+      <c r="F117" t="s">
+        <v>613</v>
+      </c>
+      <c r="G117" t="s">
+        <v>671</v>
+      </c>
+      <c r="H117" t="s">
+        <v>615</v>
+      </c>
+      <c r="I117" t="s">
+        <v>604</v>
+      </c>
+      <c r="J117" s="68">
+        <v>46322</v>
+      </c>
+      <c r="K117" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11">
+      <c r="A118">
+        <v>115</v>
+      </c>
+      <c r="B118" t="s">
+        <v>270</v>
+      </c>
+      <c r="C118" t="s">
+        <v>653</v>
+      </c>
+      <c r="E118" s="68">
+        <v>46317</v>
+      </c>
+      <c r="F118" t="s">
+        <v>613</v>
+      </c>
+      <c r="G118" t="s">
+        <v>683</v>
+      </c>
+      <c r="H118" t="s">
+        <v>615</v>
+      </c>
+      <c r="I118" t="s">
+        <v>604</v>
+      </c>
+      <c r="J118" s="68">
+        <v>46324</v>
+      </c>
+      <c r="K118" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11">
+      <c r="A119">
+        <v>116</v>
+      </c>
+      <c r="B119" t="s">
+        <v>440</v>
+      </c>
+      <c r="C119" t="s">
+        <v>612</v>
+      </c>
+      <c r="E119" s="68">
+        <v>46318</v>
+      </c>
+      <c r="F119" t="s">
+        <v>613</v>
+      </c>
+      <c r="G119" t="s">
+        <v>684</v>
+      </c>
+      <c r="H119" t="s">
+        <v>615</v>
+      </c>
+      <c r="I119" t="s">
+        <v>637</v>
+      </c>
+      <c r="J119" s="68"/>
+      <c r="K119" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11">
+      <c r="A120">
+        <v>117</v>
+      </c>
+      <c r="B120" t="s">
+        <v>530</v>
+      </c>
+      <c r="C120" t="s">
+        <v>206</v>
+      </c>
+      <c r="D120" t="s">
+        <v>618</v>
+      </c>
+      <c r="E120" s="68">
+        <v>46318</v>
+      </c>
+      <c r="F120" t="s">
+        <v>613</v>
+      </c>
+      <c r="G120" t="s">
+        <v>685</v>
+      </c>
+      <c r="H120" t="s">
+        <v>615</v>
+      </c>
+      <c r="I120" t="s">
+        <v>604</v>
+      </c>
+      <c r="J120" s="68">
+        <v>46325</v>
+      </c>
+      <c r="K120" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11">
+      <c r="A121">
+        <v>118</v>
+      </c>
+      <c r="B121" t="s">
+        <v>542</v>
+      </c>
+      <c r="C121" t="s">
+        <v>206</v>
+      </c>
+      <c r="D121" t="s">
+        <v>628</v>
+      </c>
+      <c r="E121" s="68">
+        <v>46320</v>
+      </c>
+      <c r="F121" t="s">
+        <v>613</v>
+      </c>
+      <c r="G121" t="s">
+        <v>629</v>
+      </c>
+      <c r="H121" t="s">
+        <v>615</v>
+      </c>
+      <c r="I121" t="s">
+        <v>637</v>
+      </c>
+      <c r="J121" s="68"/>
+      <c r="K121" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11">
+      <c r="A122">
+        <v>119</v>
+      </c>
+      <c r="B122" t="s">
+        <v>530</v>
+      </c>
+      <c r="C122" t="s">
+        <v>206</v>
+      </c>
+      <c r="D122" t="s">
+        <v>618</v>
+      </c>
+      <c r="E122" s="68">
+        <v>46320</v>
+      </c>
+      <c r="F122" t="s">
+        <v>613</v>
+      </c>
+      <c r="G122" t="s">
+        <v>686</v>
+      </c>
+      <c r="H122" t="s">
+        <v>615</v>
+      </c>
+      <c r="I122" t="s">
+        <v>604</v>
+      </c>
+      <c r="J122" s="68">
+        <v>46327</v>
+      </c>
+      <c r="K122" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11">
+      <c r="A123">
+        <v>120</v>
+      </c>
+      <c r="B123" t="s">
+        <v>177</v>
+      </c>
+      <c r="C123" t="s">
+        <v>633</v>
+      </c>
+      <c r="E123" s="68">
+        <v>46320</v>
+      </c>
+      <c r="F123" t="s">
+        <v>613</v>
+      </c>
+      <c r="G123" t="s">
+        <v>634</v>
+      </c>
+      <c r="H123" t="s">
+        <v>615</v>
+      </c>
+      <c r="I123" t="s">
+        <v>637</v>
+      </c>
+      <c r="J123" s="68"/>
+      <c r="K123" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11">
+      <c r="A124">
+        <v>121</v>
+      </c>
+      <c r="B124" t="s">
+        <v>212</v>
+      </c>
+      <c r="C124" t="s">
+        <v>215</v>
+      </c>
+      <c r="D124" t="s">
+        <v>620</v>
+      </c>
+      <c r="E124" s="68">
+        <v>46321</v>
+      </c>
+      <c r="F124" t="s">
+        <v>613</v>
+      </c>
+      <c r="G124" t="s">
+        <v>687</v>
+      </c>
+      <c r="H124" t="s">
+        <v>615</v>
+      </c>
+      <c r="I124" t="s">
+        <v>604</v>
+      </c>
+      <c r="J124" s="68">
+        <v>46328</v>
+      </c>
+      <c r="K124" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11">
+      <c r="A125">
+        <v>122</v>
+      </c>
+      <c r="B125" t="s">
+        <v>270</v>
+      </c>
+      <c r="C125" t="s">
+        <v>653</v>
+      </c>
+      <c r="E125" s="68">
+        <v>46321</v>
+      </c>
+      <c r="F125" t="s">
+        <v>613</v>
+      </c>
+      <c r="G125" t="s">
+        <v>688</v>
+      </c>
+      <c r="H125" t="s">
+        <v>615</v>
+      </c>
+      <c r="I125" t="s">
+        <v>604</v>
+      </c>
+      <c r="J125" s="68">
+        <v>46328</v>
+      </c>
+      <c r="K125" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11">
+      <c r="A126">
+        <v>123</v>
+      </c>
+      <c r="B126" t="s">
+        <v>292</v>
+      </c>
+      <c r="C126" t="s">
+        <v>257</v>
+      </c>
+      <c r="E126" s="68">
+        <v>46322</v>
+      </c>
+      <c r="F126" t="s">
+        <v>613</v>
+      </c>
+      <c r="G126" t="s">
+        <v>640</v>
+      </c>
+      <c r="H126" t="s">
+        <v>615</v>
+      </c>
+      <c r="I126" t="s">
+        <v>604</v>
+      </c>
+      <c r="J126" s="68">
+        <v>46329</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11">
+      <c r="A127">
+        <v>124</v>
+      </c>
+      <c r="B127" t="s">
+        <v>440</v>
+      </c>
+      <c r="C127" t="s">
+        <v>612</v>
+      </c>
+      <c r="E127" s="68">
+        <v>46322</v>
+      </c>
+      <c r="F127" t="s">
+        <v>613</v>
+      </c>
+      <c r="G127" t="s">
+        <v>684</v>
+      </c>
+      <c r="H127" t="s">
+        <v>615</v>
+      </c>
+      <c r="I127" t="s">
+        <v>637</v>
+      </c>
+      <c r="J127" s="68"/>
+      <c r="K127" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11">
+      <c r="A128">
+        <v>125</v>
+      </c>
+      <c r="B128" t="s">
+        <v>256</v>
+      </c>
+      <c r="C128" t="s">
+        <v>257</v>
+      </c>
+      <c r="E128" s="68">
+        <v>46322</v>
+      </c>
+      <c r="F128" t="s">
+        <v>613</v>
+      </c>
+      <c r="G128" t="s">
+        <v>671</v>
+      </c>
+      <c r="H128" t="s">
+        <v>615</v>
+      </c>
+      <c r="I128" t="s">
+        <v>604</v>
+      </c>
+      <c r="J128" s="68">
+        <v>46329</v>
+      </c>
+      <c r="K128" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11">
+      <c r="A129">
+        <v>126</v>
+      </c>
+      <c r="B129" t="s">
+        <v>292</v>
+      </c>
+      <c r="C129" t="s">
+        <v>257</v>
+      </c>
+      <c r="E129" s="68">
+        <v>46323</v>
+      </c>
+      <c r="F129" t="s">
+        <v>613</v>
+      </c>
+      <c r="G129" t="s">
+        <v>640</v>
+      </c>
+      <c r="H129" t="s">
+        <v>615</v>
+      </c>
+      <c r="I129" t="s">
+        <v>604</v>
+      </c>
+      <c r="J129" s="68">
+        <v>46330</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11">
+      <c r="A130">
+        <v>127</v>
+      </c>
+      <c r="B130" t="s">
+        <v>261</v>
+      </c>
+      <c r="C130" t="s">
+        <v>653</v>
+      </c>
+      <c r="E130" s="68">
+        <v>46323</v>
+      </c>
+      <c r="F130" t="s">
+        <v>613</v>
+      </c>
+      <c r="G130" t="s">
+        <v>689</v>
+      </c>
+      <c r="H130" t="s">
+        <v>615</v>
+      </c>
+      <c r="I130" t="s">
+        <v>604</v>
+      </c>
+      <c r="J130" s="68">
+        <v>46330</v>
+      </c>
+      <c r="K130" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11">
+      <c r="A131">
+        <v>128</v>
+      </c>
+      <c r="B131" t="s">
+        <v>246</v>
+      </c>
+      <c r="C131" t="s">
+        <v>215</v>
+      </c>
+      <c r="E131" s="68">
+        <v>46323</v>
+      </c>
+      <c r="F131" t="s">
+        <v>613</v>
+      </c>
+      <c r="G131" t="s">
+        <v>690</v>
+      </c>
+      <c r="H131" t="s">
+        <v>615</v>
+      </c>
+      <c r="I131" t="s">
+        <v>604</v>
+      </c>
+      <c r="J131" s="68">
+        <v>46330</v>
+      </c>
+      <c r="K131" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11">
+      <c r="A132">
+        <v>129</v>
+      </c>
+      <c r="B132" t="s">
+        <v>521</v>
+      </c>
+      <c r="C132" t="s">
+        <v>206</v>
+      </c>
+      <c r="D132" t="s">
+        <v>618</v>
+      </c>
+      <c r="E132" s="68">
+        <v>46323</v>
+      </c>
+      <c r="F132" t="s">
+        <v>613</v>
+      </c>
+      <c r="G132" t="s">
+        <v>691</v>
+      </c>
+      <c r="H132" t="s">
+        <v>615</v>
+      </c>
+      <c r="I132" t="s">
+        <v>604</v>
+      </c>
+      <c r="J132" s="68">
+        <v>46330</v>
+      </c>
+      <c r="K132" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11">
+      <c r="A133">
+        <v>130</v>
+      </c>
+      <c r="B133" t="s">
+        <v>256</v>
+      </c>
+      <c r="C133" t="s">
+        <v>257</v>
+      </c>
+      <c r="E133" s="68">
+        <v>46323</v>
+      </c>
+      <c r="F133" t="s">
+        <v>613</v>
+      </c>
+      <c r="G133" t="s">
+        <v>671</v>
+      </c>
+      <c r="H133" t="s">
+        <v>615</v>
+      </c>
+      <c r="I133" t="s">
+        <v>604</v>
+      </c>
+      <c r="J133" s="68">
+        <v>46330</v>
+      </c>
+      <c r="K133" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11">
+      <c r="A134">
+        <v>131</v>
+      </c>
+      <c r="B134" t="s">
+        <v>553</v>
+      </c>
+      <c r="C134" t="s">
+        <v>215</v>
+      </c>
+      <c r="D134" t="s">
+        <v>620</v>
+      </c>
+      <c r="E134" s="68">
+        <v>46323</v>
+      </c>
+      <c r="F134" t="s">
+        <v>613</v>
+      </c>
+      <c r="G134" t="s">
+        <v>692</v>
+      </c>
+      <c r="H134" t="s">
+        <v>615</v>
+      </c>
+      <c r="I134" t="s">
+        <v>604</v>
+      </c>
+      <c r="J134" s="68">
+        <v>46330</v>
+      </c>
+      <c r="K134" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11">
+      <c r="A135">
+        <v>132</v>
+      </c>
+      <c r="B135" t="s">
+        <v>64</v>
+      </c>
+      <c r="C135" t="s">
+        <v>257</v>
+      </c>
+      <c r="D135" t="s">
+        <v>620</v>
+      </c>
+      <c r="E135" s="68">
+        <v>46324</v>
+      </c>
+      <c r="F135" t="s">
+        <v>613</v>
+      </c>
+      <c r="G135" t="s">
+        <v>693</v>
+      </c>
+      <c r="H135" t="s">
+        <v>615</v>
+      </c>
+      <c r="I135" t="s">
+        <v>604</v>
+      </c>
+      <c r="J135" s="68">
+        <v>46331</v>
+      </c>
+      <c r="K135" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11">
+      <c r="A136">
+        <v>133</v>
+      </c>
+      <c r="B136" t="s">
+        <v>490</v>
+      </c>
+      <c r="C136" t="s">
+        <v>206</v>
+      </c>
+      <c r="D136" t="s">
+        <v>618</v>
+      </c>
+      <c r="E136" s="68">
+        <v>46324</v>
+      </c>
+      <c r="F136" t="s">
+        <v>613</v>
+      </c>
+      <c r="G136" t="s">
+        <v>694</v>
+      </c>
+      <c r="H136" t="s">
+        <v>615</v>
+      </c>
+      <c r="I136" t="s">
+        <v>604</v>
+      </c>
+      <c r="J136" s="68">
+        <v>46331</v>
+      </c>
+      <c r="K136" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11">
+      <c r="A137">
+        <v>134</v>
+      </c>
+      <c r="B137" t="s">
+        <v>440</v>
+      </c>
+      <c r="C137" t="s">
+        <v>612</v>
+      </c>
+      <c r="E137" s="68">
+        <v>46324</v>
+      </c>
+      <c r="F137" t="s">
+        <v>613</v>
+      </c>
+      <c r="G137" t="s">
+        <v>695</v>
+      </c>
+      <c r="H137" t="s">
+        <v>615</v>
+      </c>
+      <c r="I137" t="s">
+        <v>637</v>
+      </c>
+      <c r="J137" s="68"/>
+      <c r="K137" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11">
+      <c r="A138">
+        <v>135</v>
+      </c>
+      <c r="B138" t="s">
+        <v>270</v>
+      </c>
+      <c r="C138" t="s">
+        <v>653</v>
+      </c>
+      <c r="E138" s="68">
+        <v>46324</v>
+      </c>
+      <c r="F138" t="s">
+        <v>613</v>
+      </c>
+      <c r="G138" t="s">
+        <v>696</v>
+      </c>
+      <c r="H138" t="s">
+        <v>615</v>
+      </c>
+      <c r="I138" t="s">
+        <v>604</v>
+      </c>
+      <c r="J138" s="68">
+        <v>46331</v>
+      </c>
+      <c r="K138" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11">
+      <c r="A139">
+        <v>136</v>
+      </c>
+      <c r="B139" t="s">
+        <v>463</v>
+      </c>
+      <c r="C139" t="s">
+        <v>206</v>
+      </c>
+      <c r="D139" t="s">
+        <v>618</v>
+      </c>
+      <c r="E139" s="68">
+        <v>46324</v>
+      </c>
+      <c r="F139" t="s">
+        <v>613</v>
+      </c>
+      <c r="G139" t="s">
+        <v>697</v>
+      </c>
+      <c r="H139" t="s">
+        <v>615</v>
+      </c>
+      <c r="I139" t="s">
+        <v>604</v>
+      </c>
+      <c r="J139" s="68">
+        <v>46331</v>
+      </c>
+      <c r="K139" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11">
+      <c r="A140">
+        <v>137</v>
+      </c>
+      <c r="B140" t="s">
+        <v>440</v>
+      </c>
+      <c r="C140" t="s">
+        <v>612</v>
+      </c>
+      <c r="E140" s="68">
+        <v>46325</v>
+      </c>
+      <c r="F140" t="s">
+        <v>613</v>
+      </c>
+      <c r="G140" t="s">
+        <v>684</v>
+      </c>
+      <c r="H140" t="s">
+        <v>615</v>
+      </c>
+      <c r="I140" t="s">
+        <v>604</v>
+      </c>
+      <c r="J140" s="68">
+        <v>46332</v>
+      </c>
+      <c r="K140" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -30663,26 +33993,26 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18.95">
       <c r="A1" s="34" t="s">
-        <v>635</v>
+        <v>698</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="B3" s="35" t="s">
-        <v>636</v>
+        <v>699</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>637</v>
+        <v>700</v>
       </c>
       <c r="D3" s="35" t="s">
-        <v>638</v>
+        <v>701</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="B4" s="36" t="s">
-        <v>639</v>
+        <v>702</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>640</v>
+        <v>703</v>
       </c>
       <c r="D4" s="38">
         <v>7</v>
@@ -30690,13 +34020,13 @@
     </row>
     <row r="5" spans="1:4" ht="45.95" customHeight="1">
       <c r="B5" s="36" t="s">
-        <v>641</v>
+        <v>704</v>
       </c>
       <c r="C5" s="39" t="s">
-        <v>642</v>
+        <v>705</v>
       </c>
       <c r="D5" s="39" t="s">
-        <v>643</v>
+        <v>706</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="45.95" customHeight="1">
@@ -30704,109 +34034,109 @@
         <v>12</v>
       </c>
       <c r="C6" s="39" t="s">
-        <v>644</v>
+        <v>707</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>645</v>
+        <v>708</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="45.95" customHeight="1">
       <c r="B7" s="36" t="s">
-        <v>646</v>
+        <v>709</v>
       </c>
       <c r="C7" s="39" t="s">
-        <v>647</v>
+        <v>710</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>648</v>
+        <v>711</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="45.95" customHeight="1">
       <c r="B8" s="36" t="s">
-        <v>649</v>
+        <v>712</v>
       </c>
       <c r="C8" s="39" t="s">
-        <v>650</v>
+        <v>713</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>651</v>
+        <v>714</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="45.95" customHeight="1">
       <c r="B9" s="36" t="s">
-        <v>652</v>
+        <v>715</v>
       </c>
       <c r="C9" s="39" t="s">
-        <v>653</v>
+        <v>716</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>654</v>
+        <v>717</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="45.95" customHeight="1">
       <c r="B10" s="36" t="s">
-        <v>655</v>
+        <v>718</v>
       </c>
       <c r="C10" s="39" t="s">
-        <v>656</v>
+        <v>719</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>657</v>
+        <v>720</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="45.95" customHeight="1">
       <c r="B11" s="36" t="s">
-        <v>658</v>
+        <v>721</v>
       </c>
       <c r="C11" s="39" t="s">
-        <v>659</v>
+        <v>722</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>660</v>
+        <v>723</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="45.95" customHeight="1">
       <c r="B12" s="36" t="s">
-        <v>661</v>
+        <v>724</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>662</v>
+        <v>725</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>663</v>
+        <v>726</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="45.95" customHeight="1">
       <c r="B13" s="36" t="s">
-        <v>664</v>
+        <v>727</v>
       </c>
       <c r="C13" s="39" t="s">
-        <v>665</v>
+        <v>728</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>666</v>
+        <v>729</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="45.95" customHeight="1">
       <c r="B14" s="36" t="s">
-        <v>667</v>
+        <v>730</v>
       </c>
       <c r="C14" s="39" t="s">
-        <v>668</v>
+        <v>731</v>
       </c>
       <c r="D14" s="39" t="s">
-        <v>669</v>
+        <v>732</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="45.95" customHeight="1">
       <c r="B15" s="36" t="s">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="C15" s="39" t="s">
-        <v>671</v>
+        <v>734</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>672</v>
+        <v>735</v>
       </c>
     </row>
   </sheetData>

--- a/data/Dev_Schedule.xlsx
+++ b/data/Dev_Schedule.xlsx
@@ -3087,8 +3087,23 @@
     <xf numFmtId="0" fontId="43" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3100,21 +3115,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5530,67 +5530,67 @@
       </c>
     </row>
     <row r="4" spans="2:21" ht="30" customHeight="1">
-      <c r="B4" s="79" t="s">
+      <c r="B4" s="74" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="88"/>
-      <c r="D4" s="79" t="s">
+      <c r="D4" s="74" t="s">
         <v>2</v>
       </c>
       <c r="E4" s="88"/>
-      <c r="F4" s="79" t="s">
+      <c r="F4" s="74" t="s">
         <v>3</v>
       </c>
       <c r="G4" s="88"/>
-      <c r="H4" s="79" t="s">
+      <c r="H4" s="74" t="s">
         <v>4</v>
       </c>
       <c r="I4" s="88"/>
-      <c r="J4" s="79" t="s">
+      <c r="J4" s="74" t="s">
         <v>5</v>
       </c>
       <c r="K4" s="88"/>
-      <c r="L4" s="79" t="s">
+      <c r="L4" s="74" t="s">
         <v>6</v>
       </c>
       <c r="M4" s="88"/>
-      <c r="N4" s="79" t="s">
+      <c r="N4" s="74" t="s">
         <v>7</v>
       </c>
       <c r="O4" s="88"/>
     </row>
     <row r="5" spans="2:21">
-      <c r="B5" s="80">
+      <c r="B5" s="76">
         <f>COUNTA('스위칭 업체 Switch vendors'!$G$5:$G$400)+COUNTA('스위칭 연동 Switching'!$G$5:$G$400)+COUNTA('서드파티 연동 3rd Party'!$G$5:$G$399)+COUNTA('우리가 공급사 OMH Supply'!$G$5:$G$399)+COUNTA('상호연동 Two-way'!$G$5:$G$400)</f>
         <v>142</v>
       </c>
       <c r="C5" s="88"/>
-      <c r="D5" s="81">
+      <c r="D5" s="77">
         <f>COUNTIF('스위칭 업체 Switch vendors'!$B$5:$B$400,"Live")+COUNTIF('스위칭 업체 Switch vendors'!$B$5:$B$400,"Partially Live")+COUNTIF('스위칭 연동 Switching'!$B$5:$B$400,"Live")+COUNTIF('스위칭 연동 Switching'!$B$5:$B$400,"Partially Live")+COUNTIF('서드파티 연동 3rd Party'!$B$5:$B$399,"Live")+COUNTIF('서드파티 연동 3rd Party'!$B$5:$B$399,"Partially Live")+COUNTIF('우리가 공급사 OMH Supply'!$B$5:$B$399,"Live")+COUNTIF('우리가 공급사 OMH Supply'!$B$5:$B$399,"Partially Live")+COUNTIF('상호연동 Two-way'!$B$5:$B$400,"Live")+COUNTIF('상호연동 Two-way'!$B$5:$B$400,"Partially Live")</f>
         <v>35</v>
       </c>
       <c r="E5" s="88"/>
-      <c r="F5" s="82">
+      <c r="F5" s="78">
         <f>COUNTIF('스위칭 업체 Switch vendors'!$B$5:$B$400,"In Development")+COUNTIF('스위칭 업체 Switch vendors'!$B$5:$B$400,"Testing")+COUNTIF('스위칭 업체 Switch vendors'!$B$5:$B$400,"Pending Live")+COUNTIF('스위칭 연동 Switching'!$B$5:$B$400,"In Development")+COUNTIF('스위칭 연동 Switching'!$B$5:$B$400,"Testing")+COUNTIF('스위칭 연동 Switching'!$B$5:$B$400,"Pending Live")+COUNTIF('서드파티 연동 3rd Party'!$B$5:$B$399,"In Development")+COUNTIF('서드파티 연동 3rd Party'!$B$5:$B$399,"Testing")+COUNTIF('서드파티 연동 3rd Party'!$B$5:$B$399,"Pending Live")+COUNTIF('우리가 공급사 OMH Supply'!$B$5:$B$399,"In Development")+COUNTIF('우리가 공급사 OMH Supply'!$B$5:$B$399,"Testing")+COUNTIF('우리가 공급사 OMH Supply'!$B$5:$B$399,"Pending Live")+COUNTIF('상호연동 Two-way'!$B$5:$B$400,"In Development")+COUNTIF('상호연동 Two-way'!$B$5:$B$400,"Testing")+COUNTIF('상호연동 Two-way'!$B$5:$B$400,"Pending Live")</f>
         <v>14</v>
       </c>
       <c r="G5" s="88"/>
-      <c r="H5" s="76">
+      <c r="H5" s="81">
         <f>COUNTIF('스위칭 업체 Switch vendors'!$B$5:$B$400,"NDA/Contract")+COUNTIF('스위칭 연동 Switching'!$B$5:$B$400,"NDA/Contract")+COUNTIF('서드파티 연동 3rd Party'!$B$5:$B$399,"NDA/Contract")+COUNTIF('우리가 공급사 OMH Supply'!$B$5:$B$399,"NDA/Contract")+COUNTIF('상호연동 Two-way'!$B$5:$B$400,"NDA/Contract")</f>
         <v>16</v>
       </c>
       <c r="I5" s="88"/>
-      <c r="J5" s="77">
+      <c r="J5" s="82">
         <f>COUNTIF('스위칭 업체 Switch vendors'!$B$5:$B$400,"Pipeline")+COUNTIF('스위칭 업체 Switch vendors'!$B$5:$B$400,"Contact")+COUNTIF('스위칭 연동 Switching'!$B$5:$B$400,"Pipeline")+COUNTIF('스위칭 연동 Switching'!$B$5:$B$400,"Contact")+COUNTIF('서드파티 연동 3rd Party'!$B$5:$B$399,"Pipeline")+COUNTIF('서드파티 연동 3rd Party'!$B$5:$B$399,"Contact")+COUNTIF('우리가 공급사 OMH Supply'!$B$5:$B$399,"Pipeline")+COUNTIF('우리가 공급사 OMH Supply'!$B$5:$B$399,"Contact")+COUNTIF('상호연동 Two-way'!$B$5:$B$400,"Pipeline")+COUNTIF('상호연동 Two-way'!$B$5:$B$400,"Contact")</f>
         <v>77</v>
       </c>
       <c r="K5" s="88"/>
-      <c r="L5" s="74">
+      <c r="L5" s="79">
         <f ca="1">COUNTIF('스위칭 업체 Switch vendors'!$V$5:$V$400,"Stalled 60d+")+COUNTIF('스위칭 업체 Switch vendors'!$V$5:$V$400,"Stalled 90d+")+COUNTIF('스위칭 연동 Switching'!$S$5:$S$400,"Stalled 60d+")+COUNTIF('스위칭 연동 Switching'!$S$5:$S$400,"Stalled 90d+")+COUNTIF('서드파티 연동 3rd Party'!$S$5:$S$399,"Stalled 60d+")+COUNTIF('서드파티 연동 3rd Party'!$S$5:$S$399,"Stalled 90d+")+COUNTIF('우리가 공급사 OMH Supply'!$S$5:$S$399,"Stalled 60d+")+COUNTIF('우리가 공급사 OMH Supply'!$S$5:$S$399,"Stalled 90d+")+COUNTIF('상호연동 Two-way'!$V$5:$V$400,"Stalled 60d+")+COUNTIF('상호연동 Two-way'!$V$5:$V$400,"Stalled 90d+")</f>
         <v>14</v>
       </c>
       <c r="M5" s="88"/>
-      <c r="N5" s="78">
+      <c r="N5" s="73">
         <f ca="1">COUNTIF('스위칭 업체 Switch vendors'!$AC$5:$AC$400,"Chase Overdue")+COUNTIF('스위칭 업체 Switch vendors'!$AC$5:$AC$400,"Chase Needed")+COUNTIF('스위칭 연동 Switching'!$Z$5:$Z$400,"Chase Overdue")+COUNTIF('스위칭 연동 Switching'!$Z$5:$Z$400,"Chase Needed")+COUNTIF('서드파티 연동 3rd Party'!$Z$5:$Z$399,"Chase Overdue")+COUNTIF('서드파티 연동 3rd Party'!$Z$5:$Z$399,"Chase Needed")+COUNTIF('우리가 공급사 OMH Supply'!$Z$5:$Z$399,"Chase Overdue")+COUNTIF('우리가 공급사 OMH Supply'!$Z$5:$Z$399,"Chase Needed")+COUNTIF('상호연동 Two-way'!$AC$5:$AC$400,"Chase Overdue")+COUNTIF('상호연동 Two-way'!$AC$5:$AC$400,"Chase Needed")</f>
         <v>45</v>
       </c>
@@ -6512,7 +6512,7 @@
       <c r="G36" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="H36" s="75" t="s">
+      <c r="H36" s="80" t="s">
         <v>53</v>
       </c>
       <c r="I36" s="89"/>
@@ -6540,7 +6540,7 @@
       <c r="G37" s="15">
         <v>406</v>
       </c>
-      <c r="H37" s="73"/>
+      <c r="H37" s="75"/>
       <c r="I37" s="89"/>
       <c r="J37" s="89"/>
       <c r="K37" s="89"/>
@@ -6566,7 +6566,7 @@
       <c r="G38" s="15">
         <v>402</v>
       </c>
-      <c r="H38" s="73" t="s">
+      <c r="H38" s="75" t="s">
         <v>56</v>
       </c>
       <c r="I38" s="89"/>
@@ -6594,7 +6594,7 @@
       <c r="G39" s="15">
         <v>357</v>
       </c>
-      <c r="H39" s="73"/>
+      <c r="H39" s="75"/>
       <c r="I39" s="89"/>
       <c r="J39" s="89"/>
       <c r="K39" s="89"/>
@@ -6620,7 +6620,7 @@
       <c r="G40" s="15">
         <v>321</v>
       </c>
-      <c r="H40" s="73"/>
+      <c r="H40" s="75"/>
       <c r="I40" s="89"/>
       <c r="J40" s="89"/>
       <c r="K40" s="89"/>
@@ -6646,7 +6646,7 @@
       <c r="G41" s="15">
         <v>313</v>
       </c>
-      <c r="H41" s="73" t="s">
+      <c r="H41" s="75" t="s">
         <v>60</v>
       </c>
       <c r="I41" s="89"/>
@@ -6674,7 +6674,7 @@
       <c r="G42" s="15">
         <v>287</v>
       </c>
-      <c r="H42" s="73"/>
+      <c r="H42" s="75"/>
       <c r="I42" s="89"/>
       <c r="J42" s="89"/>
       <c r="K42" s="89"/>
@@ -6700,7 +6700,7 @@
       <c r="G43" s="15">
         <v>102</v>
       </c>
-      <c r="H43" s="73" t="s">
+      <c r="H43" s="75" t="s">
         <v>63</v>
       </c>
       <c r="I43" s="89"/>
@@ -6728,7 +6728,7 @@
       <c r="G44" s="15">
         <v>101</v>
       </c>
-      <c r="H44" s="73"/>
+      <c r="H44" s="75"/>
       <c r="I44" s="89"/>
       <c r="J44" s="89"/>
       <c r="K44" s="89"/>
@@ -6754,7 +6754,7 @@
       <c r="G45" s="15">
         <v>68</v>
       </c>
-      <c r="H45" s="73" t="s">
+      <c r="H45" s="75" t="s">
         <v>66</v>
       </c>
       <c r="I45" s="89"/>
@@ -6782,7 +6782,7 @@
       <c r="G46" s="15">
         <v>68</v>
       </c>
-      <c r="H46" s="73" t="s">
+      <c r="H46" s="75" t="s">
         <v>66</v>
       </c>
       <c r="I46" s="89"/>
@@ -6810,7 +6810,7 @@
       <c r="G47" s="15">
         <v>66</v>
       </c>
-      <c r="H47" s="73" t="s">
+      <c r="H47" s="75" t="s">
         <v>68</v>
       </c>
       <c r="I47" s="89"/>
@@ -6838,7 +6838,7 @@
       <c r="G48" s="15">
         <v>66</v>
       </c>
-      <c r="H48" s="73"/>
+      <c r="H48" s="75"/>
       <c r="I48" s="89"/>
       <c r="J48" s="89"/>
       <c r="K48" s="89"/>
@@ -6864,7 +6864,7 @@
       <c r="G49" s="15">
         <v>61</v>
       </c>
-      <c r="H49" s="73" t="s">
+      <c r="H49" s="75" t="s">
         <v>71</v>
       </c>
       <c r="I49" s="89"/>
@@ -6875,18 +6875,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="N5:O6"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="H38:M38"/>
-    <mergeCell ref="B5:C6"/>
-    <mergeCell ref="D5:E6"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F5:G6"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="L4:M4"/>
     <mergeCell ref="H40:M40"/>
     <mergeCell ref="H39:M39"/>
     <mergeCell ref="L5:M6"/>
@@ -6903,6 +6891,18 @@
     <mergeCell ref="H43:M43"/>
     <mergeCell ref="H41:M41"/>
     <mergeCell ref="H44:M44"/>
+    <mergeCell ref="N5:O6"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="H38:M38"/>
+    <mergeCell ref="B5:C6"/>
+    <mergeCell ref="D5:E6"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G6"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="L4:M4"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
